--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -27,7 +27,8 @@
     <sheet name="🏪 Shop" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="🧬 Classes" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="🌳 Skill Tree" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="🐉 World Bosses" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="🏷️ Titres" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="🐉 World Bosses" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,7 +482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Généré le 2026-05-06 10:22 UTC</t>
+          <t>Généré le 2026-05-06 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -5994,6 +5995,242 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Icône</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Exclusif</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Cible / Valeur</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Effets</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>slime_slayer</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Slime Slayer</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>kills_family</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>slime / 100</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>damage_bonus_vs_family → target=slime, value=10
+damage_reduction_from_family → target=slime, value=10</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Tueur de slimes confirmé. +10% dégâts infligés et -10% dégâts subis face aux slimes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>gobelin_slayer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Gobelin Slayer</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>👹</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>kills_family</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>gobelin / 100</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>damage_bonus_vs_family → target=gobelin, value=10
+damage_reduction_from_family → target=gobelin, value=10</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bourreau des gobelins. +10% dégâts infligés et -10% dégâts subis face aux gobelins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>champion_1v1</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Champion en 1vs1</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>👑</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>duel_top1</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>champion_all_stats → value=1</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Détenteur du sommet du ladder 1v1. +1% sur toutes vos stats (multiplicatif sur PV/atk/def, additif sur crit/esquive, +1 flat sur vitesse/régen). Perdu dès qu'un autre joueur prend la première place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>farmer_fou</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Le Farmer Fou</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🌾</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>kills_record</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>gold_xp_bonus_pct → value=1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Détenteur du record absolu de monstres tués. +1% sur l'or et l'XP gagnés à la fin d'un combat (uniquement pour le détenteur). Perdu dès qu'un autre joueur dépasse votre record.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Généré le 2026-05-06 11:26 UTC</t>
+          <t>Généré le 2026-05-06 11:52 UTC</t>
         </is>
       </c>
     </row>
@@ -5995,15 +5995,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
@@ -6217,6 +6217,510 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>Détenteur du record absolu de monstres tués. +1% sur l'or et l'XP gagnés à la fin d'un combat (uniquement pour le détenteur). Perdu dès qu'un autre joueur dépasse votre record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>bourreau</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Le Bourreau</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>kills_total</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → value=5</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Tueur impitoyable de 500 monstres au total. +5% sur les dégâts critiques (additif sur crit_damage).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>intouchable</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>L'Intouchable</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>🌪️</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>dodges_total</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>dodge_flat → value=1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Esquiveur aguerri (100 esquives encaissées en combat de groupe). +1% d'esquive permanent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>taverne_addict</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Taverne Addict</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>🍺</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>daily_streak</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>daily_bonus_item → target=potion_soin_i, value=1</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Daily streak de 30 jours. Reçoit en bonus une potion de soin I à chaque /daily (en plus de l'or).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>slime_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Slime</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>slime / 50</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=slime, value=5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>50 slimes tués. +5% drop rate sur les slimes (multiplicatif, préserve la rareté).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Gobelin</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>gobelin / 50</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=gobelin, value=5</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>50 gobelins tués. +5% drop rate sur les gobelins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>gobelin_combattant_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Gobelin Combattant</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>gobelin_combattant / 50</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_combattant, value=5</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>50 gobelins combattants tués. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_chaman_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Gobelin Chaman</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_chaman / 50</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_chaman, value=5</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>50 gobelins chamans tués. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>gobelin_geant_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Gobelin Géant</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>gobelin_geant / 50</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_geant, value=5</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>50 gobelins géants tués. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_runique_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Gobelin Runique</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_runique / 50</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_runique, value=5</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>50 gobelins runiques tués. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>gobelin_ballon_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Gobelin Ballon</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>gobelin_ballon / 50</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_ballon, value=5</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>50 gobelins ballons tués. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_assassin_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Gobelin Assassin</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_assassin / 50</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_assassin, value=5</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>50 gobelins assassins tués. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>gobelin_superieur_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Gobelin Supérieur</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>gobelin_superieur / 50</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_superieur, value=5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>50 gobelins supérieurs tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -28,7 +28,8 @@
     <sheet name="🧬 Classes" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="🌳 Skill Tree" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="🏷️ Titres" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="🐉 World Bosses" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="🌸 Panoplies" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="🐉 World Bosses" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Généré le 2026-05-06 11:52 UTC</t>
+          <t>Généré le 2026-05-07 06:13 UTC</t>
         </is>
       </c>
     </row>
@@ -647,11 +648,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -936,6 +937,130 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>slime_bracelet</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bracelet de slime</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bracelet</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>18</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_bracelet</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Bracelet gobelin</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>bracelet</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -947,7 +1072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1236,6 +1361,192 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>leather_bague</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bague en cuir</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bague</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>slime_bague</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Bague de slime</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>bague</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>linen_bague</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bague en lin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>bague</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>12</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1247,11 +1558,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -1412,6 +1723,254 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>iron_ceinture</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ceinture en fer</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ceinture</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>24</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie iron — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>slime_ceinture</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Ceinture de slime</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>ceinture</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>gobelin_ceinture</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ceinture gobelin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ceinture</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>21</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>linen_ceinture</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Ceinture en lin</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>ceinture</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1423,10 +1982,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -1650,6 +2209,192 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>iron_cape</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Cape en fer</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>cape</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie iron — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>leather_cape</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cape en cuir</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>cape</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_cape</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Cape gobelin</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>cape</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1661,10 +2406,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -1823,6 +2568,316 @@
       <c r="P2" s="3" t="inlineStr">
         <is>
           <t>Petit ornement d'oreille modestement enchanté.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>iron_boucle_oreille</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Boucle en fer</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>24</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie iron — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>leather_boucle_oreille</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Boucle en cuir</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>slime_boucle_oreille</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Boucle de slime</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>18</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_boucle_oreille</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Boucle gobelin</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>linen_boucle_oreille</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Boucle en lin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>12</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
@@ -6735,6 +7790,303 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Code famille</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Icône</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Items existants</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Palier 2 (type/value)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Palier 4</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Palier 8</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Palier 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Acier</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Armure lourde et fiable, taillée pour encaisser.</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>defense_flat +1</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>defense_flat +2</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>defense_flat +5</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>defense_flat +8</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>leather</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cuir</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🟫</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Souple et discret — favorise l'esquive.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>dodge_flat +1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>dodge_flat +2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>dodge_flat +5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>dodge_flat +8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>slime</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Slime</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Imprégnée de gelée régénératrice.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>hp_regeneration_flat +1</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>hp_regeneration_flat +2</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>hp_regeneration_flat +5</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>hp_regeneration_flat +8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Gobeline</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>👹</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Affutée par les fourbes habitudes des gobelins.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>crit_chance_flat +1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>crit_chance_flat +2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>crit_chance_flat +5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>crit_chance_flat +8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>linen</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Lin</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>🧵</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Tissu léger imprégné d'aura magique.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>crit_damage_flat +1</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>crit_damage_flat +2</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>crit_damage_flat +5</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>crit_damage_flat +8</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7069,7 +8421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7606,6 +8958,130 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>leather_main_droite</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Lame en cuir</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>12</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>linen_main_droite</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Lame en lin</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7617,10 +9093,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -7906,6 +9382,192 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>leather_main_gauche</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bouclier en cuir</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>main_gauche</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_main_gauche</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Bouclier gobelin</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>main_gauche</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>linen_main_gauche</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bouclier en lin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>main_gauche</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>12</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7917,7 +9579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -8268,6 +9930,68 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>slime_casque</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Casque de slime</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>casque</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8279,11 +10003,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -8568,6 +10292,130 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>slime_plastron</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Plastron de slime</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>plastron</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>18</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_plastron</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Plastron gobelin</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>plastron</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8579,11 +10427,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -8806,6 +10654,192 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>slime_jambieres</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Jambières de slime</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>jambieres</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>gobelin_jambieres</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jambières gobelin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>jambieres</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>21</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>linen_jambieres</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Jambières en lin</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>jambieres</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8817,11 +10851,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -9044,6 +11078,192 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>slime_bottes</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Bottes de slime</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>bottes</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>gobelin_bottes</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bottes gobelin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bottes</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>21</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>linen_bottes</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Bottes en lin</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>bottes</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9055,10 +11275,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -9282,6 +11502,192 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>iron_collier</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Collier en fer</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>collier</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie iron — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>leather_collier</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Collier en cuir</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>collier</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>linen_collier</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Collier en lin</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>collier</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Généré le 2026-05-07 06:13 UTC</t>
+          <t>Généré le 2026-05-07 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Acier</t>
+          <t>Fer</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -7917,27 +7917,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Souple et discret — favorise l'esquive.</t>
+          <t>Souple et résistant, renforce la vitalité du porteur.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>dodge_flat +1</t>
+          <t>max_hp_flat +4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>dodge_flat +2</t>
+          <t>max_hp_flat +8</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>dodge_flat +5</t>
+          <t>max_hp_flat +20</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>dodge_flat +8</t>
+          <t>max_hp_flat +32</t>
         </is>
       </c>
     </row>
@@ -8007,27 +8007,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Affutée par les fourbes habitudes des gobelins.</t>
+          <t>Affutée par les fourbes habitudes des gobelins — frappe rare mais brutale.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>crit_chance_flat +1</t>
+          <t>crit_damage_flat +1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>crit_chance_flat +2</t>
+          <t>crit_damage_flat +2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>crit_chance_flat +5</t>
+          <t>crit_damage_flat +4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>crit_chance_flat +8</t>
+          <t>crit_damage_flat +8</t>
         </is>
       </c>
     </row>
@@ -8052,27 +8052,27 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Tissu léger imprégné d'aura magique.</t>
+          <t>Tissu léger qui favorise l'agilité et l'esquive.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>crit_damage_flat +1</t>
+          <t>dodge_flat +1</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>crit_damage_flat +2</t>
+          <t>dodge_flat +2</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>crit_damage_flat +5</t>
+          <t>dodge_flat +3</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>crit_damage_flat +8</t>
+          <t>dodge_flat +5</t>
         </is>
       </c>
     </row>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Généré le 2026-05-07 07:46 UTC</t>
+          <t>Généré le 2026-05-07 18:18 UTC</t>
         </is>
       </c>
     </row>
@@ -3398,12 +3398,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
@@ -4636,6 +4636,1946 @@
           <t>slime_gel ×4
 wood_log ×3
 leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>gobelin_plastron_recipe</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Plastron gobelin</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>gobelin_plastron</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>chest</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>plastron</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>gobelin_tooth ×5
+iron_ingot ×2
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_jambieres_recipe</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Jambières gobelin</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_jambieres</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>legs</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>jambieres</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>gobelin_tooth ×4
+iron_ingot ×2
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>gobelin_bottes_recipe</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Bottes gobelin</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>gobelin_bottes</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>boots</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>bottes</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>gobelin_tooth ×3
+iron_ingot ×1
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_main_gauche_recipe</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Bouclier gobelin</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_main_gauche</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>main_gauche</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>gobelin_tooth ×3
+iron_ingot ×1
+wood_log ×2
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>gobelin_bracelet_recipe</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Bracelet gobelin</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>gobelin_bracelet</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>bracelet</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>bracelet</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>gobelin_tooth ×2
+iron_ingot ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_ceinture_recipe</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Ceinture gobelin</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_ceinture</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>belt</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>ceinture</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>gobelin_tooth ×2
+iron_ingot ×1
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>gobelin_cape_recipe</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Cape gobelin</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>gobelin_cape</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>cape</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>cape</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>gobelin_tooth ×4
+linen_cloth ×2
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_boucle_oreille_recipe</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Boucle gobelin</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_boucle_oreille</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>earring</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>gobelin_tooth ×2
+polished_stone ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>iron_collier_recipe</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Collier en fer</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>iron_collier</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>necklace</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>collier</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>iron_ingot ×4
+polished_stone ×1
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>iron_ceinture_recipe</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Ceinture en fer</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>iron_ceinture</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>belt</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>ceinture</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>iron_ingot ×2
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>iron_cape_recipe</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cape en fer</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>iron_cape</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>cape</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>cape</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>iron_ingot ×4
+linen_cloth ×2
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>iron_boucle_oreille_recipe</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Boucle en fer</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>iron_boucle_oreille</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>earring</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>iron_ingot ×2
+polished_stone ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>leather_main_droite_recipe</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Lame en cuir</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>leather_main_droite</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>leather_strip ×3
+wood_log ×2
+iron_ingot ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>leather_main_gauche_recipe</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Bouclier en cuir</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>leather_main_gauche</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>main_gauche</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>leather_strip ×3
+wood_log ×3
+iron_ingot ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>leather_collier_recipe</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Collier en cuir</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>leather_collier</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>necklace</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>collier</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>leather_strip ×4
+polished_stone ×1
+linen_cloth ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>leather_bague_recipe</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Bague en cuir</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>leather_bague</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>ring</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>bague</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>leather_strip ×2
+polished_stone ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>leather_cape_recipe</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Cape en cuir</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>leather_cape</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>cape</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>cape</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>leather_strip ×5
+linen_cloth ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>leather_boucle_oreille_recipe</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Boucle en cuir</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>leather_boucle_oreille</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>earring</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>leather_strip ×2
+polished_stone ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>linen_jambieres_recipe</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Jambières en lin</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>linen_jambieres</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>legs</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>jambieres</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>linen_cloth ×4
+leather_strip ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>linen_bottes_recipe</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Bottes en lin</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>linen_bottes</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>boots</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>bottes</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>linen_cloth ×3
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>linen_main_droite_recipe</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Lame en lin</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>linen_main_droite</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>linen_cloth ×3
+wood_log ×2
+iron_ingot ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>linen_main_gauche_recipe</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Bouclier en lin</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>linen_main_gauche</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>main_gauche</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>linen_cloth ×3
+wood_log ×3
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>linen_collier_recipe</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Collier en lin</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>linen_collier</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>necklace</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>collier</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>linen_cloth ×4
+polished_stone ×1
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>linen_bague_recipe</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Bague en lin</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>linen_bague</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>ring</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>bague</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>linen_cloth ×2
+polished_stone ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>linen_ceinture_recipe</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Ceinture en lin</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>linen_ceinture</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>belt</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ceinture</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>linen_cloth ×2
+iron_ingot ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>linen_boucle_oreille_recipe</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Boucle en lin</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>linen_boucle_oreille</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>earring</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>linen_cloth ×2
+polished_stone ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>slime_casque_recipe</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Casque de slime</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>slime_casque</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>helmet</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>casque</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>slime_gel ×4
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>slime_plastron_recipe</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Plastron de slime</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>slime_plastron</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>chest</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>plastron</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>slime_gel ×5
+leather_strip ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>slime_jambieres_recipe</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Jambières de slime</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>slime_jambieres</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>legs</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>jambieres</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>slime_gel ×4
+leather_strip ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>slime_bottes_recipe</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Bottes de slime</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>slime_bottes</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>boots</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>bottes</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>slime_gel ×3
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>slime_bracelet_recipe</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Bracelet de slime</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>slime_bracelet</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>bracelet</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>bracelet</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>slime_gel ×2
+iron_ingot ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>slime_bague_recipe</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Bague de slime</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>slime_bague</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>ring</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>bague</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>slime_gel ×2
+polished_stone ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>slime_ceinture_recipe</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Ceinture de slime</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>slime_ceinture</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>belt</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ceinture</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>slime_gel ×2
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>slime_boucle_oreille_recipe</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Boucle de slime</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>slime_boucle_oreille</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>earring</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>slime_gel ×2
+polished_stone ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>iron_sword_recipe</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Épée en fer</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>iron_sword</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>iron_ingot ×3
+wood_log ×1
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>iron_warshield_recipe</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Pavois en fer</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>iron_warshield</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>iron_ingot ×4
+leather_strip ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>iron_greatsword_recipe</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Espadon en fer</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>iron_greatsword</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>iron_ingot ×6
+wood_log ×3
+leather_strip ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>iron_tower_shield_recipe</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Tour en fer</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>iron_tower_shield</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>iron_ingot ×9
+leather_strip ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>slime_morningstar_recipe</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Morningstar visqueuse</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>slime_morningstar</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>slime_gel ×3
+wood_log ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>slime_buckler_recipe</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Bouclier de gel</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>slime_buckler</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>slime_gel ×3
+wood_log ×2
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>slime_greatblade_recipe</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Lame visqueuse colossale</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>slime_greatblade</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>slime_gel ×9
+wood_log ×6
+iron_ingot ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>slime_tower_shield_recipe</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Tour de gel</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>slime_tower_shield</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>slime_gel ×12
+wood_log ×9
+leather_strip ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>gobelin_buckler_recipe</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Rondache gobeline</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>gobelin_buckler</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>gobelin_tooth ×3
+iron_ingot ×1
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_greataxe_recipe</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Grande hache gobeline</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_greataxe</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>gobelin_tooth ×12
+iron_ingot ×6
+wood_log ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>gobelin_warshield_recipe</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Pavois gobelin</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>gobelin_warshield</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>gobelin_tooth ×9
+iron_ingot ×3
+wood_log ×6
+leather_strip ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>leather_dagger_recipe</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Dague en cuir</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>leather_dagger</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>leather_strip ×2
+wood_log ×2
+iron_ingot ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>leather_buckler_recipe</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Rondache en cuir</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>leather_buckler</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>leather_strip ×2
+wood_log ×2
+iron_ingot ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>leather_greatsword_recipe</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Grande lame en cuir</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>leather_greatsword</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>leather_strip ×9
+wood_log ×6
+iron_ingot ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>leather_tower_shield_recipe</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Tour en cuir</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>leather_tower_shield</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>leather_strip ×9
+wood_log ×9
+iron_ingot ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>linen_rapier_recipe</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Rapière en lin</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>linen_rapier</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>linen_cloth ×2
+wood_log ×2
+iron_ingot ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>linen_aegis_recipe</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Égide en lin</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>linen_aegis</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>linen_cloth ×2
+wood_log ×2
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>linen_greatblade_recipe</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Grande lame en lin</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>linen_greatblade</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>linen_cloth ×9
+wood_log ×6
+iron_ingot ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>linen_tower_shield_recipe</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tour en lin</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>linen_tower_shield</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>linen_cloth ×9
+wood_log ×9
+leather_strip ×3</t>
         </is>
       </c>
     </row>
@@ -7868,7 +9808,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -7913,7 +9853,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -7958,7 +9898,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -8003,7 +9943,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -8048,7 +9988,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -8421,10 +10361,1240 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Rareté</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Slot</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>2-mains</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Atk +</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Def +</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>PV +</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Crit chance +</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Crit dmg +</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Esquive +</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Vitesse +</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Regen +</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Prix vente</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Prix achat</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>wood_sword</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Épée en bois</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>Une arme basique pour débuter. Une main.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>slime_blade</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Lame visqueuse</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Une épée recouverte d'une étrange matière gélatineuse. Une main.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>hunter_dagger</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Dague du chasseur</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Une dague légère favorisant les coups précis. Une main.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>gobelin_axe</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hache gobeline</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>18</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hache fruste taillée par les gobelins. Une main.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>two_handed_iron_sword</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Espadon de fer</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Une longue lame qui demande de tenir des deux mains.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>iron_dagger</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dague en fer</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>12</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dague affûtée, légère et discrète.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>goblin_blade</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Lame gobeline</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Lame ébréchée mais redoutable, taillée d'os de gobelin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>leather_main_droite</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Lame en cuir</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>12</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>linen_main_droite</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Lame en lin</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>iron_sword</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Épée en fer</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>18</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Variante équilibrée de la dague en fer — atk + un peu de def/PV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>iron_greatsword</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Espadon en fer</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Lame à 2 mains — frappe lourde mais on s'expose en attaquant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>slime_morningstar</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Morningstar visqueuse</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" t="n">
+        <v>22</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Variante régen de la lame visqueuse — atk soutenue + un peu de régen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>slime_greatblade</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Lame visqueuse colossale</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>2 mains — frappe massive, on perd en résilience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>gobelin_greataxe</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Grande hache gobeline</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>18</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>15</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>80</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2 mains — crit massifs, on se découvre complètement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>leather_dagger</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Dague en cuir</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>Variante offensive de la lame en cuir — un peu d'attaque en plus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>leather_greatsword</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Grande lame en cuir</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>50</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2 mains — atk solide pour la panoplie cuir, on perd en couverture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>linen_rapier</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Rapière en lin</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>Variante speed/crit de la lame en lin — précise mais fragile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>linen_greatblade</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Grande lame en lin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>55</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2 mains — crit dmg massif mais peu de couverture.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -8527,12 +11697,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>wood_sword</t>
+          <t>wooden_shield</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Épée en bois</t>
+          <t>Bouclier en bois</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -8542,7 +11712,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>main_droite</t>
+          <t>main_gauche</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -8551,13 +11721,13 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -8575,26 +11745,26 @@
         <v>0</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Une arme basique pour débuter. Une main.</t>
+          <t>Un bouclier léger, à porter en main gauche.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>slime_blade</t>
+          <t>iron_buckler</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lame visqueuse</t>
+          <t>Rondache en fer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -8604,7 +11774,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>main_droite</t>
+          <t>main_gauche</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8613,13 +11783,13 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>5</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -8628,7 +11798,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -8637,26 +11807,26 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Une épée recouverte d'une étrange matière gélatineuse. Une main.</t>
+          <t>Un petit bouclier rond, à porter en main gauche.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>hunter_dagger</t>
+          <t>slime_shield</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Dague du chasseur</t>
+          <t>Bouclier visqueux</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -8666,7 +11836,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>main_droite</t>
+          <t>main_gauche</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -8675,16 +11845,16 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>0</v>
@@ -8699,36 +11869,36 @@
         <v>0</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Une dague légère favorisant les coups précis. Une main.</t>
+          <t>Bouclier en bois enveloppé de gel de slime — absorbe les chocs comme une éponge.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gobelin_axe</t>
+          <t>leather_main_gauche</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hache gobeline</t>
+          <t>Bouclier en cuir</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>main_droite</t>
+          <t>main_gauche</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -8737,10 +11907,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -8749,10 +11919,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -8761,45 +11931,45 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hache fruste taillée par les gobelins. Une main.</t>
+          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>two_handed_iron_sword</t>
+          <t>gobelin_main_gauche</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Espadon de fer</t>
+          <t>Bouclier gobelin</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>main_droite</t>
+          <t>main_gauche</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -8808,10 +11978,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -8823,26 +11993,26 @@
         <v>0</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>Une longue lame qui demande de tenir des deux mains.</t>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>iron_dagger</t>
+          <t>linen_main_gauche</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dague en fer</t>
+          <t>Bouclier en lin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8852,7 +12022,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>main_droite</t>
+          <t>main_gauche</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -8861,7 +12031,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -8870,46 +12040,46 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>2</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
         <v>12</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dague affûtée, légère et discrète.</t>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>goblin_blade</t>
+          <t>iron_warshield</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Lame gobeline</t>
+          <t>Pavois en fer</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -8923,19 +12093,19 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -8947,31 +12117,31 @@
         <v>0</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Lame ébréchée mais redoutable, taillée d'os de gobelin.</t>
+          <t>Variante tanky de la rondache — plus de PV, moins d'esquive.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>leather_main_droite</t>
+          <t>iron_tower_shield</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lame en cuir</t>
+          <t>Tour en fer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8981,54 +12151,54 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="O9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
+          <t>Bouclier-tour à 2 mains — forteresse mobile au prix de l'offensive.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>linen_main_droite</t>
+          <t>slime_buckler</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Lame en lin</t>
+          <t>Bouclier de gel</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -9050,7 +12220,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0</v>
@@ -9059,512 +12229,460 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Variante régen du bouclier visqueux — moins de PV, plus de régen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>slime_tower_shield</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tour de gel</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" t="n">
+        <v>18</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>70</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bouclier 2 mains — pure défense, on n'attaque presque plus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_buckler</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Rondache gobeline</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3" t="n">
+      <c r="J12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Variante du bouclier gobelin — orientée crit + défense.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>gobelin_warshield</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pavois gobelin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>60</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bouclier gobelin 2 mains — défense brute + crit, on tape moins fort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>leather_buckler</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Rondache en cuir</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="O10" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:P7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Rareté</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Slot</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2-mains</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Atk +</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Def +</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>PV +</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Crit chance +</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Crit dmg +</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>Esquive +</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>Vitesse +</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>Regen +</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>Prix vente</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>Prix achat</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>wooden_shield</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Bouclier en bois</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="I14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Variante tanky du bouclier en cuir — plus de PV, moins d'esquive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>leather_tower_shield</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tour en cuir</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>50</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bouclier 2 mains en cuir tanné — défense + esquive contre 0 attaque.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>linen_aegis</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Égide en lin</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>main_gauche</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3" t="n">
+      <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>Variante esquive du bouclier en lin — optimisée pour les agiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>linen_tower_shield</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tour en lin</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
         <v>3</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K17" t="n">
         <v>5</v>
       </c>
-      <c r="I2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>Un bouclier léger, à porter en main gauche.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>iron_buckler</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rondache en fer</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>main_gauche</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>14</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Un petit bouclier rond, à porter en main gauche.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>slime_shield</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Bouclier visqueux</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>main_gauche</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>Bouclier en bois enveloppé de gel de slime — absorbe les chocs comme une éponge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>leather_main_gauche</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Bouclier en cuir</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>main_gauche</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4</v>
-      </c>
-      <c r="O5" t="n">
-        <v>12</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>gobelin_main_gauche</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Bouclier gobelin</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>main_gauche</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>linen_main_gauche</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Bouclier en lin</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>main_gauche</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4</v>
-      </c>
-      <c r="O7" t="n">
-        <v>12</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>55</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bouclier 2 mains en lin — pure esquive, dégâts en chute libre.</t>
         </is>
       </c>
     </row>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Généré le 2026-05-07 18:18 UTC</t>
+          <t>Généré le 2026-05-07 19:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -3952,27 +3952,27 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>two_handed_iron_sword_recipe</t>
+          <t>iron_helmet_recipe</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Espadon de fer</t>
+          <t>Casque de fer</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>two_handed_iron_sword</t>
+          <t>iron_helmet</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>weapon</t>
+          <t>helmet</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>main_droite</t>
+          <t>casque</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
@@ -3980,186 +3980,149 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>iron_ingot ×8
-leather_strip ×2
-wood_log ×2</t>
+          <t>iron_ingot ×4
+leather_strip ×1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>iron_helmet_recipe</t>
+          <t>iron_chest_recipe</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Casque de fer</t>
+          <t>Plastron de fer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>iron_helmet</t>
+          <t>iron_chest</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>helmet</t>
+          <t>chest</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>casque</t>
+          <t>plastron</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>iron_ingot ×6
+leather_strip ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>iron_legs_recipe</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Jambières de fer</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>iron_legs</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>legs</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>jambieres</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>iron_ingot ×5
+leather_strip ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>iron_boots_recipe</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bottes en fer</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>iron_boots</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>boots</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>bottes</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>iron_ingot ×4
 leather_strip ×1</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>iron_chest_recipe</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Plastron de fer</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>iron_chest</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>chest</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>plastron</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>iron_ingot ×6
-leather_strip ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>iron_legs_recipe</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Jambières de fer</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>iron_legs</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>legs</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>jambieres</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>iron_ingot ×5
-leather_strip ×2</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>iron_boots_recipe</t>
+          <t>gobelin_crown_recipe</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Bottes en fer</t>
+          <t>Couronne gobeline</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>iron_boots</t>
+          <t>gobelin_crown</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>boots</t>
+          <t>helmet</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>bottes</t>
+          <t>casque</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>iron_ingot ×4
-leather_strip ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>gobelin_crown_recipe</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Couronne gobeline</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>gobelin_crown</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>helmet</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>casque</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>gobelin_tooth ×6
 polished_stone ×2
@@ -4167,20 +4130,55 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>iron_ring_recipe</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Anneau de fer</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>iron_ring</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ring</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>bague</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>iron_ingot ×2</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>iron_ring_recipe</t>
+          <t>gobelin_ring_recipe</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Anneau de fer</t>
+          <t>Bague gobeline</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>iron_ring</t>
+          <t>gobelin_ring</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -4196,42 +4194,7 @@
       <c r="F22" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>iron_ingot ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>gobelin_ring_recipe</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Bague gobeline</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>gobelin_ring</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>ring</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>bague</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>gobelin_tooth ×3
 iron_ingot ×1
@@ -4239,36 +4202,36 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>slime_pendant_recipe</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Pendentif de Slime</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>slime_pendant</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>necklace</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>collier</t>
         </is>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>slime_gel ×5
 polished_stone ×1
@@ -4276,30 +4239,66 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>linen_hood_recipe</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Capuche en lin</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>linen_hood</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>helmet</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>casque</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>linen_cloth ×4
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>linen_hood_recipe</t>
+          <t>linen_robe_recipe</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capuche en lin</t>
+          <t>Robe en lin</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>linen_hood</t>
+          <t>linen_robe</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>helmet</t>
+          <t>chest</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>casque</t>
+          <t>plastron</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -4307,7 +4306,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>linen_cloth ×4
+          <t>linen_cloth ×6
 leather_strip ×1</t>
         </is>
       </c>
@@ -4315,104 +4314,68 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>linen_robe_recipe</t>
+          <t>linen_gloves_recipe</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Robe en lin</t>
+          <t>Mitaines en lin</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>linen_robe</t>
+          <t>linen_gloves</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>chest</t>
+          <t>bracelet</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>plastron</t>
+          <t>bracelet</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>linen_cloth ×6
-leather_strip ×1</t>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>linen_cloth ×3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>linen_gloves_recipe</t>
+          <t>slime_cloak_recipe</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mitaines en lin</t>
+          <t>Cape gluante</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>linen_gloves</t>
+          <t>slime_cloak</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>bracelet</t>
+          <t>cape</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>bracelet</t>
+          <t>cape</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>linen_cloth ×3</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>slime_cloak_recipe</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Cape gluante</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>slime_cloak</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>cape</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>cape</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>slime_gel ×5
 linen_cloth ×3
@@ -4420,36 +4383,36 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>goblin_amulet_recipe</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Amulette gobeline</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>goblin_amulet</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>necklace</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>collier</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="F28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>gobelin_tooth ×5
 polished_stone ×2
@@ -4457,107 +4420,107 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>polished_stone_ring_recipe</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Anneau de pierre polie</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>polished_stone_ring</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ring</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>bague</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>polished_stone ×3</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>polished_stone_ring_recipe</t>
+          <t>iron_gauntlets_recipe</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Anneau de pierre polie</t>
+          <t>Gantelets en fer</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>polished_stone_ring</t>
+          <t>iron_gauntlets</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>ring</t>
+          <t>bracelet</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>bague</t>
+          <t>bracelet</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>polished_stone ×3</t>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>iron_ingot ×4
+leather_strip ×2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>iron_gauntlets_recipe</t>
+          <t>iron_dagger_recipe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gantelets en fer</t>
+          <t>Dague en fer</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>iron_gauntlets</t>
+          <t>iron_dagger</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>bracelet</t>
+          <t>weapon</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>bracelet</t>
+          <t>main_droite</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>iron_ingot ×4
-leather_strip ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>iron_dagger_recipe</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Dague en fer</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>iron_dagger</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>weapon</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>main_droite</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>iron_ingot ×2
 wood_log ×1
@@ -4565,36 +4528,36 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>goblin_blade_recipe</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Lame gobeline</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>goblin_blade</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>weapon</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>main_droite</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="F32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>gobelin_tooth ×4
 iron_ingot ×2
@@ -4602,36 +4565,36 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>slime_shield_recipe</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Bouclier visqueux</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>slime_shield</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>shield</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>main_gauche</t>
         </is>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>slime_gel ×4
 wood_log ×3
@@ -4639,36 +4602,36 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>gobelin_plastron_recipe</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Plastron gobelin</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>gobelin_plastron</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>chest</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>plastron</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="F34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>gobelin_tooth ×5
 iron_ingot ×2
@@ -4676,36 +4639,36 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>gobelin_jambieres_recipe</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Jambières gobelin</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>gobelin_jambieres</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>legs</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>jambieres</t>
         </is>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>gobelin_tooth ×4
 iron_ingot ×2
@@ -4713,36 +4676,36 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>gobelin_bottes_recipe</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Bottes gobelin</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>gobelin_bottes</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>boots</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>bottes</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="F36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>gobelin_tooth ×3
 iron_ingot ×1
@@ -4750,36 +4713,36 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>gobelin_main_gauche_recipe</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Bouclier gobelin</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>gobelin_main_gauche</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>shield</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>main_gauche</t>
         </is>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>gobelin_tooth ×3
 iron_ingot ×1
@@ -4788,72 +4751,72 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_bracelet_recipe</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Bracelet gobelin</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>gobelin_bracelet</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>bracelet</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>bracelet</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>gobelin_tooth ×2
+iron_ingot ×1</t>
+        </is>
+      </c>
+    </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>gobelin_bracelet_recipe</t>
+          <t>gobelin_ceinture_recipe</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bracelet gobelin</t>
+          <t>Ceinture gobelin</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>gobelin_bracelet</t>
+          <t>gobelin_ceinture</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>bracelet</t>
+          <t>belt</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>bracelet</t>
+          <t>ceinture</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>gobelin_tooth ×2
-iron_ingot ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>gobelin_ceinture_recipe</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Ceinture gobelin</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>gobelin_ceinture</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>belt</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>ceinture</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>gobelin_tooth ×2
 iron_ingot ×1
@@ -4861,36 +4824,36 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>gobelin_cape_recipe</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Cape gobelin</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>gobelin_cape</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>cape</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>cape</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="F40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>gobelin_tooth ×4
 linen_cloth ×2
@@ -4898,72 +4861,72 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>gobelin_boucle_oreille_recipe</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Boucle gobelin</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>gobelin_boucle_oreille</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>earring</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>gobelin_tooth ×2
+polished_stone ×1</t>
+        </is>
+      </c>
+    </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>gobelin_boucle_oreille_recipe</t>
+          <t>iron_collier_recipe</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Boucle gobelin</t>
+          <t>Collier en fer</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>gobelin_boucle_oreille</t>
+          <t>iron_collier</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>earring</t>
+          <t>necklace</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>boucle_oreille</t>
+          <t>collier</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>gobelin_tooth ×2
-polished_stone ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>iron_collier_recipe</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Collier en fer</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>iron_collier</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>necklace</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>collier</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>iron_ingot ×4
 polished_stone ×1
@@ -4971,72 +4934,72 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>iron_ceinture_recipe</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ceinture en fer</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>iron_ceinture</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>belt</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ceinture</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>iron_ingot ×2
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>iron_ceinture_recipe</t>
+          <t>iron_cape_recipe</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Ceinture en fer</t>
+          <t>Cape en fer</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>iron_ceinture</t>
+          <t>iron_cape</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>belt</t>
+          <t>cape</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>ceinture</t>
+          <t>cape</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>iron_ingot ×2
-leather_strip ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>iron_cape_recipe</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Cape en fer</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>iron_cape</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>cape</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>cape</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>iron_ingot ×4
 linen_cloth ×2
@@ -5044,72 +5007,72 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>iron_boucle_oreille_recipe</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Boucle en fer</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>iron_boucle_oreille</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>earring</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>iron_ingot ×2
+polished_stone ×1</t>
+        </is>
+      </c>
+    </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>iron_boucle_oreille_recipe</t>
+          <t>leather_main_droite_recipe</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Boucle en fer</t>
+          <t>Lame en cuir</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>iron_boucle_oreille</t>
+          <t>leather_main_droite</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>earring</t>
+          <t>weapon</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>boucle_oreille</t>
+          <t>main_droite</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>iron_ingot ×2
-polished_stone ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>leather_main_droite_recipe</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Lame en cuir</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>leather_main_droite</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>weapon</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>main_droite</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>leather_strip ×3
 wood_log ×2
@@ -5117,36 +5080,36 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>leather_main_gauche_recipe</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Bouclier en cuir</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>leather_main_gauche</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>shield</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>main_gauche</t>
         </is>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>leather_strip ×3
 wood_log ×3
@@ -5154,36 +5117,36 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>leather_collier_recipe</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Collier en cuir</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>leather_collier</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>necklace</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>collier</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="F48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>leather_strip ×4
 polished_stone ×1
@@ -5191,102 +5154,138 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>leather_bague_recipe</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Bague en cuir</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>leather_bague</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ring</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>bague</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>leather_strip ×2
+polished_stone ×1</t>
+        </is>
+      </c>
+    </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>leather_bague_recipe</t>
+          <t>leather_cape_recipe</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Bague en cuir</t>
+          <t>Cape en cuir</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>leather_bague</t>
+          <t>leather_cape</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>ring</t>
+          <t>cape</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>bague</t>
+          <t>cape</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>leather_strip ×5
+linen_cloth ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>leather_boucle_oreille_recipe</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Boucle en cuir</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>leather_boucle_oreille</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>earring</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>leather_strip ×2
 polished_stone ×1</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>leather_cape_recipe</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Cape en cuir</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>leather_cape</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>cape</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>cape</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>leather_strip ×5
-linen_cloth ×2</t>
-        </is>
-      </c>
-    </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>leather_boucle_oreille_recipe</t>
+          <t>linen_jambieres_recipe</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Boucle en cuir</t>
+          <t>Jambières en lin</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>leather_boucle_oreille</t>
+          <t>linen_jambieres</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>earring</t>
+          <t>legs</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>boucle_oreille</t>
+          <t>jambieres</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
@@ -5294,35 +5293,35 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>leather_strip ×2
-polished_stone ×1</t>
+          <t>linen_cloth ×4
+leather_strip ×2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>linen_jambieres_recipe</t>
+          <t>linen_bottes_recipe</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jambières en lin</t>
+          <t>Bottes en lin</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>linen_jambieres</t>
+          <t>linen_bottes</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>legs</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>jambieres</t>
+          <t>bottes</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5330,77 +5329,41 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>linen_cloth ×4
-leather_strip ×2</t>
+          <t>linen_cloth ×3
+leather_strip ×1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>linen_bottes_recipe</t>
+          <t>linen_main_droite_recipe</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Bottes en lin</t>
+          <t>Lame en lin</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>linen_bottes</t>
+          <t>linen_main_droite</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>boots</t>
+          <t>weapon</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>bottes</t>
+          <t>main_droite</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>linen_cloth ×3
-leather_strip ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>linen_main_droite_recipe</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Lame en lin</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>linen_main_droite</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>weapon</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>main_droite</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>linen_cloth ×3
 wood_log ×2
@@ -5408,36 +5371,36 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>linen_main_gauche_recipe</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Bouclier en lin</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>linen_main_gauche</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>shield</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>main_gauche</t>
         </is>
       </c>
-      <c r="F56" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>linen_cloth ×3
 wood_log ×3
@@ -5445,36 +5408,36 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>linen_collier_recipe</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>Collier en lin</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>linen_collier</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>necklace</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>collier</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="F56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
         <is>
           <t>linen_cloth ×4
 polished_stone ×1
@@ -5482,102 +5445,138 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>linen_bague_recipe</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Bague en lin</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>linen_bague</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ring</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>bague</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>linen_cloth ×2
+polished_stone ×1</t>
+        </is>
+      </c>
+    </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>linen_bague_recipe</t>
+          <t>linen_ceinture_recipe</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Bague en lin</t>
+          <t>Ceinture en lin</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>linen_bague</t>
+          <t>linen_ceinture</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>ring</t>
+          <t>belt</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>bague</t>
+          <t>ceinture</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>linen_cloth ×2
+iron_ingot ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>linen_boucle_oreille_recipe</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Boucle en lin</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>linen_boucle_oreille</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>earring</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>linen_cloth ×2
 polished_stone ×1</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>linen_ceinture_recipe</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Ceinture en lin</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>linen_ceinture</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>belt</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>ceinture</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>linen_cloth ×2
-iron_ingot ×1</t>
-        </is>
-      </c>
-    </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>linen_boucle_oreille_recipe</t>
+          <t>slime_casque_recipe</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Boucle en lin</t>
+          <t>Casque de slime</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>linen_boucle_oreille</t>
+          <t>slime_casque</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>earring</t>
+          <t>helmet</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>boucle_oreille</t>
+          <t>casque</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
@@ -5585,35 +5584,35 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>linen_cloth ×2
-polished_stone ×1</t>
+          <t>slime_gel ×4
+leather_strip ×1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>slime_casque_recipe</t>
+          <t>slime_plastron_recipe</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Casque de slime</t>
+          <t>Plastron de slime</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>slime_casque</t>
+          <t>slime_plastron</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>helmet</t>
+          <t>chest</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>casque</t>
+          <t>plastron</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -5621,35 +5620,35 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>slime_gel ×4
-leather_strip ×1</t>
+          <t>slime_gel ×5
+leather_strip ×2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>slime_plastron_recipe</t>
+          <t>slime_jambieres_recipe</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Plastron de slime</t>
+          <t>Jambières de slime</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>slime_plastron</t>
+          <t>slime_jambieres</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>chest</t>
+          <t>legs</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>plastron</t>
+          <t>jambieres</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
@@ -5657,7 +5656,7 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>slime_gel ×5
+          <t>slime_gel ×4
 leather_strip ×2</t>
         </is>
       </c>
@@ -5665,27 +5664,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>slime_jambieres_recipe</t>
+          <t>slime_bottes_recipe</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jambières de slime</t>
+          <t>Bottes de slime</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>slime_jambieres</t>
+          <t>slime_bottes</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>legs</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>jambieres</t>
+          <t>bottes</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -5693,35 +5692,35 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>slime_gel ×4
-leather_strip ×2</t>
+          <t>slime_gel ×3
+leather_strip ×1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>slime_bottes_recipe</t>
+          <t>slime_bracelet_recipe</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Bottes de slime</t>
+          <t>Bracelet de slime</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>slime_bottes</t>
+          <t>slime_bracelet</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>boots</t>
+          <t>bracelet</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>bottes</t>
+          <t>bracelet</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
@@ -5729,35 +5728,35 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>slime_gel ×3
-leather_strip ×1</t>
+          <t>slime_gel ×2
+iron_ingot ×1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>slime_bracelet_recipe</t>
+          <t>slime_bague_recipe</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bracelet de slime</t>
+          <t>Bague de slime</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>slime_bracelet</t>
+          <t>slime_bague</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>bracelet</t>
+          <t>ring</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>bracelet</t>
+          <t>bague</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -5766,148 +5765,112 @@
       <c r="G65" s="5" t="inlineStr">
         <is>
           <t>slime_gel ×2
-iron_ingot ×1</t>
+polished_stone ×1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>slime_bague_recipe</t>
+          <t>slime_ceinture_recipe</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Bague de slime</t>
+          <t>Ceinture de slime</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>slime_bague</t>
+          <t>slime_ceinture</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>ring</t>
+          <t>belt</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>bague</t>
+          <t>ceinture</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>slime_gel ×2
+leather_strip ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>slime_boucle_oreille_recipe</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Boucle de slime</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>slime_boucle_oreille</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>earring</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>slime_gel ×2
 polished_stone ×1</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>slime_ceinture_recipe</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Ceinture de slime</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>slime_ceinture</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>belt</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>ceinture</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>slime_gel ×2
-leather_strip ×1</t>
-        </is>
-      </c>
-    </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>slime_boucle_oreille_recipe</t>
+          <t>iron_sword_recipe</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Boucle de slime</t>
+          <t>Épée en fer</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>slime_boucle_oreille</t>
+          <t>iron_sword</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>earring</t>
+          <t>weapon</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>boucle_oreille</t>
+          <t>main_droite</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>slime_gel ×2
-polished_stone ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>iron_sword_recipe</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Épée en fer</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>iron_sword</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>weapon</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>main_droite</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>iron_ingot ×3
 wood_log ×1
@@ -5915,25 +5878,61 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>iron_warshield_recipe</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Pavois en fer</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>iron_warshield</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>iron_ingot ×4
+leather_strip ×2</t>
+        </is>
+      </c>
+    </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>iron_warshield_recipe</t>
+          <t>iron_greatsword_recipe</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Pavois en fer</t>
+          <t>Espadon en fer</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>iron_warshield</t>
+          <t>iron_greatsword</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>shield</t>
+          <t>weapon</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -5945,42 +5944,6 @@
         <v>1</v>
       </c>
       <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>iron_ingot ×4
-leather_strip ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>iron_greatsword_recipe</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Espadon en fer</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>iron_greatsword</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>weapon</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>main_droite</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>iron_ingot ×6
 wood_log ×3
@@ -5988,25 +5951,61 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>iron_tower_shield_recipe</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Tour en fer</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>iron_tower_shield</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>iron_ingot ×9
+leather_strip ×3</t>
+        </is>
+      </c>
+    </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>iron_tower_shield_recipe</t>
+          <t>slime_morningstar_recipe</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Tour en fer</t>
+          <t>Morningstar visqueuse</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>iron_tower_shield</t>
+          <t>slime_morningstar</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>shield</t>
+          <t>weapon</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -6019,30 +6018,30 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>iron_ingot ×9
-leather_strip ×3</t>
+          <t>slime_gel ×3
+wood_log ×2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>slime_morningstar_recipe</t>
+          <t>slime_buckler_recipe</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Morningstar visqueuse</t>
+          <t>Bouclier de gel</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>slime_morningstar</t>
+          <t>slime_buckler</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>weapon</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6054,42 +6053,6 @@
         <v>1</v>
       </c>
       <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>slime_gel ×3
-wood_log ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>slime_buckler_recipe</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>Bouclier de gel</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>slime_buckler</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>shield</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>main_droite</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>slime_gel ×3
 wood_log ×2
@@ -6097,36 +6060,36 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>slime_greatblade_recipe</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>Lame visqueuse colossale</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>slime_greatblade</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>weapon</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>main_droite</t>
         </is>
       </c>
-      <c r="F75" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="F74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>slime_gel ×9
 wood_log ×6
@@ -6134,36 +6097,36 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>slime_tower_shield_recipe</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>Tour de gel</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>slime_tower_shield</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>shield</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>main_droite</t>
         </is>
       </c>
-      <c r="F76" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>slime_gel ×12
 wood_log ×9
@@ -6171,36 +6134,36 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>gobelin_buckler_recipe</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>Rondache gobeline</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>gobelin_buckler</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>shield</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>main_droite</t>
         </is>
       </c>
-      <c r="F77" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="F76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
         <is>
           <t>gobelin_tooth ×3
 iron_ingot ×1
@@ -6208,36 +6171,36 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>gobelin_greataxe_recipe</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Grande hache gobeline</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>gobelin_greataxe</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>weapon</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>main_droite</t>
         </is>
       </c>
-      <c r="F78" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
         <is>
           <t>gobelin_tooth ×12
 iron_ingot ×6
@@ -6245,36 +6208,36 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>gobelin_warshield_recipe</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>Pavois gobelin</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>gobelin_warshield</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>shield</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>main_droite</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
+      <c r="F78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
         <is>
           <t>gobelin_tooth ×9
 iron_ingot ×3
@@ -6283,36 +6246,36 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>leather_dagger_recipe</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Dague en cuir</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>leather_dagger</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>weapon</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>main_droite</t>
         </is>
       </c>
-      <c r="F80" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
         <is>
           <t>leather_strip ×2
 wood_log ×2
@@ -6320,36 +6283,36 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>leather_buckler_recipe</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>Rondache en cuir</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>leather_buckler</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>shield</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E80" s="3" t="inlineStr">
         <is>
           <t>main_droite</t>
         </is>
       </c>
-      <c r="F81" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="F80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
         <is>
           <t>leather_strip ×2
 wood_log ×2
@@ -6357,36 +6320,36 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>leather_greatsword_recipe</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>Grande lame en cuir</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>leather_greatsword</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>weapon</t>
         </is>
       </c>
-      <c r="E82" s="3" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>main_droite</t>
         </is>
       </c>
-      <c r="F82" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
         <is>
           <t>leather_strip ×9
 wood_log ×6
@@ -6394,36 +6357,36 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>leather_tower_shield_recipe</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>Tour en cuir</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>leather_tower_shield</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>shield</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr">
         <is>
           <t>main_droite</t>
         </is>
       </c>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="F82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t>leather_strip ×9
 wood_log ×9
@@ -6431,36 +6394,36 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>linen_rapier_recipe</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>Rapière en lin</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>linen_rapier</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>weapon</t>
         </is>
       </c>
-      <c r="E84" s="3" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>main_droite</t>
         </is>
       </c>
-      <c r="F84" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="4" t="inlineStr">
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
         <is>
           <t>linen_cloth ×2
 wood_log ×2
@@ -6468,36 +6431,36 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>linen_aegis_recipe</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>Égide en lin</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>linen_aegis</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>shield</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E84" s="3" t="inlineStr">
         <is>
           <t>main_droite</t>
         </is>
       </c>
-      <c r="F85" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="F84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t>linen_cloth ×2
 wood_log ×2
@@ -6505,36 +6468,36 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>linen_greatblade_recipe</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Grande lame en lin</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>linen_greatblade</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>weapon</t>
         </is>
       </c>
-      <c r="E86" s="3" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>main_droite</t>
         </is>
       </c>
-      <c r="F86" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" s="4" t="inlineStr">
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
         <is>
           <t>linen_cloth ×9
 wood_log ×6
@@ -6542,36 +6505,36 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>linen_tower_shield_recipe</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>Tour en lin</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>linen_tower_shield</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>shield</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>main_droite</t>
         </is>
       </c>
-      <c r="F87" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="F86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
         <is>
           <t>linen_cloth ×9
 wood_log ×9
@@ -10361,10 +10324,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -10715,17 +10678,17 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>two_handed_iron_sword</t>
+          <t>iron_dagger</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Espadon de fer</t>
+          <t>Dague en fer</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -10735,11 +10698,11 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -10748,46 +10711,46 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>Une longue lame qui demande de tenir des deux mains.</t>
+          <t>Dague affûtée, légère et discrète.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>iron_dagger</t>
+          <t>goblin_blade</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dague en fer</t>
+          <t>Lame gobeline</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -10801,7 +10764,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -10810,46 +10773,46 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dague affûtée, légère et discrète.</t>
+          <t>Lame ébréchée mais redoutable, taillée d'os de gobelin.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>goblin_blade</t>
+          <t>leather_main_droite</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Lame gobeline</t>
+          <t>Lame en cuir</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -10863,10 +10826,10 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0</v>
@@ -10875,10 +10838,10 @@
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>0</v>
@@ -10887,26 +10850,26 @@
         <v>0</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Lame ébréchée mais redoutable, taillée d'os de gobelin.</t>
+          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>leather_main_droite</t>
+          <t>linen_main_droite</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lame en cuir</t>
+          <t>Lame en lin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10928,7 +10891,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -10937,7 +10900,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -10956,19 +10919,19 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>linen_main_droite</t>
+          <t>iron_sword</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Lame en lin</t>
+          <t>Épée en fer</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -10987,22 +10950,22 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>0</v>
@@ -11011,31 +10974,31 @@
         <v>0</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+          <t>Variante équilibrée de la dague en fer — atk + un peu de def/PV.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iron_sword</t>
+          <t>iron_greatsword</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Épée en fer</t>
+          <t>Espadon en fer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -11045,59 +11008,59 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Variante équilibrée de la dague en fer — atk + un peu de def/PV.</t>
+          <t>Lame à 2 mains — frappe lourde mais on s'expose en attaquant.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>iron_greatsword</t>
+          <t>slime_morningstar</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Espadon en fer</t>
+          <t>Morningstar visqueuse</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -11107,59 +11070,59 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>Lame à 2 mains — frappe lourde mais on s'expose en attaquant.</t>
+          <t>Variante régen de la lame visqueuse — atk soutenue + un peu de régen.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>slime_morningstar</t>
+          <t>slime_greatblade</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Morningstar visqueuse</t>
+          <t>Lame visqueuse colossale</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -11169,17 +11132,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -11194,29 +11157,29 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Variante régen de la lame visqueuse — atk soutenue + un peu de régen.</t>
+          <t>2 mains — frappe massive, on perd en résilience.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>slime_greatblade</t>
+          <t>gobelin_greataxe</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Lame visqueuse colossale</t>
+          <t>Grande hache gobeline</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11235,20 +11198,20 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J14" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" s="3" t="n">
         <v>0</v>
       </c>
@@ -11259,31 +11222,31 @@
         <v>0</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>2 mains — frappe massive, on perd en résilience.</t>
+          <t>2 mains — crit massifs, on se découvre complètement.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gobelin_greataxe</t>
+          <t>leather_dagger</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Grande hache gobeline</t>
+          <t>Dague en cuir</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11293,26 +11256,26 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -11321,31 +11284,31 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2 mains — crit massifs, on se découvre complètement.</t>
+          <t>Variante offensive de la lame en cuir — un peu d'attaque en plus.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>leather_dagger</t>
+          <t>leather_greatsword</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Dague en cuir</t>
+          <t>Grande lame en cuir</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -11355,27 +11318,27 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="L16" s="3" t="n">
         <v>0</v>
       </c>
@@ -11383,31 +11346,31 @@
         <v>0</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>Variante offensive de la lame en cuir — un peu d'attaque en plus.</t>
+          <t>2 mains — atk solide pour la panoplie cuir, on perd en couverture.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>leather_greatsword</t>
+          <t>linen_rapier</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Grande lame en cuir</t>
+          <t>Rapière en lin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11417,59 +11380,59 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2 mains — atk solide pour la panoplie cuir, on perd en couverture.</t>
+          <t>Variante speed/crit de la lame en lin — précise mais fragile.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>linen_rapier</t>
+          <t>linen_greatblade</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Rapière en lin</t>
+          <t>Grande lame en lin</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -11479,102 +11442,40 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t>Variante speed/crit de la lame en lin — précise mais fragile.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>linen_greatblade</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Grande lame en lin</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>main_droite</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-3</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>6</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>55</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>2 mains — crit dmg massif mais peu de couverture.</t>
         </is>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Généré le 2026-05-07 19:19 UTC</t>
+          <t>Généré le 2026-05-07 19:24 UTC</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>main_gauche</t>
+          <t>main_droite</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>main_gauche</t>
+          <t>main_droite</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>main_gauche</t>
+          <t>main_droite</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>main_gauche</t>
+          <t>main_droite</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>main_gauche</t>
+          <t>main_droite</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>main_gauche</t>
+          <t>main_droite</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>main_gauche</t>
+          <t>main_droite</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -11675,7 +11675,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>main_gauche</t>
+          <t>main_droite</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -11737,7 +11737,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>main_gauche</t>
+          <t>main_droite</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>main_gauche</t>
+          <t>main_droite</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>main_gauche</t>
+          <t>main_droite</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>main_gauche</t>
+          <t>main_droite</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Généré le 2026-05-07 19:24 UTC</t>
+          <t>Généré le 2026-05-14 10:33 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Généré le 2026-05-14 10:33 UTC</t>
+          <t>Généré le 2026-05-15 17:21 UTC</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>goblin_amulet_recipe</t>
+          <t>gobelin_amulet_recipe</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>goblin_amulet</t>
+          <t>gobelin_amulet</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>goblin_blade_recipe</t>
+          <t>gobelin_blade_recipe</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>goblin_blade</t>
+          <t>gobelin_blade</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -10740,7 +10740,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>goblin_blade</t>
+          <t>gobelin_blade</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -14462,7 +14462,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>goblin_amulet</t>
+          <t>gobelin_amulet</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Généré le 2026-05-15 17:21 UTC</t>
+          <t>Généré le 2026-05-16 10:51 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Généré le 2026-05-16 10:51 UTC</t>
+          <t>Généré le 2026-05-25 19:37 UTC</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
     <col width="24" customWidth="1" min="18" max="18"/>
     <col width="36" customWidth="1" min="19" max="19"/>
   </cols>
@@ -7326,22 +7326,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>100</v>
+        <v>158</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J2" s="3" t="n">
         <v>0</v>
@@ -7350,27 +7350,23 @@
         <v>0</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>60</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
           <t>F-</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>slime_gel ×1-2 (75%)</t>
-        </is>
-      </c>
+      <c r="Q2" s="3" t="inlineStr"/>
       <c r="R2" s="3" t="inlineStr">
         <is>
           <t>slime.png</t>
@@ -7399,51 +7395,47 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>500</v>
+        <v>238</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N3" t="n">
         <v>40</v>
       </c>
       <c r="O3" t="n">
-        <v>100</v>
+        <v>219</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>F-</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>gobelin_tooth ×1-2 (75%)</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>gobelin.png</t>
@@ -7472,51 +7464,47 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>600</v>
+        <v>317</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>30</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>507</v>
+        <v>353</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>F+</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>gobelin_tooth ×1-2 (75%)</t>
-        </is>
-      </c>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
       <c r="R4" s="3" t="inlineStr">
         <is>
           <t>gobelin_combattant.png</t>
@@ -7545,51 +7533,47 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>700</v>
+        <v>381</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="M5" t="n">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="N5" t="n">
         <v>30</v>
       </c>
       <c r="O5" t="n">
-        <v>500</v>
+        <v>741</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>F+</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>gobelin_tooth ×1-2 (75%)</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>gobelin_chaman.png</t>
@@ -7604,12 +7588,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>gobelin_geant</t>
+          <t>gobelin_assassin</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Gobelin Géant</t>
+          <t>Gobelin Assassin</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -7618,19 +7602,19 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1100</v>
+        <v>286</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>150</v>
@@ -7642,47 +7626,43 @@
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>25</v>
+        <v>144</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>1008</v>
+        <v>548</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>E-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>gobelin_tooth ×1-2 (75%)</t>
-        </is>
-      </c>
+          <t>F+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>gobelin_geant.png</t>
+          <t>gobelin_assassin.png</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>Une créature imposante.</t>
+          <t>Une créature discrète.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gobelin_runique</t>
+          <t>gobelin_ballon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gobelin Runique</t>
+          <t>Gobelin Ballon</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7691,71 +7671,67 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>600</v>
+        <v>557</v>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="F7" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="M7" t="n">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="N7" t="n">
         <v>20</v>
       </c>
       <c r="O7" t="n">
-        <v>1001</v>
+        <v>1018</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>E-</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>gobelin_tooth ×1-2 (75%)</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>gobelin_runique.png</t>
+          <t>gobelin_ballon.png</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Une créature mystérieuse.</t>
+          <t>Un groupe de créatures inventives.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>gobelin_ballon</t>
+          <t>gobelin_geant</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Gobelin Ballon</t>
+          <t>Gobelin Géant</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -7764,71 +7740,67 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>800</v>
+        <v>955</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>25</v>
+        <v>206</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>20</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>1004</v>
+        <v>1221</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>E-</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>gobelin_tooth ×1-2 (75%)</t>
-        </is>
-      </c>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>gobelin_ballon.png</t>
+          <t>gobelin_geant.png</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>Un groupe de créatures inventives.</t>
+          <t>Une créature imposante.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gobelin_assassin</t>
+          <t>gobelin_runique</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gobelin Assassin</t>
+          <t>Gobelin Runique</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7837,59 +7809,55 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>225</v>
+        <v>573</v>
       </c>
       <c r="E9" t="n">
+        <v>68</v>
+      </c>
+      <c r="F9" t="n">
+        <v>15</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>100</v>
       </c>
-      <c r="F9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" t="n">
-        <v>75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>75</v>
-      </c>
-      <c r="I9" t="n">
-        <v>250</v>
-      </c>
       <c r="J9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>30</v>
+        <v>238</v>
       </c>
       <c r="M9" t="n">
-        <v>30</v>
+        <v>114</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O9" t="n">
-        <v>2005</v>
+        <v>1611</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>gobelin_tooth ×1-2 (75%)</t>
-        </is>
-      </c>
+          <t>E+</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>gobelin_assassin.png</t>
+          <t>gobelin_runique.png</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Une créature discrète.</t>
+          <t>Une créature mystérieuse.</t>
         </is>
       </c>
     </row>
@@ -7910,51 +7878,47 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>900</v>
+        <v>876</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>30</v>
+        <v>144</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>10</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>2012</v>
+        <v>2442</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>gobelin_tooth ×1-2 (75%)</t>
-        </is>
-      </c>
+          <t>D-</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
       <c r="R10" s="3" t="inlineStr">
         <is>
           <t>gobelin_superieur.png</t>
@@ -7977,15 +7941,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="39" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
@@ -8079,19 +8043,19 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Le commencement de votre voyage. Toutes les voies partent d'ici.</t>
+          <t>Le commencement de votre voyage. Les trois voies partent d'ici.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>combat_root</t>
+          <t>voie_atq</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Voie du Combat</t>
+          <t>Voie de l'Attaque</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -8114,7 +8078,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-800, 220</t>
+          <t>0, -140</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -8124,604 +8088,604 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Discipline du combat rapproché : porter des coups, encaisser, frapper plus vite.</t>
+          <t>Entrée de la voie de l'attaque.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>force_brute</t>
+          <t>atq_1</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Force Brute</t>
+          <t>Force 1</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1,2,3,4,5</t>
+          <t>1,1,1</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>atk_percent → [1,3,6,10,15]</t>
+          <t>atk_flat → [5,10,15]</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>combat_root</t>
+          <t>voie_atq</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-1000, 440</t>
+          <t>0, -218</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>💪</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Augmente votre attaque (multiplicatif). +1/3/6/10/15%.</t>
+          <t>+5 par niveau (cumulatif, max 3).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>armes_aiguisees</t>
+          <t>atq_2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Armes Aiguisées</t>
+          <t>Force 1</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1,1,2,3,4</t>
+          <t>1,1,1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>crit_chance_flat → [1,2,3,4,5]</t>
+          <t>atk_flat → [5,10,15]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>combat_root</t>
+          <t>atq_1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-600, 440</t>
+          <t>0, -296</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>🗡️</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Augmente votre chance de coup critique. +1/2/3/4/5%.</t>
+          <t>+5 par niveau (cumulatif, max 3).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>coups_critiques</t>
+          <t>atq_3</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Coups Critiques</t>
+          <t>Force 1</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>1,2,2,3,4</t>
+          <t>1,1,1</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>crit_damage_flat → [5,10,15,20,25]</t>
+          <t>atk_flat → [5,10,15]</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>armes_aiguisees</t>
+          <t>atq_2</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-1000, 660</t>
+          <t>0, -374</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>💥</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Augmente les dégâts de vos coups critiques. +5/10/15/20/25%.</t>
+          <t>+5 par niveau (cumulatif, max 3).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>frappe_eclair</t>
+          <t>atq_4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Frappe Éclair</t>
+          <t>Force 1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1,2,3,4,5</t>
+          <t>1,1,1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>speed_flat → [1,2,3,4,5]</t>
+          <t>atk_flat → [5,10,15]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>force_brute</t>
+          <t>atq_3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-600, 660</t>
+          <t>0, -452</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Augmente votre vitesse de combat. +1/2/3/4/5.</t>
+          <t>+5 par niveau (cumulatif, max 3).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>survie_root</t>
+          <t>atq_5</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Voie de la Survie</t>
+          <t>Force 1</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,1,1</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>atk_flat → [5,10,15]</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>aventurier</t>
+          <t>atq_4</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>0, 220</t>
+          <t>0, -530</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>🛡️</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Endurance et résistance : tenir là où d'autres tombent.</t>
+          <t>+5 par niveau (cumulatif, max 3).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>vitalite</t>
+          <t>atq_6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vitalité</t>
+          <t>Frappe affûtée</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1,2,3,4,5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>hp_max_percent → [2,5,10,17,25]</t>
+          <t>atk_percent → [1]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>survie_root</t>
+          <t>atq_5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-200, 440</t>
+          <t>0, -608</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>❤️</t>
+          <t>💥</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Augmente vos points de vie maximum (multiplicatif). +2/5/10/17/25%.</t>
+          <t>Nœud spécial : +1 atk percent (1 amélioration).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>peau_de_pierre</t>
+          <t>atq_7</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Peau de Pierre</t>
+          <t>Force 2</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1,2,3,4,5</t>
+          <t>1,1,1</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>def_percent → [1,3,6,10,15]</t>
+          <t>atk_flat → [6,12,18]</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>survie_root</t>
+          <t>atq_6</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>200, 440</t>
+          <t>0, -686</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>🪨</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Augmente votre défense (multiplicatif). +1/3/6/10/15%.</t>
+          <t>+6 par niveau (cumulatif, max 3).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>instinct_evasion</t>
+          <t>atq_8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Instinct d'Évasion</t>
+          <t>Force 2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1,1,2,3,4</t>
+          <t>1,1,1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>dodge_flat → [1,2,3,4,5]</t>
+          <t>atk_flat → [6,12,18]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>vitalite</t>
+          <t>atq_7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-200, 660</t>
+          <t>0, -764</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>🌀</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Augmente votre chance d'esquiver une attaque. +1/2/3/4/5%.</t>
+          <t>+6 par niveau (cumulatif, max 3).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>regeneration_rapide</t>
+          <t>atq_9</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Régénération Rapide</t>
+          <t>Force 2</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1,2,2,3,4</t>
+          <t>1,1,1</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>hp_regeneration_flat → [1,2,4,6,9]</t>
+          <t>atk_flat → [6,12,18]</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>peau_de_pierre</t>
+          <t>atq_8</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>200, 660</t>
+          <t>0, -842</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>💚</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Augmente la régénération de PV. +1/2/4/6/9 PV/min.</t>
+          <t>+6 par niveau (cumulatif, max 3).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>chasseur_root</t>
+          <t>atq_10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Voie du Chasseur</t>
+          <t>Force 2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,1,1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>atk_flat → [6,12,18]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>aventurier</t>
+          <t>atq_9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>800, 220</t>
+          <t>0, -920</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>🏹</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Trouver plus, gagner plus : optimisation des récoltes de combat.</t>
+          <t>+6 par niveau (cumulatif, max 3).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>traqueur_aguerri</t>
+          <t>atq_11</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Traqueur Aguerri</t>
+          <t>Force 2</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>1,2,3,4,5</t>
+          <t>1,1,1</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>xp_drop_percent → [2,5,10,17,25]</t>
+          <t>atk_flat → [6,12,18]</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>chasseur_root</t>
+          <t>atq_10</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>600, 440</t>
+          <t>0, -998</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>🎯</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Augmente l'XP gagnée sur les monstres. +2/5/10/17/25%.</t>
+          <t>+6 par niveau (cumulatif, max 3).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bourse_remplie</t>
+          <t>atq_12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bourse Remplie</t>
+          <t>Œil vif</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1,2,3,4,5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>gold_drop_percent → [2,5,10,17,25]</t>
+          <t>crit_chance_flat → [1]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>chasseur_root</t>
+          <t>atq_11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1000, 440</t>
+          <t>0, -1076</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>💰</t>
+          <t>🎯</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Augmente l'or gagné sur les monstres. +2/5/10/17/25%.</t>
+          <t>Nœud spécial : +1 crit chance flat (1 amélioration).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>chance_pillarde</t>
+          <t>atq_13</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Chance Pillarde</t>
+          <t>Force 3</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>1,2,3,4,5</t>
+          <t>1,1,1</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>drop_rate_multiplier → [1,2,3,4,5]</t>
+          <t>atk_flat → [7,14,21]</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>chasseur_root</t>
+          <t>atq_12</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1000, 660</t>
+          <t>0, -1154</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>🍀</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Augmente vos chances de drop d'objets (multiplicatif sur le taux de base). +1/2/3/4/5%.</t>
+          <t>+7 par niveau (cumulatif, max 3).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>oeil_du_lynx</t>
+          <t>atq_14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Œil du Lynx</t>
+          <t>Force 3</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -8729,44 +8693,44 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2,3,4</t>
+          <t>1,1,1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>crit_chance_flat → [2,4,6]</t>
+          <t>atk_flat → [7,14,21]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>traqueur_aguerri</t>
+          <t>atq_13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>600, 660</t>
+          <t>0, -1232</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>👁️</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Augmente votre chance de coup critique. +2/4/6%.</t>
+          <t>+7 par niveau (cumulatif, max 3).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>chasseur_silencieux</t>
+          <t>atq_15</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Chasseur Silencieux</t>
+          <t>Force 3</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -8774,44 +8738,44 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>2,3,4</t>
+          <t>1,1,1</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>speed_flat → [1,2,4]</t>
+          <t>atk_flat → [7,14,21]</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>bourse_remplie</t>
+          <t>atq_14</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>900, 770</t>
+          <t>0, -1310</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>🐾</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Augmente la vitesse en combat. +1/2/4.</t>
+          <t>+7 par niveau (cumulatif, max 3).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>maitrise_combat</t>
+          <t>atq_16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Maîtrise du Combat</t>
+          <t>Force 3</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -8819,45 +8783,44 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3,5,7</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>atk_percent → [3,8,15]
-def_percent → [3,8,15]</t>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>atk_flat → [7,14,21]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>coups_critiques, frappe_eclair</t>
+          <t>atq_15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-800, 880</t>
+          <t>0, -1388</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>🛡️⚔️</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Bonus combiné offensif et défensif. +3/8/15% atk et def.</t>
+          <t>+7 par niveau (cumulatif, max 3).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>endurance_legendaire</t>
+          <t>atq_17</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Endurance Légendaire</t>
+          <t>Force 3</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -8865,80 +8828,5837 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>3,5,7</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>hp_max_percent → [5,12,20]
-hp_regeneration_flat → [2,5,10]</t>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>atk_flat → [7,14,21]</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>instinct_evasion, regeneration_rapide</t>
+          <t>atq_16</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>0, 880</t>
+          <t>0, -1466</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>🌳</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>PV et régénération massifs. +5/12/20% HP, +2/5/10 régen.</t>
+          <t>+7 par niveau (cumulatif, max 3).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fortune_du_chasseur</t>
+          <t>atq_18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fortune du Chasseur</t>
+          <t>Célérité</t>
         </is>
       </c>
       <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>speed_flat → [1]</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>atq_17</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0, -1544</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>💨</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +1 speed flat (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>atq_19</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Force 4</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>3,5,7</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>xp_drop_percent → [3,8,15]
-gold_drop_percent → [3,8,15]
-drop_rate_multiplier → [1,3,5]</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>oeil_du_lynx, chasseur_silencieux</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>800, 880</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>atk_flat → [8,16,24]</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>atq_18</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>0, -1622</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>+8 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>atq_20</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Force 4</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>atk_flat → [8,16,24]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>atq_19</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0, -1700</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>+8 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>atq_21</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Force 4</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>atk_flat → [8,16,24]</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>atq_20</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>0, -1778</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>+8 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>atq_22</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Force 4</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>atk_flat → [8,16,24]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>atq_21</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0, -1856</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>+8 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>atq_23</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Force 4</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>atk_flat → [8,16,24]</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>atq_22</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>0, -1934</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>+8 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>atq_24</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Coup dévastateur</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → [5]</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>atq_23</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0, -2012</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +5 crit damage flat (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>atq_25</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Force 5</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>atk_flat → [9,18,27]</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>atq_24</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>0, -2090</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>+9 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>atq_26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Force 5</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>atk_flat → [9,18,27]</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>atq_25</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0, -2168</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>+9 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>atq_27</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Force 5</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>atk_flat → [9,18,27]</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>atq_26</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>0, -2246</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>+9 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>atq_28</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Force 5</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>atk_flat → [9,18,27]</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>atq_27</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0, -2324</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>+9 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>atq_29</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Force 5</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>atk_flat → [9,18,27]</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>atq_28</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>0, -2402</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>+9 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>atq_30</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Frappe affûtée</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>atk_percent → [1]</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>atq_29</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0, -2480</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>💥</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +1 atk percent (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>atq_31</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Force 6</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>atk_flat → [10,20,30]</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>atq_30</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>0, -2558</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>+10 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>atq_32</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Force 6</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>atk_flat → [10,20,30]</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>atq_31</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0, -2636</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>+10 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>atq_33</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Force 6</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>atk_flat → [10,20,30]</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>atq_32</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>0, -2714</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>+10 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>atq_34</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Force 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>atk_flat → [10,20,30]</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>atq_33</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0, -2792</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>+10 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>atq_35</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Force 6</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>atk_flat → [10,20,30]</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>atq_34</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>0, -2870</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>+10 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>atq_36</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Œil vif</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>crit_chance_flat → [1]</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>atq_35</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0, -2948</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>🎯</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +1 crit chance flat (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>atq_37</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Force 7</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>atk_flat → [11,22,33]</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>atq_36</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>0, -3026</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>+11 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>atq_38</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Force 7</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>atk_flat → [11,22,33]</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>atq_37</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0, -3104</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>+11 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>atq_39</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Force 7</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>atk_flat → [11,22,33]</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>atq_38</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>0, -3182</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>+11 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>atq_40</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Force 7</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>atk_flat → [11,22,33]</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>atq_39</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0, -3260</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>+11 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>atq_41</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Force 7</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>atk_flat → [11,22,33]</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>atq_40</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>0, -3338</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>+11 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>atq_42</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Célérité</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>speed_flat → [1]</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>atq_41</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0, -3416</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>💨</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +1 speed flat (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>atq_43</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Force 8</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>atk_flat → [12,24,36]</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>atq_42</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>0, -3494</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>+12 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>atq_44</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Force 8</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>atk_flat → [12,24,36]</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>atq_43</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0, -3572</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>+12 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>atq_45</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Force 8</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>atk_flat → [12,24,36]</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>atq_44</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>0, -3650</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>+12 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>atq_46</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Force 8</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>atk_flat → [12,24,36]</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>atq_45</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0, -3728</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>+12 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>atq_47</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Force 8</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>atk_flat → [12,24,36]</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>atq_46</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>0, -3806</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>+12 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>atq_48</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Coup dévastateur</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → [5]</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>atq_47</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0, -3884</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +5 crit damage flat (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>voie_def</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Voie de la Défense</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>aventurier</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>121, 70</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>Entrée de la voie de la défense.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>def_1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Armure 1</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>def_flat → [5,10,15]</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>voie_def</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>189, 109</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>+5 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>def_2</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Vitalité 1</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [100,200,300]</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>def_1</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>256, 148</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>+100 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>def_3</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Armure 1</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>def_flat → [5,10,15]</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>def_2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>324, 187</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>+5 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>def_4</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Vitalité 1</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [100,200,300]</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>def_3</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>391, 226</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>+100 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>def_5</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Armure 1</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>def_flat → [5,10,15]</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>def_4</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>459, 265</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>+5 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>def_6</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Peau de pierre</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>def_percent → [1]</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>def_5</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>527, 304</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>🪨</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +1 def percent (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>def_7</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Vitalité 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [120,240,360]</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>def_6</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>594, 343</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>+120 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>def_8</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Armure 2</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>def_flat → [6,12,18]</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>def_7</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>662, 382</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>+6 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>def_9</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Vitalité 2</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [120,240,360]</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>def_8</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>729, 421</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>+120 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>def_10</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Armure 2</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>def_flat → [6,12,18]</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>def_9</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>797, 460</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>+6 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>def_11</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Vitalité 2</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [120,240,360]</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>def_10</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>864, 499</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>+120 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>def_12</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Endurance</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>hp_max_percent → [1]</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>def_11</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>932, 538</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>💗</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +1 hp max percent (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>def_13</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Armure 3</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>3</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>def_flat → [7,14,21]</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>def_12</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>999, 577</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>+7 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>def_14</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Vitalité 3</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [140,280,420]</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>def_13</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>1067, 616</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>+140 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>def_15</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Armure 3</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>def_flat → [7,14,21]</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>def_14</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1134, 655</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>+7 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>def_16</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Vitalité 3</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [140,280,420]</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>def_15</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>1202, 694</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>+140 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>def_17</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Armure 3</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>3</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>def_flat → [7,14,21]</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>def_16</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1270, 733</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>+7 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>def_18</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Esquive</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>dodge_flat → [1]</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>def_17</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>1337, 772</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>🌀</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +1 dodge flat (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>def_19</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Vitalité 4</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>3</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [160,320,480]</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>def_18</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1405, 811</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>+160 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>def_20</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Armure 4</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>def_flat → [8,16,24]</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>def_19</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>1472, 850</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>+8 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>def_21</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Vitalité 4</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>3</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [160,320,480]</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>def_20</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1540, 889</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>+160 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>def_22</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Armure 4</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>def_flat → [8,16,24]</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>def_21</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>1607, 928</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>+8 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>def_23</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Vitalité 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [160,320,480]</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>def_22</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1675, 967</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>+160 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>def_24</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Régénération</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>hp_regeneration_flat → [1]</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>def_23</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>1742, 1006</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>💚</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +1 hp regeneration flat (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>def_25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Armure 5</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>3</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>def_flat → [9,18,27]</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>def_24</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1810, 1045</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>+9 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>def_26</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Vitalité 5</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [180,360,540]</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>def_25</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>1878, 1084</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>+180 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>def_27</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Armure 5</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>3</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>def_flat → [9,18,27]</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>def_26</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1945, 1123</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>+9 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>def_28</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Vitalité 5</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [180,360,540]</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>def_27</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>2013, 1162</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>+180 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>def_29</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Armure 5</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>3</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>def_flat → [9,18,27]</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>def_28</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2080, 1201</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>+9 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>def_30</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Peau de pierre</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>def_percent → [1]</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>def_29</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>2148, 1240</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>🪨</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +1 def percent (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>def_31</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Vitalité 6</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>3</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [200,400,600]</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>def_30</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2215, 1279</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>+200 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>def_32</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Armure 6</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>def_flat → [10,20,30]</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>def_31</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>2283, 1318</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>+10 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>def_33</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Vitalité 6</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [200,400,600]</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>def_32</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2350, 1357</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>+200 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>def_34</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Armure 6</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>def_flat → [10,20,30]</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>def_33</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>2418, 1396</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>+10 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>def_35</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Vitalité 6</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [200,400,600]</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>def_34</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2485, 1435</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>+200 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>def_36</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Endurance</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>hp_max_percent → [1]</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>def_35</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>2553, 1474</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>💗</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +1 hp max percent (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>def_37</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Armure 7</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>3</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>def_flat → [11,22,33]</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>def_36</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2621, 1513</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>+11 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>def_38</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Vitalité 7</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [220,440,660]</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>def_37</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>2688, 1552</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>+220 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>def_39</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Armure 7</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>3</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>def_flat → [11,22,33]</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>def_38</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2756, 1591</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>+11 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>def_40</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Vitalité 7</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [220,440,660]</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>def_39</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>2823, 1630</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>+220 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>def_41</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Armure 7</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>def_flat → [11,22,33]</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>def_40</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2891, 1669</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>+11 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>def_42</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Esquive</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>dodge_flat → [1]</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>def_41</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>2958, 1708</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>🌀</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +1 dodge flat (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>def_43</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Vitalité 8</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>3</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [240,480,720]</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>def_42</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>3026, 1747</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>+240 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>def_44</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Armure 8</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>def_flat → [12,24,36]</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>def_43</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>3093, 1786</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>+12 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>def_45</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Vitalité 8</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [240,480,720]</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>def_44</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>3161, 1825</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>+240 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>def_46</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Armure 8</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>def_flat → [12,24,36]</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>def_45</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>3229, 1864</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>+12 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>def_47</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Vitalité 8</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>3</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>hp_max_flat → [240,480,720]</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>def_46</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>3296, 1903</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>+240 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>def_48</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Régénération</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>hp_regeneration_flat → [1]</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>def_47</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>3364, 1942</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>💚</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +1 hp regeneration flat (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>voie_uti</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Voie Utilitaire</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>aventurier</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-121, 70</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>🎒</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Entrée de la voie utilitaire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>uti_1</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Chance 1</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>voie_uti</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>-189, 109</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>uti_2</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Bourse 1</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>uti_1</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-256, 148</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>uti_3</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Sagesse 1</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>uti_2</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>-324, 187</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
         <is>
           <t>✨</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>XP, or et drops cumulés. +3/8/15% sur chaque.</t>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>uti_4</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Chance 1</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>3</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>uti_3</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-391, 226</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>uti_5</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>Bourse 1</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>uti_4</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>-459, 265</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>uti_6</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Fortune</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [2]</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>uti_5</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-527, 304</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +2 gold drop percent (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>uti_7</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>Sagesse 2</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>uti_6</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>-594, 343</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>uti_8</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Chance 2</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>uti_7</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-662, 382</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>uti_9</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>Bourse 2</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>uti_8</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>-729, 421</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>uti_10</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Sagesse 2</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>3</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>uti_9</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-797, 460</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>uti_11</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>Chance 2</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>uti_10</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>-864, 499</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>uti_12</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Érudition</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [2]</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>uti_11</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-932, 538</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +2 xp drop percent (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>uti_13</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>Bourse 3</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>uti_12</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>-999, 577</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>uti_14</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Sagesse 3</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>3</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>uti_13</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-1067, 616</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>uti_15</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>Chance 3</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>uti_14</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>-1134, 655</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>uti_16</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Bourse 3</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>3</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>uti_15</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-1202, 694</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>uti_17</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>Sagesse 3</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>uti_16</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>-1270, 733</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>uti_18</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Pillage</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [2]</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>uti_17</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-1337, 772</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +2 drop rate multiplier (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>uti_19</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>Chance 4</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>uti_18</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>-1405, 811</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>uti_20</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Bourse 4</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>3</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>uti_19</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-1472, 850</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>uti_21</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Sagesse 4</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>uti_20</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>-1540, 889</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>uti_22</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Chance 4</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>3</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>uti_21</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-1607, 928</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>uti_23</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>Bourse 4</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>uti_22</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>-1675, 967</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>uti_24</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Fortune</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [2]</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>uti_23</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-1742, 1006</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +2 gold drop percent (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>uti_25</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>Sagesse 5</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>uti_24</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>-1810, 1045</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>uti_26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Chance 5</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>3</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>uti_25</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-1878, 1084</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>uti_27</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>Bourse 5</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>uti_26</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>-1945, 1123</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>uti_28</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Sagesse 5</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>3</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>uti_27</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-2013, 1162</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>uti_29</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Chance 5</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>uti_28</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>-2080, 1201</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>uti_30</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Érudition</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [2]</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>uti_29</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-2148, 1240</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +2 xp drop percent (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>uti_31</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>Bourse 6</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>uti_30</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>-2215, 1279</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>uti_32</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Sagesse 6</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>3</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>uti_31</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-2283, 1318</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>uti_33</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>Chance 6</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>uti_32</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>-2350, 1357</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>uti_34</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Bourse 6</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>3</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>uti_33</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-2418, 1396</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>uti_35</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>Sagesse 6</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>uti_34</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>-2485, 1435</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>uti_36</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Pillage</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [2]</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>uti_35</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-2553, 1474</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +2 drop rate multiplier (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>uti_37</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>Chance 7</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>uti_36</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>-2621, 1513</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>uti_38</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Bourse 7</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>3</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>uti_37</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-2688, 1552</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>uti_39</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>Sagesse 7</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>uti_38</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>-2756, 1591</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>uti_40</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Chance 7</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>3</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>uti_39</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-2823, 1630</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>uti_41</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>Bourse 7</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>uti_40</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>-2891, 1669</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>uti_42</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Fortune</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [2]</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>uti_41</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-2958, 1708</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +2 gold drop percent (1 amélioration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>uti_43</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>Sagesse 8</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>uti_42</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>-3026, 1747</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>uti_44</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Chance 8</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>3</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>uti_43</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-3093, 1786</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>uti_45</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>Bourse 8</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>uti_44</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>-3161, 1825</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>uti_46</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Sagesse 8</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>3</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>uti_45</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-3229, 1864</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>uti_47</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>Chance 8</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [1,2,3]</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>uti_46</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>-3296, 1903</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>+1 par niveau (cumulatif, max 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>uti_48</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Érudition</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [2]</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>uti_47</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-3364, 1942</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Nœud spécial : +2 xp drop percent (1 amélioration).</t>
         </is>
       </c>
     </row>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Généré le 2026-05-25 19:37 UTC</t>
+          <t>Généré le 2026-05-25 19:53 UTC</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -6781,30 +6781,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>slime_gel</t>
+          <t>potion_soin_i</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gelée de Slime</t>
+          <t>Potion de soin I</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>resource</t>
+          <t>consumable</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -6815,30 +6815,30 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>gobelin_tooth</t>
+          <t>potion_soin_ii</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Dent de Gobelin</t>
+          <t>Potion de soin II</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>resource</t>
+          <t>consumable</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -6849,12 +6849,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>potion_soin_i</t>
+          <t>potion_soin_iii</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Potion de soin I</t>
+          <t>Potion de soin III</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6863,86 +6863,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H9" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>potion_soin_ii</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Potion de soin II</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>consumable</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>potion_soin_iii</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Potion de soin III</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>consumable</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>150</v>
-      </c>
-      <c r="E11" t="n">
-        <v>40</v>
-      </c>
-      <c r="F11" t="n">
-        <v>15</v>
-      </c>
-      <c r="G11" t="n">
-        <v>20</v>
-      </c>
-      <c r="H11" t="inlineStr">
         <is>
           <t>oui</t>
         </is>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Généré le 2026-05-25 22:09 UTC</t>
+          <t>Généré le 2026-05-25 22:18 UTC</t>
         </is>
       </c>
     </row>
@@ -9476,12 +9476,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>gobelin_assassin</t>
+          <t>gobelin_ballon</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Gobelin Assassin</t>
+          <t>Gobelin Ballon</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -9490,71 +9490,67 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>286</v>
+        <v>557</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="N6" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>144</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="O6" s="3" t="n">
-        <v>548</v>
+        <v>1018</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>F+</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>sang_gobelin_hq ×1-1 (15%)</t>
-        </is>
-      </c>
+          <t>E-</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>gobelin_assassin.png</t>
+          <t>gobelin_ballon.png</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>Une créature discrète.</t>
+          <t>Un groupe de créatures inventives.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gobelin_ballon</t>
+          <t>gobelin_geant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gobelin Ballon</t>
+          <t>Gobelin Géant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9563,13 +9559,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>955</v>
       </c>
       <c r="E7" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
         <v>5</v>
@@ -9587,43 +9583,43 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="M7" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="N7" t="n">
         <v>20</v>
       </c>
       <c r="O7" t="n">
-        <v>1018</v>
+        <v>1221</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>E-</t>
+          <t>E</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>gobelin_ballon.png</t>
+          <t>gobelin_geant.png</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Un groupe de créatures inventives.</t>
+          <t>Une créature imposante.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>gobelin_geant</t>
+          <t>gobelin_runique</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Gobelin Géant</t>
+          <t>Gobelin Runique</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -9632,13 +9628,13 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>955</v>
+        <v>573</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>5</v>
@@ -9656,43 +9652,43 @@
         <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>20</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>1221</v>
+        <v>1611</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>E+</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr"/>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>gobelin_geant.png</t>
+          <t>gobelin_runique.png</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>Une créature imposante.</t>
+          <t>Une créature mystérieuse.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gobelin_runique</t>
+          <t>gobelin_superieur</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gobelin Runique</t>
+          <t>Gobelin Supérieur</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -9701,13 +9697,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>573</v>
+        <v>876</v>
       </c>
       <c r="E9" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
         <v>5</v>
@@ -9725,43 +9721,47 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>238</v>
+        <v>300</v>
       </c>
       <c r="M9" t="n">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="N9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>1611</v>
+        <v>2442</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>E+</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+          <t>D-</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>sang_gobelin_hq ×1-1 (15%)</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>gobelin_runique.png</t>
+          <t>gobelin_superieur.png</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Une créature mystérieuse.</t>
+          <t>Une créature supérieure.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>gobelin_superieur</t>
+          <t>gobelin_assassin</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Gobelin Supérieur</t>
+          <t>Gobelin Assassin</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -9770,22 +9770,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>876</v>
+        <v>564</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>0</v>
@@ -9794,16 +9794,16 @@
         <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>10</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>2442</v>
+        <v>2025</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -9817,12 +9817,12 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>gobelin_superieur.png</t>
+          <t>gobelin_assassin.png</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>Une créature supérieure.</t>
+          <t>Une créature discrète.</t>
         </is>
       </c>
     </row>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Généré le 2026-05-25 22:18 UTC</t>
+          <t>Généré le 2026-05-26 00:11 UTC</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>1</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>0</v>
@@ -849,16 +849,16 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -970,7 +970,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>6</v>
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>0</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1156,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>12</v>
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1397,10 +1397,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -1515,10 +1515,10 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0</v>
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>6</v>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1645,13 +1645,13 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -1707,10 +1707,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
         <v>12</v>
@@ -1939,19 +1939,19 @@
         <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>6</v>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -2131,7 +2131,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -2193,13 +2193,13 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>0</v>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -2255,7 +2255,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>12</v>
@@ -2487,19 +2487,19 @@
         <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
@@ -2549,10 +2549,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>14</v>
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>4</v>
@@ -2673,10 +2673,10 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -2741,10 +2741,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -2859,10 +2859,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -2877,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>28</v>
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -3224,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3239,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>6</v>
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>0</v>
@@ -3351,13 +3351,13 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3487,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>12</v>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Catalyseur d'infusion. Permet d'améliorer un équipement de panoplie. Achetable en boutique.</t>
+          <t>Catalyseur d'infusion. Améliore un équipement de panoplie. Achetable en boutique.</t>
         </is>
       </c>
     </row>
@@ -17319,7 +17319,7 @@
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -17406,12 +17406,12 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>defense_flat +5</t>
+          <t>defense_flat +3</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>defense_flat +8</t>
+          <t>defense_flat +4</t>
         </is>
       </c>
     </row>
@@ -17436,27 +17436,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Souple et résistant, renforce la vitalité du porteur.</t>
+          <t>Souple et légère, favorise l'esquive.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>max_hp_flat +4</t>
+          <t>dodge_flat +1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>max_hp_flat +8</t>
+          <t>dodge_flat +2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>max_hp_flat +20</t>
+          <t>dodge_flat +3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>max_hp_flat +32</t>
+          <t>dodge_flat +4</t>
         </is>
       </c>
     </row>
@@ -17486,22 +17486,22 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>hp_regeneration_flat +1</t>
+          <t>hp_regeneration_flat +3</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>hp_regeneration_flat +2</t>
+          <t>hp_regeneration_flat +6</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>hp_regeneration_flat +5</t>
+          <t>hp_regeneration_flat +10</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>hp_regeneration_flat +8</t>
+          <t>hp_regeneration_flat +15</t>
         </is>
       </c>
     </row>
@@ -17526,27 +17526,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Affutée par les fourbes habitudes des gobelins — frappe rare mais brutale.</t>
+          <t>Fourbe et vicieuse : frappe critique accrue.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>crit_damage_flat +1</t>
+          <t>crit_chance_flat +1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>crit_damage_flat +2</t>
+          <t>crit_chance_flat +1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>crit_damage_flat +4</t>
+          <t>crit_chance_flat +2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>crit_damage_flat +8</t>
+          <t>crit_chance_flat +3</t>
         </is>
       </c>
     </row>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>🧵</t>
+          <t>⬜</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -17571,27 +17571,27 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Tissu léger qui favorise l'agilité et l'esquive.</t>
+          <t>Tissée pour amplifier les coups critiques.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>dodge_flat +1</t>
+          <t>crit_damage_flat +2</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>dodge_flat +2</t>
+          <t>crit_damage_flat +4</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>dodge_flat +3</t>
+          <t>crit_damage_flat +6</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>dodge_flat +5</t>
+          <t>crit_damage_flat +10</t>
         </is>
       </c>
     </row>
@@ -17616,27 +17616,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Panoplie gobeline infusée — frappe critique renforcée.</t>
+          <t>Fourbe et vicieuse : frappe critique accrue. Version infusée.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>crit_damage_flat +2</t>
+          <t>crit_chance_flat +2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>crit_damage_flat +4</t>
+          <t>crit_chance_flat +2</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>crit_damage_flat +7</t>
+          <t>crit_chance_flat +3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>crit_damage_flat +12</t>
+          <t>crit_chance_flat +5</t>
         </is>
       </c>
     </row>
@@ -17661,27 +17661,27 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Panoplie slime infusée — régénération renforcée.</t>
+          <t>Imprégnée de gelée régénératrice. Version infusée.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>hp_regeneration_flat +2</t>
+          <t>hp_regeneration_flat +5</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>hp_regeneration_flat +4</t>
+          <t>hp_regeneration_flat +9</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>hp_regeneration_flat +8</t>
+          <t>hp_regeneration_flat +14</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>hp_regeneration_flat +12</t>
+          <t>hp_regeneration_flat +21</t>
         </is>
       </c>
     </row>
@@ -18228,7 +18228,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -18346,7 +18346,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -18355,10 +18355,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -18408,16 +18408,16 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>0</v>
@@ -18426,7 +18426,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0</v>
@@ -18479,10 +18479,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -18532,7 +18532,7 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -18594,22 +18594,22 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>4</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5</v>
-      </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -18659,10 +18659,10 @@
         <v>6</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0</v>
@@ -18718,25 +18718,25 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>-2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>5</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -18780,7 +18780,7 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -18801,7 +18801,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>22</v>
@@ -18842,13 +18842,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="H13" t="n">
-        <v>-8</v>
+        <v>8</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -18904,19 +18904,19 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0</v>
@@ -18966,7 +18966,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -18981,7 +18981,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -19028,7 +19028,7 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-2</v>
@@ -19043,7 +19043,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>0</v>
@@ -19090,7 +19090,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -19099,16 +19099,16 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -19161,13 +19161,13 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>0</v>
@@ -19214,7 +19214,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -19223,10 +19223,10 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -19285,10 +19285,10 @@
         <v>0</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0</v>
@@ -19338,19 +19338,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G21" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -19406,7 +19406,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>0</v>
@@ -19462,7 +19462,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -19483,7 +19483,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>44</v>
@@ -19524,13 +19524,13 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>-8</v>
+        <v>12</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>0</v>
@@ -19765,10 +19765,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -19777,7 +19777,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -19830,7 +19830,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -19889,7 +19889,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -19957,7 +19957,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>0</v>
@@ -20013,7 +20013,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -20022,10 +20022,10 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -20075,10 +20075,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -20137,10 +20137,10 @@
         <v>-4</v>
       </c>
       <c r="G9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -20149,10 +20149,10 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -20199,10 +20199,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0</v>
@@ -20217,7 +20217,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>22</v>
@@ -20258,13 +20258,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -20323,13 +20323,13 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -20382,19 +20382,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="G13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -20447,10 +20447,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0</v>
@@ -20459,7 +20459,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>0</v>
@@ -20506,10 +20506,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -20571,7 +20571,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0</v>
@@ -20583,7 +20583,7 @@
         <v>2</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>0</v>
@@ -20630,10 +20630,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -20642,10 +20642,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -20701,7 +20701,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>0</v>
@@ -20757,13 +20757,13 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -20816,19 +20816,19 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0</v>
@@ -20884,7 +20884,7 @@
         <v>8</v>
       </c>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -20943,10 +20943,10 @@
         <v>0</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>0</v>
@@ -20961,7 +20961,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>44</v>
@@ -21002,13 +21002,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="G23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H23" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -21181,19 +21181,19 @@
         <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
@@ -21243,10 +21243,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -21302,19 +21302,19 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
@@ -21364,22 +21364,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -21429,10 +21429,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0</v>
@@ -21488,19 +21488,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -21553,10 +21553,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -21729,19 +21729,19 @@
         <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
@@ -21791,10 +21791,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -21850,25 +21850,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>0</v>
@@ -21915,10 +21915,10 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21974,19 +21974,19 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -22036,19 +22036,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -22101,10 +22101,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -22277,22 +22277,22 @@
         <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>0</v>
@@ -22339,10 +22339,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -22404,7 +22404,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -22460,7 +22460,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -22469,10 +22469,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -22522,7 +22522,7 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -22531,13 +22531,13 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>0</v>
@@ -22584,7 +22584,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -22593,10 +22593,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -22652,7 +22652,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -22825,22 +22825,22 @@
         <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>0</v>
@@ -22887,10 +22887,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -22952,7 +22952,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -23008,7 +23008,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -23020,13 +23020,13 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -23079,13 +23079,13 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>0</v>
@@ -23132,7 +23132,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -23144,13 +23144,13 @@
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -23200,7 +23200,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -23376,7 +23376,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -23391,7 +23391,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>10</v>
@@ -23432,7 +23432,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -23441,10 +23441,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -23497,10 +23497,10 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -23559,10 +23559,10 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23618,7 +23618,7 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -23627,13 +23627,13 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>0</v>
@@ -23680,7 +23680,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -23689,10 +23689,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -23763,7 +23763,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>20</v>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Généré le 2026-05-26 00:11 UTC</t>
+          <t>Généré le 2026-05-26 00:32 UTC</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -908,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -970,7 +970,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>6</v>
@@ -1156,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>12</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0</v>
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>6</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>12</v>
@@ -2552,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -2614,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -3162,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -3224,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3239,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>6</v>
@@ -3472,7 +3472,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3487,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
         <v>12</v>
@@ -17318,7 +17318,7 @@
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
@@ -17401,17 +17401,17 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>defense_flat +2</t>
+          <t>defense_flat +3</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>defense_flat +3</t>
+          <t>defense_flat +5</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>defense_flat +4</t>
+          <t>defense_flat +7</t>
         </is>
       </c>
     </row>
@@ -17451,12 +17451,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>dodge_flat +3</t>
+          <t>dodge_flat +4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>dodge_flat +4</t>
+          <t>dodge_flat +6</t>
         </is>
       </c>
     </row>
@@ -17486,22 +17486,22 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>hp_regeneration_flat +3</t>
+          <t>hp_regeneration_flat +4</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>hp_regeneration_flat +6</t>
+          <t>hp_regeneration_flat +8</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>hp_regeneration_flat +10</t>
+          <t>hp_regeneration_flat +13</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>hp_regeneration_flat +15</t>
+          <t>hp_regeneration_flat +18</t>
         </is>
       </c>
     </row>
@@ -17536,17 +17536,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>crit_chance_flat +1</t>
+          <t>crit_chance_flat +2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>crit_chance_flat +2</t>
+          <t>crit_chance_flat +3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>crit_chance_flat +3</t>
+          <t>crit_chance_flat +4</t>
         </is>
       </c>
     </row>
@@ -17576,22 +17576,22 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>crit_damage_flat +2</t>
+          <t>crit_damage_flat +3</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>crit_damage_flat +4</t>
+          <t>crit_damage_flat +6</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>crit_damage_flat +6</t>
+          <t>crit_damage_flat +9</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>crit_damage_flat +10</t>
+          <t>crit_damage_flat +14</t>
         </is>
       </c>
     </row>
@@ -17626,17 +17626,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>crit_chance_flat +2</t>
+          <t>crit_chance_flat +3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>crit_chance_flat +3</t>
+          <t>crit_chance_flat +5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>crit_chance_flat +5</t>
+          <t>crit_chance_flat +6</t>
         </is>
       </c>
     </row>
@@ -17666,22 +17666,22 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>hp_regeneration_flat +5</t>
+          <t>hp_regeneration_flat +6</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>hp_regeneration_flat +9</t>
+          <t>hp_regeneration_flat +12</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>hp_regeneration_flat +14</t>
+          <t>hp_regeneration_flat +19</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>hp_regeneration_flat +21</t>
+          <t>hp_regeneration_flat +26</t>
         </is>
       </c>
     </row>
@@ -18222,7 +18222,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -18346,7 +18346,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -18408,7 +18408,7 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>1</v>
@@ -18470,7 +18470,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -18532,7 +18532,7 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -18594,7 +18594,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -18656,7 +18656,7 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>1</v>
@@ -18718,7 +18718,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -18780,7 +18780,7 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -18842,7 +18842,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G13" t="n">
         <v>-3</v>
@@ -18904,7 +18904,7 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
@@ -18966,7 +18966,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -19028,7 +19028,7 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-2</v>
@@ -19090,7 +19090,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -19152,7 +19152,7 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>-3</v>
@@ -19214,7 +19214,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -19276,7 +19276,7 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>0</v>
@@ -19338,7 +19338,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -19400,7 +19400,7 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0</v>
@@ -19462,7 +19462,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -19524,7 +19524,7 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>-3</v>
@@ -19765,7 +19765,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -19827,7 +19827,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>6</v>
@@ -19889,7 +19889,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -19951,7 +19951,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0</v>
@@ -20013,7 +20013,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -20075,7 +20075,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>4</v>
@@ -20137,7 +20137,7 @@
         <v>-4</v>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
@@ -20199,7 +20199,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>6</v>
@@ -20261,7 +20261,7 @@
         <v>-4</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
         <v>12</v>
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -20385,7 +20385,7 @@
         <v>-4</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -20447,7 +20447,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0</v>
@@ -20509,7 +20509,7 @@
         <v>-4</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -20571,7 +20571,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0</v>
@@ -20633,7 +20633,7 @@
         <v>-4</v>
       </c>
       <c r="G17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -20695,7 +20695,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0</v>
@@ -20757,7 +20757,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>-4</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0</v>
@@ -20881,7 +20881,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H21" t="n">
         <v>9</v>
@@ -20943,7 +20943,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>9</v>
@@ -21005,7 +21005,7 @@
         <v>-4</v>
       </c>
       <c r="G23" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H23" t="n">
         <v>18</v>
@@ -21246,7 +21246,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -21432,7 +21432,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0</v>
@@ -21556,7 +21556,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -21732,7 +21732,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -21791,10 +21791,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -21918,7 +21918,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -22104,7 +22104,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -22342,7 +22342,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -22404,7 +22404,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -22652,7 +22652,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -22828,7 +22828,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -22890,7 +22890,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -22952,7 +22952,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -23200,7 +23200,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -23376,7 +23376,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -23500,7 +23500,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -23562,7 +23562,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Généré le 2026-05-26 00:32 UTC</t>
+          <t>Généré le 2026-05-26 00:43 UTC</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
@@ -852,7 +852,7 @@
         <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -970,7 +970,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>6</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -1100,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1156,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>12</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1397,10 +1397,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0</v>
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>6</v>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -1707,10 +1707,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>12</v>
@@ -1942,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>6</v>
@@ -2134,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -2258,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>12</v>
@@ -2552,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>14</v>
@@ -2676,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2685,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -2741,10 +2741,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -2877,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>28</v>
@@ -3162,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -3171,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>0</v>
@@ -3224,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3239,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>6</v>
@@ -3292,7 +3292,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -3351,10 +3351,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3487,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>12</v>
@@ -21184,7 +21184,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -21193,7 +21193,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
@@ -21302,7 +21302,7 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -21311,10 +21311,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
@@ -21364,7 +21364,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -21376,7 +21376,7 @@
         <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -21432,7 +21432,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0</v>
@@ -21447,7 +21447,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>6</v>
@@ -21488,7 +21488,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -21497,10 +21497,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -21556,7 +21556,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -21571,7 +21571,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>12</v>
@@ -21732,7 +21732,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -21741,7 +21741,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
@@ -21850,7 +21850,7 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -21859,10 +21859,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
@@ -21918,7 +21918,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21933,7 +21933,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
         <v>6</v>
@@ -21974,7 +21974,7 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -21983,10 +21983,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -22045,10 +22045,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -22104,7 +22104,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>12</v>
@@ -22280,7 +22280,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -22289,7 +22289,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
@@ -22404,7 +22404,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -22419,7 +22419,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>6</v>
@@ -22460,7 +22460,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -22469,10 +22469,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -22522,7 +22522,7 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -22534,7 +22534,7 @@
         <v>2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -22584,7 +22584,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -22593,10 +22593,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -22652,7 +22652,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -22667,7 +22667,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>12</v>
@@ -22828,7 +22828,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -22837,7 +22837,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
@@ -22952,7 +22952,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -22967,7 +22967,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>6</v>
@@ -23008,7 +23008,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -23017,10 +23017,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -23132,7 +23132,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -23141,10 +23141,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -23200,7 +23200,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -23215,7 +23215,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>12</v>
@@ -23376,7 +23376,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -23391,7 +23391,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>10</v>
@@ -23432,7 +23432,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -23441,10 +23441,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -23500,7 +23500,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -23562,7 +23562,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23571,7 +23571,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -23618,7 +23618,7 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -23630,7 +23630,7 @@
         <v>2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -23680,7 +23680,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -23689,10 +23689,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -23763,7 +23763,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>20</v>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Généré le 2026-05-26 00:43 UTC</t>
+          <t>Généré le 2026-05-26 00:48 UTC</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -849,10 +849,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -908,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -970,7 +970,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -1100,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1156,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -1397,7 +1397,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0</v>
@@ -1645,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>0</v>
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -2134,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -2193,10 +2193,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -2258,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -2493,10 +2493,10 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0</v>
@@ -2552,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -2614,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2741,7 +2741,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -3162,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -3224,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3292,7 +3292,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -21184,7 +21184,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -21193,7 +21193,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
@@ -21246,7 +21246,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -21302,7 +21302,7 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -21373,10 +21373,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -21432,7 +21432,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0</v>
@@ -21447,7 +21447,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>6</v>
@@ -21488,7 +21488,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -21556,7 +21556,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -21571,7 +21571,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>12</v>
@@ -21732,7 +21732,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -21741,7 +21741,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
@@ -21794,7 +21794,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -21850,7 +21850,7 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -21859,10 +21859,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
@@ -21918,7 +21918,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21933,7 +21933,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N5" t="n">
         <v>6</v>
@@ -21974,7 +21974,7 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -22104,7 +22104,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>12</v>
@@ -22280,7 +22280,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -22289,7 +22289,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
@@ -22342,7 +22342,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -22404,7 +22404,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -22419,7 +22419,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>6</v>
@@ -22460,7 +22460,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -22531,10 +22531,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -22584,7 +22584,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -22652,7 +22652,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -22667,7 +22667,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>12</v>
@@ -22828,7 +22828,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -22890,7 +22890,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -22952,7 +22952,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -23017,7 +23017,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -23079,10 +23079,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -23141,7 +23141,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -23200,7 +23200,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -23376,7 +23376,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0</v>
@@ -23391,7 +23391,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>10</v>
@@ -23432,7 +23432,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -23500,7 +23500,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -23562,7 +23562,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23571,7 +23571,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -23627,10 +23627,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -23680,7 +23680,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -23763,7 +23763,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>20</v>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -22,7 +22,7 @@
     <sheet name="⚙️ Calibrage" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$R$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$R$123</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👹 Mobs'!$A$1:$S$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🧪 Consommables'!$A$1:$H$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'📦 Ressources'!$A$1:$H$11</definedName>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🏪 Shop'!$A$1:$H$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🧬 Classes'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🌳 Skill Tree'!$A$1:$I$149</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'🏷️ Titres'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'🏷️ Titres'!$A$1:$H$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'🌸 Panoplies'!$A$1:$I$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'🐉 World Bosses'!$A$1:$M$6</definedName>
   </definedNames>
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-05-26 08:30 UTC</t>
+          <t>Généré le 2026-06-22 17:14 UTC</t>
         </is>
       </c>
     </row>
@@ -736,14 +736,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
@@ -1465,8 +1465,260 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>mvp_world_boss</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>MVP des World Boss</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>🏆</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>world_boss_mvp</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>champion_all_stats → value=2</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Meilleur contributeur du dernier world boss vaincu. +2% sur toutes vos stats. Transmis au MVP du prochain boss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tueur_slime_titan</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tueur du Titan Visqueux</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>world_boss_kill</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>slime_titan / 1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → value=3</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>A participé à la victoire contre Titan Visqueux. +3 dégâts critiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>tueur_gobelin_warlord</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Tueur du Seigneur de Guerre Gobelin</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>world_boss_kill</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>gobelin_warlord / 1</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → value=3</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>A participé à la victoire contre Seigneur de Guerre Gobelin. +3 dégâts critiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tueur_stone_colossus</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tueur du Colosse de Pierre</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>world_boss_kill</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>stone_colossus / 1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → value=3</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>A participé à la victoire contre Colosse de Pierre. +3 dégâts critiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>tueur_shadow_wraith</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Tueur du Spectre des Ténèbres</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>world_boss_kill</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>shadow_wraith / 1</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → value=3</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>A participé à la victoire contre Spectre des Ténèbres. +3 dégâts critiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>tueur_ancient_dragon</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tueur du Dragon Ancestral</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>world_boss_kill</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ancient_dragon / 1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → value=3</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>A participé à la victoire contre Dragon Ancestral. +3 dégâts critiques.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H17"/>
+  <autoFilter ref="A1:H23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1878,7 +2130,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="33" customWidth="1" min="11" max="11"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
   </cols>
@@ -1983,9 +2235,10 @@
       <c r="J2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>damage_immunity_threshold = 5</t>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>damage_immunity_threshold = 5
+auto_heal_per_turn = 50</t>
         </is>
       </c>
       <c r="L2" s="5" t="n">
@@ -1993,7 +2246,7 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>Un slime ancestral devenu colosse, sa masse étouffante absorbe les coups les plus faibles.</t>
+          <t>Un slime ancestral devenu colosse, sa masse étouffante absorbe les coups les plus faibles et se régénère lentement.</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2286,8 @@
       <c r="K3" s="9" t="inlineStr">
         <is>
           <t>enrage_below_pct = 30
-enrage_attack_multiplier = 1.5</t>
+enrage_attack_multiplier = 1.5
+adds = {'attack': 80, 'summon_turn_interval': 4, 'max_active': 3}</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -2041,7 +2295,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Le chef d'une horde sanguinaire. Plus il est blessé, plus sa rage l'amplifie.</t>
+          <t>Le chef d'une horde sanguinaire. Plus il est blessé, plus sa rage l'amplifie, et il appelle des renforts.</t>
         </is>
       </c>
     </row>
@@ -2078,9 +2332,10 @@
       <c r="J4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>damage_immunity_threshold = 50</t>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>damage_immunity_threshold = 50
+reflect_pct = 15</t>
         </is>
       </c>
       <c r="L4" s="5" t="n">
@@ -2088,7 +2343,7 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>Une statue runique animée par d'antiques magies. Inébranlable face aux frappes faibles.</t>
+          <t>Une statue runique animée par d'antiques magies. Inébranlable face aux frappes faibles, sa carapace renvoie une part des coups.</t>
         </is>
       </c>
     </row>
@@ -2125,9 +2380,10 @@
       <c r="J5" t="n">
         <v>30</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>crit_immunity = True</t>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>crit_immunity = True
+phases = [{'below_pct': 50, 'attack_multiplier': 1.3}, {'below_pct': 20, 'attack_multiplier': 1.6}]</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -2135,7 +2391,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Une entité incorporelle qui glisse entre les coups. Les coups critiques traversent sa forme étherée.</t>
+          <t>Une entité incorporelle qui glisse entre les coups. Les coups critiques traversent sa forme étherée, et il mute en s'affaiblissant.</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2432,11 @@
         <is>
           <t>damage_immunity_threshold = 100
 enrage_below_pct = 25
-enrage_attack_multiplier = 1.8</t>
+enrage_attack_multiplier = 1.8
+auto_heal_per_turn = 2000
+reflect_pct = 20
+adds = {'attack': 250, 'summon_turn_interval': 5, 'max_active': 2}
+phases = [{'below_pct': 50, 'attack_multiplier': 1.25}]</t>
         </is>
       </c>
       <c r="L6" s="5" t="n">
@@ -2184,7 +2444,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>Le sommet de l'évolution. Inflige des coups dévastateurs et entre en rage à la fin.</t>
+          <t>Le sommet de l'évolution. Inflige des coups dévastateurs, renvoie les frappes, invoque des drakelings, se régénère et entre en rage à la fin.</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R118"/>
+  <dimension ref="A1:R123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -2706,12 +2966,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>gobelin_greataxe</t>
+          <t>warlord_blade</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Grande hache gobeline</t>
+          <t>Lame du Seigneur de Guerre</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -2726,21 +2986,21 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>gobelin</t>
+          <t>boss</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H2" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>0</v>
@@ -2749,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L2" s="5" t="n">
         <v>0</v>
@@ -2772,19 +3032,19 @@
       </c>
       <c r="R2" s="5" t="inlineStr">
         <is>
-          <t>2 mains — crit massifs, on se découvre complètement.</t>
+          <t>Trophée du Seigneur Gobelin. Tranchante et sanguinaire.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gobelin_axe</t>
+          <t>gobelin_greataxe</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hache gobeline</t>
+          <t>Grande hache gobeline</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2804,16 +3064,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -2845,19 +3105,19 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Hache fruste taillée par les gobelins. Une main.</t>
+          <t>2 mains — crit massifs, on se découvre complètement.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>gobelin_blade</t>
+          <t>gobelin_axe</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Lame gobeline</t>
+          <t>Hache gobeline</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -2918,19 +3178,19 @@
       </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>Lame ébréchée mais redoutable, taillée d'os de gobelin.</t>
+          <t>Hache fruste taillée par les gobelins. Une main.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gobelin_greataxe_plus</t>
+          <t>gobelin_blade</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grande hache gobeline +</t>
+          <t>Lame gobeline</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2945,21 +3205,21 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>gobelin_plus</t>
+          <t>gobelin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2968,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2991,19 +3251,19 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2 mains — crit massifs, on se découvre complètement. — version infusée (améliorée).</t>
+          <t>Lame ébréchée mais redoutable, taillée d'os de gobelin.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>gobelin_axe_plus</t>
+          <t>gobelin_greataxe_plus</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Hache gobeline +</t>
+          <t>Grande hache gobeline +</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -3023,16 +3283,16 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>0</v>
@@ -3064,19 +3324,19 @@
       </c>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>Hache fruste taillée par les gobelins. Une main. — version infusée (améliorée).</t>
+          <t>2 mains — crit massifs, on se découvre complètement. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gobelin_blade_plus</t>
+          <t>gobelin_axe_plus</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lame gobeline +</t>
+          <t>Hache gobeline +</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3137,19 +3397,19 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Lame ébréchée mais redoutable, taillée d'os de gobelin. — version infusée (améliorée).</t>
+          <t>Hache fruste taillée par les gobelins. Une main. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>iron_dagger</t>
+          <t>gobelin_blade_plus</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Dague en fer</t>
+          <t>Lame gobeline +</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3164,12 +3424,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>gobelin_plus</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -3178,16 +3438,16 @@
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" s="5" t="n">
         <v>0</v>
@@ -3210,19 +3470,19 @@
       </c>
       <c r="R8" s="5" t="inlineStr">
         <is>
-          <t>Dague affûtée, légère et discrète.</t>
+          <t>Lame ébréchée mais redoutable, taillée d'os de gobelin. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>iron_greatsword</t>
+          <t>iron_dagger</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Espadon en fer</t>
+          <t>Dague en fer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3242,19 +3502,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -3269,7 +3529,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -3283,19 +3543,19 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Lame à 2 mains — frappe lourde mais on s'expose en attaquant.</t>
+          <t>Dague affûtée, légère et discrète.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>iron_sword</t>
+          <t>iron_greatsword</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Épée en fer</t>
+          <t>Espadon en fer</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3315,19 +3575,19 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>0</v>
@@ -3342,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="O10" s="5" t="n">
         <v>0</v>
@@ -3356,19 +3616,19 @@
       </c>
       <c r="R10" s="5" t="inlineStr">
         <is>
-          <t>Variante équilibrée de la dague en fer — atk + un peu de def/PV.</t>
+          <t>Lame à 2 mains — frappe lourde mais on s'expose en attaquant.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>leather_dagger</t>
+          <t>iron_sword</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dague en cuir</t>
+          <t>Épée en fer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3383,7 +3643,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>leather</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3400,7 +3660,7 @@
         <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -3412,7 +3672,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -3429,19 +3689,19 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Variante offensive de la lame en cuir — un peu d'attaque en plus.</t>
+          <t>Variante équilibrée de la dague en fer — atk + un peu de def/PV.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>leather_greatsword</t>
+          <t>leather_dagger</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Grande lame en cuir</t>
+          <t>Dague en cuir</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -3461,19 +3721,19 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>0</v>
@@ -3485,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>0</v>
@@ -3502,19 +3762,19 @@
       </c>
       <c r="R12" s="5" t="inlineStr">
         <is>
-          <t>2 mains — atk solide pour la panoplie cuir, on perd en couverture.</t>
+          <t>Variante offensive de la lame en cuir — un peu d'attaque en plus.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>leather_main_droite</t>
+          <t>leather_greatsword</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lame en cuir</t>
+          <t>Grande lame en cuir</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3534,19 +3794,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -3558,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3571,23 +3831,23 @@
         <v/>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
+          <t>2 mains — atk solide pour la panoplie cuir, on perd en couverture.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>linen_greatblade</t>
+          <t>leather_main_droite</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Grande lame en lin</t>
+          <t>Lame en cuir</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -3602,24 +3862,24 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>linen</t>
+          <t>leather</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>0</v>
@@ -3628,10 +3888,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>0</v>
@@ -3644,23 +3904,23 @@
         <v/>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>2 mains — crit dmg massif mais peu de couverture.</t>
+          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>linen_main_droite</t>
+          <t>linen_greatblade</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lame en lin</t>
+          <t>Grande lame en lin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3680,28 +3940,28 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H15" t="n">
+        <v>16</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>8</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -3717,23 +3977,23 @@
         <v/>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+          <t>2 mains — crit dmg massif mais peu de couverture.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>linen_rapier</t>
+          <t>linen_main_droite</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Rapière en lin</t>
+          <t>Lame en lin</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -3790,23 +4050,23 @@
         <v/>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>Variante speed/crit de la lame en lin — précise mais fragile.</t>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>slime_blade</t>
+          <t>linen_rapier</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lame visqueuse</t>
+          <t>Rapière en lin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3821,12 +4081,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>linen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3841,13 +4101,13 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -3867,19 +4127,19 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Une épée recouverte d'une étrange matière gélatineuse. Une main.</t>
+          <t>Variante speed/crit de la lame en lin — précise mais fragile.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>slime_greatblade</t>
+          <t>slime_blade</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Lame visqueuse colossale</t>
+          <t>Lame visqueuse</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3899,22 +4159,22 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>0</v>
@@ -3940,19 +4200,19 @@
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>2 mains — frappe massive, on perd en résilience.</t>
+          <t>Une épée recouverte d'une étrange matière gélatineuse. Une main.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>slime_morningstar</t>
+          <t>slime_greatblade</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Morningstar visqueuse</t>
+          <t>Lame visqueuse colossale</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3972,22 +4232,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H19" t="n">
+        <v>16</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J19" t="n">
         <v>8</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -4013,19 +4273,19 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Variante régen de la lame visqueuse — atk soutenue + un peu de régen.</t>
+          <t>2 mains — frappe massive, on perd en résilience.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>slime_blade_plus</t>
+          <t>slime_morningstar</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Lame visqueuse +</t>
+          <t>Morningstar visqueuse</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4040,12 +4300,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>slime_plus</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -4054,13 +4314,13 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>0</v>
@@ -4086,19 +4346,19 @@
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>Une épée recouverte d'une étrange matière gélatineuse. Une main. — version infusée (améliorée).</t>
+          <t>Variante régen de la lame visqueuse — atk soutenue + un peu de régen.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>slime_greatblade_plus</t>
+          <t>slime_blade_plus</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lame visqueuse colossale +</t>
+          <t>Lame visqueuse +</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4118,22 +4378,22 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I21" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -4159,19 +4419,19 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2 mains — frappe massive, on perd en résilience. — version infusée (améliorée).</t>
+          <t>Une épée recouverte d'une étrange matière gélatineuse. Une main. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>slime_morningstar_plus</t>
+          <t>slime_greatblade_plus</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Morningstar visqueuse +</t>
+          <t>Lame visqueuse colossale +</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -4191,22 +4451,22 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J22" s="5" t="n">
         <v>12</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>0</v>
@@ -4232,19 +4492,19 @@
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>Variante régen de la lame visqueuse — atk soutenue + un peu de régen. — version infusée (améliorée).</t>
+          <t>2 mains — frappe massive, on perd en résilience. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hunter_dagger</t>
+          <t>slime_morningstar_plus</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dague du chasseur</t>
+          <t>Morningstar visqueuse +</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4257,7 +4517,11 @@
           <t>main_droite</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>slime_plus</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>uncommon</t>
@@ -4269,16 +4533,16 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4301,19 +4565,19 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Une dague légère favorisant les coups précis. Une main.</t>
+          <t>Variante régen de la lame visqueuse — atk soutenue + un peu de régen. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>wood_sword</t>
+          <t>hunter_dagger</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Épée en bois</t>
+          <t>Dague du chasseur</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -4329,7 +4593,7 @@
       <c r="E24" s="5" t="inlineStr"/>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -4347,7 +4611,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L24" s="5" t="n">
         <v>0</v>
@@ -4370,24 +4634,24 @@
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>Une arme basique pour débuter. Une main.</t>
+          <t>Une dague légère favorisant les coups précis. Une main.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gobelin_main_gauche</t>
+          <t>wood_sword</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bouclier gobelin</t>
+          <t>Épée en bois</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bouclier</t>
+          <t>Arme</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4395,14 +4659,10 @@
           <t>main_droite</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>gobelin</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4411,16 +4671,16 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -4439,23 +4699,23 @@
         <v/>
       </c>
       <c r="Q25" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
+          <t>Une arme basique pour débuter. Une main.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>gobelin_warshield</t>
+          <t>gobelin_main_gauche</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Pavois gobelin</t>
+          <t>Bouclier gobelin</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -4475,25 +4735,25 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" s="5" t="n">
         <v>0</v>
@@ -4512,23 +4772,23 @@
         <v/>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>Bouclier gobelin 2 mains — défense brute + crit, on tape moins fort.</t>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>gobelin_buckler</t>
+          <t>gobelin_warshield</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rondache gobeline</t>
+          <t>Pavois gobelin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4548,25 +4808,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -4589,19 +4849,19 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Variante du bouclier gobelin — orientée crit + défense.</t>
+          <t>Bouclier gobelin 2 mains — défense brute + crit, on tape moins fort.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>gobelin_main_gauche_plus</t>
+          <t>gobelin_buckler</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Bouclier gobelin +</t>
+          <t>Rondache gobeline</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -4616,12 +4876,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>gobelin_plus</t>
+          <t>gobelin</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -4633,13 +4893,13 @@
         <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L28" s="5" t="n">
         <v>0</v>
@@ -4658,23 +4918,23 @@
         <v/>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R28" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
+          <t>Variante du bouclier gobelin — orientée crit + défense.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>gobelin_warshield_plus</t>
+          <t>gobelin_main_gauche_plus</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pavois gobelin +</t>
+          <t>Bouclier gobelin +</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4694,25 +4954,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -4731,23 +4991,23 @@
         <v/>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Bouclier gobelin 2 mains — défense brute + crit, on tape moins fort. — version infusée (améliorée).</t>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>gobelin_buckler_plus</t>
+          <t>gobelin_warshield_plus</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Rondache gobeline +</t>
+          <t>Pavois gobelin +</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -4767,25 +5027,25 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L30" s="5" t="n">
         <v>0</v>
@@ -4808,19 +5068,19 @@
       </c>
       <c r="R30" s="5" t="inlineStr">
         <is>
-          <t>Variante du bouclier gobelin — orientée crit + défense. — version infusée (améliorée).</t>
+          <t>Bouclier gobelin 2 mains — défense brute + crit, on tape moins fort. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>iron_warshield</t>
+          <t>gobelin_buckler_plus</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pavois en fer</t>
+          <t>Rondache gobeline +</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4835,12 +5095,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>gobelin_plus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4852,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -4881,19 +5141,19 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Variante tanky de la rondache — plus de PV, moins d'esquive.</t>
+          <t>Variante du bouclier gobelin — orientée crit + défense. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>iron_buckler</t>
+          <t>iron_warshield</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Rondache en fer</t>
+          <t>Pavois en fer</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -4913,7 +5173,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -4954,19 +5214,19 @@
       </c>
       <c r="R32" s="5" t="inlineStr">
         <is>
-          <t>Un petit bouclier rond, à porter en main gauche.</t>
+          <t>Variante tanky de la rondache — plus de PV, moins d'esquive.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>iron_tower_shield</t>
+          <t>iron_buckler</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tour en fer</t>
+          <t>Rondache en fer</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4986,22 +5246,22 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J33" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -5027,19 +5287,19 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Bouclier-tour à 2 mains — forteresse mobile au prix de l'offensive.</t>
+          <t>Un petit bouclier rond, à porter en main gauche.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>leather_main_gauche</t>
+          <t>iron_tower_shield</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Bouclier en cuir</t>
+          <t>Tour en fer</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -5054,27 +5314,27 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>leather</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K34" s="5" t="n">
         <v>0</v>
@@ -5083,7 +5343,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>0</v>
@@ -5096,23 +5356,23 @@
         <v/>
       </c>
       <c r="Q34" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R34" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
+          <t>Bouclier-tour à 2 mains — forteresse mobile au prix de l'offensive.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>leather_buckler</t>
+          <t>leather_main_gauche</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rondache en cuir</t>
+          <t>Bouclier en cuir</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5169,23 +5429,23 @@
         <v/>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Variante tanky du bouclier en cuir — plus de PV, moins d'esquive.</t>
+          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>leather_tower_shield</t>
+          <t>leather_buckler</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Tour en cuir</t>
+          <t>Rondache en cuir</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -5205,19 +5465,19 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J36" s="5" t="n">
         <v>0</v>
@@ -5229,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N36" s="5" t="n">
         <v>0</v>
@@ -5246,19 +5506,19 @@
       </c>
       <c r="R36" s="5" t="inlineStr">
         <is>
-          <t>Bouclier 2 mains en cuir tanné — défense + esquive contre 0 attaque.</t>
+          <t>Variante tanky du bouclier en cuir — plus de PV, moins d'esquive.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>linen_main_gauche</t>
+          <t>leather_tower_shield</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bouclier en lin</t>
+          <t>Tour en cuir</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5273,24 +5533,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>linen</t>
+          <t>leather</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="I37" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -5299,10 +5559,10 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5315,23 +5575,23 @@
         <v/>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+          <t>Bouclier 2 mains en cuir tanné — défense + esquive contre 0 attaque.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>linen_tower_shield</t>
+          <t>linen_main_gauche</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Tour en lin</t>
+          <t>Bouclier en lin</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -5351,19 +5611,19 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J38" s="5" t="n">
         <v>0</v>
@@ -5372,7 +5632,7 @@
         <v>0</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M38" s="5" t="n">
         <v>0</v>
@@ -5388,23 +5648,23 @@
         <v/>
       </c>
       <c r="Q38" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R38" s="5" t="inlineStr">
         <is>
-          <t>Bouclier 2 mains en lin — pure esquive, dégâts en chute libre.</t>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>linen_aegis</t>
+          <t>linen_tower_shield</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Égide en lin</t>
+          <t>Tour en lin</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5424,19 +5684,19 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="I39" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -5445,7 +5705,7 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -5465,19 +5725,19 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Variante esquive du bouclier en lin — optimisée pour les agiles.</t>
+          <t>Bouclier 2 mains en lin — pure esquive, dégâts en chute libre.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>slime_buckler</t>
+          <t>linen_aegis</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Bouclier de gel</t>
+          <t>Égide en lin</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -5492,7 +5752,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>linen</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -5512,13 +5772,13 @@
         <v>7</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" s="5" t="n">
         <v>0</v>
@@ -5538,19 +5798,19 @@
       </c>
       <c r="R40" s="5" t="inlineStr">
         <is>
-          <t>Variante régen du bouclier visqueux — moins de PV, plus de régen.</t>
+          <t>Variante esquive du bouclier en lin — optimisée pour les agiles.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>slime_shield</t>
+          <t>slime_buckler</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bouclier visqueux</t>
+          <t>Bouclier de gel</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5570,7 +5830,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5611,19 +5871,19 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Bouclier en bois enveloppé de gel de slime — absorbe les chocs comme une éponge.</t>
+          <t>Variante régen du bouclier visqueux — moins de PV, plus de régen.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>slime_tower_shield</t>
+          <t>slime_shield</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Tour de gel</t>
+          <t>Bouclier visqueux</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -5643,22 +5903,22 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K42" s="5" t="n">
         <v>0</v>
@@ -5684,19 +5944,19 @@
       </c>
       <c r="R42" s="5" t="inlineStr">
         <is>
-          <t>Bouclier 2 mains — pure défense, on n'attaque presque plus.</t>
+          <t>Bouclier en bois enveloppé de gel de slime — absorbe les chocs comme une éponge.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>slime_buckler_plus</t>
+          <t>slime_tower_shield</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bouclier de gel +</t>
+          <t>Tour de gel</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5711,27 +5971,27 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>slime_plus</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="I43" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J43" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -5757,19 +6017,19 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Variante régen du bouclier visqueux — moins de PV, plus de régen. — version infusée (améliorée).</t>
+          <t>Bouclier 2 mains — pure défense, on n'attaque presque plus.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>slime_shield_plus</t>
+          <t>slime_buckler_plus</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Bouclier visqueux +</t>
+          <t>Bouclier de gel +</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -5789,7 +6049,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -5830,19 +6090,19 @@
       </c>
       <c r="R44" s="5" t="inlineStr">
         <is>
-          <t>Bouclier en bois enveloppé de gel de slime — absorbe les chocs comme une éponge. — version infusée (améliorée).</t>
+          <t>Variante régen du bouclier visqueux — moins de PV, plus de régen. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>slime_tower_shield_plus</t>
+          <t>slime_shield_plus</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tour de gel +</t>
+          <t>Bouclier visqueux +</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5862,22 +6122,22 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J45" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -5903,19 +6163,19 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Bouclier 2 mains — pure défense, on n'attaque presque plus. — version infusée (améliorée).</t>
+          <t>Bouclier en bois enveloppé de gel de slime — absorbe les chocs comme une éponge. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>wooden_shield</t>
+          <t>slime_tower_shield_plus</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Bouclier en bois</t>
+          <t>Tour de gel +</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -5928,25 +6188,29 @@
           <t>main_droite</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>slime_plus</t>
+        </is>
+      </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K46" s="5" t="n">
         <v>0</v>
@@ -5972,39 +6236,35 @@
       </c>
       <c r="R46" s="5" t="inlineStr">
         <is>
-          <t>Un bouclier léger, à porter en main gauche.</t>
+          <t>Bouclier 2 mains — pure défense, on n'attaque presque plus. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>gobelin_crown</t>
+          <t>wooden_shield</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Couronne gobeline</t>
+          <t>Bouclier en bois</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Casque</t>
+          <t>Bouclier</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>casque</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>gobelin</t>
-        </is>
-      </c>
+          <t>main_droite</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6013,13 +6273,13 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -6045,19 +6305,19 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Couronne tribale, légère et étrange.</t>
+          <t>Un bouclier léger, à porter en main gauche.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>gobelin_crown_plus</t>
+          <t>gobelin_crown</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Couronne gobeline +</t>
+          <t>Couronne gobeline</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -6072,12 +6332,12 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>gobelin_plus</t>
+          <t>gobelin</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -6086,7 +6346,7 @@
         </is>
       </c>
       <c r="H48" s="5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I48" s="5" t="n">
         <v>0</v>
@@ -6118,19 +6378,19 @@
       </c>
       <c r="R48" s="5" t="inlineStr">
         <is>
-          <t>Couronne tribale, légère et étrange. — version infusée (améliorée).</t>
+          <t>Couronne tribale, légère et étrange.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>iron_helmet</t>
+          <t>gobelin_crown_plus</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Casque de fer</t>
+          <t>Couronne gobeline +</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6145,12 +6405,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>gobelin_plus</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6159,13 +6419,13 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -6191,19 +6451,19 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Un casque robuste forgé dans du fer.</t>
+          <t>Couronne tribale, légère et étrange. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>leather_cap</t>
+          <t>iron_helmet</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Casque en cuir</t>
+          <t>Casque de fer</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -6218,12 +6478,12 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>leather</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -6238,7 +6498,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="K50" s="5" t="n">
         <v>0</v>
@@ -6247,7 +6507,7 @@
         <v>0</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>0</v>
@@ -6264,19 +6524,19 @@
       </c>
       <c r="R50" s="5" t="inlineStr">
         <is>
-          <t>Un casque léger.</t>
+          <t>Un casque robuste forgé dans du fer.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>linen_hood</t>
+          <t>leather_cap</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capuche en lin</t>
+          <t>Casque en cuir</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6291,7 +6551,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>linen</t>
+          <t>leather</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6311,16 +6571,16 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
         <v>7</v>
-      </c>
-      <c r="L51" t="n">
-        <v>12</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -6337,19 +6597,19 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Une capuche légère cousue dans du lin tressé.</t>
+          <t>Un casque léger.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>slime_casque</t>
+          <t>linen_hood</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Casque de slime</t>
+          <t>Capuche en lin</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -6364,12 +6624,12 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>linen</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -6384,13 +6644,13 @@
         <v>0</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M52" s="5" t="n">
         <v>0</v>
@@ -6399,30 +6659,30 @@
         <v>0</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P52" s="6">
         <f>ROUND((('⚙️ Calibrage'!$B$2+H52)*(1+(('⚙️ Calibrage'!$B$5+K52)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L52)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N52)/100))*((('⚙️ Calibrage'!$B$4+J52)+('⚙️ Calibrage'!$B$3+I52)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M52)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
       <c r="Q52" s="5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R52" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
+          <t>Une capuche légère cousue dans du lin tressé.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>slime_casque_plus</t>
+          <t>slime_casque</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Casque de slime +</t>
+          <t>Casque de slime</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6437,12 +6697,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>slime_plus</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -6457,7 +6717,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -6472,7 +6732,7 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P53" s="6">
         <f>ROUND((('⚙️ Calibrage'!$B$2+H53)*(1+(('⚙️ Calibrage'!$B$5+K53)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L53)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N53)/100))*((('⚙️ Calibrage'!$B$4+J53)+('⚙️ Calibrage'!$B$3+I53)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M53)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
@@ -6483,39 +6743,39 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>gobelin_plastron</t>
+          <t>slime_casque_plus</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Plastron gobelin</t>
+          <t>Casque de slime +</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Plastron</t>
+          <t>Casque</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>plastron</t>
+          <t>casque</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>gobelin</t>
+          <t>slime_plus</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -6524,13 +6784,13 @@
         </is>
       </c>
       <c r="H54" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="K54" s="5" t="n">
         <v>0</v>
@@ -6545,30 +6805,30 @@
         <v>0</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P54" s="6">
         <f>ROUND((('⚙️ Calibrage'!$B$2+H54)*(1+(('⚙️ Calibrage'!$B$5+K54)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L54)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N54)/100))*((('⚙️ Calibrage'!$B$4+J54)+('⚙️ Calibrage'!$B$3+I54)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M54)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
       <c r="Q54" s="5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R54" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>gobelin_plastron_plus</t>
+          <t>colossus_plate</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Plastron gobelin +</t>
+          <t>Plastron du Colosse</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6583,12 +6843,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>gobelin_plus</t>
+          <t>boss</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6597,13 +6857,13 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -6625,23 +6885,23 @@
         <v/>
       </c>
       <c r="Q55" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
+          <t>Trophée du Colosse de Pierre. Une muraille ambulante.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>iron_chest</t>
+          <t>gobelin_plastron</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Plastron de fer</t>
+          <t>Plastron gobelin</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -6656,7 +6916,7 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>gobelin</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -6670,13 +6930,13 @@
         </is>
       </c>
       <c r="H56" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I56" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K56" s="5" t="n">
         <v>0</v>
@@ -6698,23 +6958,23 @@
         <v/>
       </c>
       <c r="Q56" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R56" s="5" t="inlineStr">
         <is>
-          <t>Plastron rigide qui absorbe les coups.</t>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>leather_chest</t>
+          <t>gobelin_plastron_plus</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Plastron en cuir</t>
+          <t>Plastron gobelin +</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6729,12 +6989,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>leather</t>
+          <t>gobelin_plus</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6743,13 +7003,13 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -6758,7 +7018,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -6771,23 +7031,23 @@
         <v/>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Une protection de torse en cuir tanné.</t>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>linen_robe</t>
+          <t>iron_chest</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Robe en lin</t>
+          <t>Plastron de fer</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -6802,12 +7062,12 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>linen</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -6822,13 +7082,13 @@
         <v>0</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M58" s="5" t="n">
         <v>0</v>
@@ -6848,19 +7108,19 @@
       </c>
       <c r="R58" s="5" t="inlineStr">
         <is>
-          <t>Vêtement modeste tissé pour les apprentis.</t>
+          <t>Plastron rigide qui absorbe les coups.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>slime_plastron</t>
+          <t>leather_chest</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Plastron de slime</t>
+          <t>Plastron en cuir</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6875,12 +7135,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>leather</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6895,7 +7155,7 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -6904,36 +7164,36 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P59" s="6">
         <f>ROUND((('⚙️ Calibrage'!$B$2+H59)*(1+(('⚙️ Calibrage'!$B$5+K59)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L59)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N59)/100))*((('⚙️ Calibrage'!$B$4+J59)+('⚙️ Calibrage'!$B$3+I59)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M59)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
       <c r="Q59" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
+          <t>Une protection de torse en cuir tanné.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>slime_plastron_plus</t>
+          <t>linen_robe</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Plastron de slime +</t>
+          <t>Robe en lin</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -6948,12 +7208,12 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>slime_plus</t>
+          <t>linen</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -6968,13 +7228,13 @@
         <v>0</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M60" s="5" t="n">
         <v>0</v>
@@ -6983,45 +7243,45 @@
         <v>0</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P60" s="6">
         <f>ROUND((('⚙️ Calibrage'!$B$2+H60)*(1+(('⚙️ Calibrage'!$B$5+K60)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L60)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N60)/100))*((('⚙️ Calibrage'!$B$4+J60)+('⚙️ Calibrage'!$B$3+I60)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M60)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
       <c r="Q60" s="5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R60" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
+          <t>Vêtement modeste tissé pour les apprentis.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>gobelin_jambieres</t>
+          <t>slime_plastron</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Jambières gobelin</t>
+          <t>Plastron de slime</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jambières</t>
+          <t>Plastron</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>jambieres</t>
+          <t>plastron</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>gobelin</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7035,13 +7295,13 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -7056,45 +7316,45 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P61" s="6">
         <f>ROUND((('⚙️ Calibrage'!$B$2+H61)*(1+(('⚙️ Calibrage'!$B$5+K61)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L61)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N61)/100))*((('⚙️ Calibrage'!$B$4+J61)+('⚙️ Calibrage'!$B$3+I61)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M61)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
       <c r="Q61" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>gobelin_jambieres_plus</t>
+          <t>slime_plastron_plus</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Jambières gobelin +</t>
+          <t>Plastron de slime +</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Jambières</t>
+          <t>Plastron</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>jambieres</t>
+          <t>plastron</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>gobelin_plus</t>
+          <t>slime_plus</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
@@ -7108,13 +7368,13 @@
         </is>
       </c>
       <c r="H62" s="5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="K62" s="5" t="n">
         <v>0</v>
@@ -7129,30 +7389,30 @@
         <v>0</v>
       </c>
       <c r="O62" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P62" s="6">
         <f>ROUND((('⚙️ Calibrage'!$B$2+H62)*(1+(('⚙️ Calibrage'!$B$5+K62)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L62)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N62)/100))*((('⚙️ Calibrage'!$B$4+J62)+('⚙️ Calibrage'!$B$3+I62)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M62)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
       <c r="Q62" s="5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R62" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>iron_legs</t>
+          <t>gobelin_jambieres</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jambières de fer</t>
+          <t>Jambières gobelin</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7167,7 +7427,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>gobelin</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7181,13 +7441,13 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -7209,23 +7469,23 @@
         <v/>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Jambières lourdes qui sacrifient la vitesse pour la défense.</t>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>leather_legs</t>
+          <t>gobelin_jambieres_plus</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Jambières en cuir</t>
+          <t>Jambières gobelin +</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -7240,12 +7500,12 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>leather</t>
+          <t>gobelin_plus</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -7254,13 +7514,13 @@
         </is>
       </c>
       <c r="H64" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K64" s="5" t="n">
         <v>0</v>
@@ -7269,7 +7529,7 @@
         <v>0</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N64" s="5" t="n">
         <v>0</v>
@@ -7282,23 +7542,23 @@
         <v/>
       </c>
       <c r="Q64" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R64" s="5" t="inlineStr">
         <is>
-          <t>Jambières souples qui protègent les jambes.</t>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>linen_jambieres</t>
+          <t>iron_legs</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Jambières en lin</t>
+          <t>Jambières de fer</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7313,12 +7573,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>linen</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -7333,13 +7593,13 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="K65" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -7355,23 +7615,23 @@
         <v/>
       </c>
       <c r="Q65" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+          <t>Jambières lourdes qui sacrifient la vitesse pour la défense.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>slime_jambieres</t>
+          <t>leather_legs</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Jambières de slime</t>
+          <t>Jambières en cuir</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -7386,12 +7646,12 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>leather</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -7406,7 +7666,7 @@
         <v>0</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="K66" s="5" t="n">
         <v>0</v>
@@ -7415,36 +7675,36 @@
         <v>0</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N66" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O66" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P66" s="6">
         <f>ROUND((('⚙️ Calibrage'!$B$2+H66)*(1+(('⚙️ Calibrage'!$B$5+K66)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L66)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N66)/100))*((('⚙️ Calibrage'!$B$4+J66)+('⚙️ Calibrage'!$B$3+I66)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M66)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
       <c r="Q66" s="5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R66" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
+          <t>Jambières souples qui protègent les jambes.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>slime_jambieres_plus</t>
+          <t>linen_jambieres</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jambières de slime +</t>
+          <t>Jambières en lin</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7459,12 +7719,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>slime_plus</t>
+          <t>linen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -7479,13 +7739,13 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -7494,45 +7754,45 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P67" s="6">
         <f>ROUND((('⚙️ Calibrage'!$B$2+H67)*(1+(('⚙️ Calibrage'!$B$5+K67)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L67)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N67)/100))*((('⚙️ Calibrage'!$B$4+J67)+('⚙️ Calibrage'!$B$3+I67)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M67)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
       <c r="Q67" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>gobelin_bottes</t>
+          <t>slime_jambieres</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Bottes gobelin</t>
+          <t>Jambières de slime</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Bottes</t>
+          <t>Jambières</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>bottes</t>
+          <t>jambieres</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>gobelin</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
@@ -7552,10 +7812,10 @@
         <v>0</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L68" s="5" t="n">
         <v>0</v>
@@ -7567,45 +7827,45 @@
         <v>0</v>
       </c>
       <c r="O68" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P68" s="6">
         <f>ROUND((('⚙️ Calibrage'!$B$2+H68)*(1+(('⚙️ Calibrage'!$B$5+K68)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L68)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N68)/100))*((('⚙️ Calibrage'!$B$4+J68)+('⚙️ Calibrage'!$B$3+I68)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M68)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
       <c r="Q68" s="5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R68" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>gobelin_bottes_plus</t>
+          <t>slime_jambieres_plus</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bottes gobelin +</t>
+          <t>Jambières de slime +</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bottes</t>
+          <t>Jambières</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>bottes</t>
+          <t>jambieres</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>gobelin_plus</t>
+          <t>slime_plus</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7625,10 +7885,10 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="K69" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -7640,30 +7900,30 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P69" s="6">
         <f>ROUND((('⚙️ Calibrage'!$B$2+H69)*(1+(('⚙️ Calibrage'!$B$5+K69)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L69)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N69)/100))*((('⚙️ Calibrage'!$B$4+J69)+('⚙️ Calibrage'!$B$3+I69)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M69)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
       <c r="Q69" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>iron_boots</t>
+          <t>gobelin_bottes</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Bottes en fer</t>
+          <t>Bottes gobelin</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -7678,7 +7938,7 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>gobelin</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -7698,10 +7958,10 @@
         <v>0</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L70" s="5" t="n">
         <v>0</v>
@@ -7720,23 +7980,23 @@
         <v/>
       </c>
       <c r="Q70" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R70" s="5" t="inlineStr">
         <is>
-          <t>Bottes robustes, légèrement encombrantes.</t>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>leather_boots</t>
+          <t>gobelin_bottes_plus</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bottes en cuir</t>
+          <t>Bottes gobelin +</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -7751,12 +8011,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>leather</t>
+          <t>gobelin_plus</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -7771,10 +8031,10 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -7793,23 +8053,23 @@
         <v/>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Bottes souples pour les longues marches.</t>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>linen_bottes</t>
+          <t>iron_boots</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Bottes en lin</t>
+          <t>Bottes en fer</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -7824,12 +8084,12 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>linen</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -7844,13 +8104,13 @@
         <v>0</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M72" s="5" t="n">
         <v>0</v>
@@ -7866,23 +8126,23 @@
         <v/>
       </c>
       <c r="Q72" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R72" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+          <t>Bottes robustes, légèrement encombrantes.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>slime_bottes</t>
+          <t>leather_boots</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bottes de slime</t>
+          <t>Bottes en cuir</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -7897,12 +8157,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>leather</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -7917,7 +8177,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -7939,23 +8199,23 @@
         <v/>
       </c>
       <c r="Q73" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
+          <t>Bottes souples pour les longues marches.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>slime_bottes_plus</t>
+          <t>linen_bottes</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Bottes de slime +</t>
+          <t>Bottes en lin</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -7970,12 +8230,12 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>slime_plus</t>
+          <t>linen</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -7990,13 +8250,13 @@
         <v>0</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M74" s="5" t="n">
         <v>0</v>
@@ -8012,38 +8272,38 @@
         <v/>
       </c>
       <c r="Q74" s="5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="R74" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>gobelin_amulet</t>
+          <t>slime_bottes</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Amulette gobeline</t>
+          <t>Bottes de slime</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Collier</t>
+          <t>Bottes</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>collier</t>
+          <t>bottes</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>gobelin</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8057,13 +8317,13 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -8085,38 +8345,38 @@
         <v/>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Petits crocs de gobelin enfilés sur une lanière de cuir.</t>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>gobelin_amulet_plus</t>
+          <t>slime_bottes_plus</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Amulette gobeline +</t>
+          <t>Bottes de slime +</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Collier</t>
+          <t>Bottes</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>collier</t>
+          <t>bottes</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>gobelin_plus</t>
+          <t>slime_plus</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
@@ -8130,13 +8390,13 @@
         </is>
       </c>
       <c r="H76" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I76" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K76" s="5" t="n">
         <v>0</v>
@@ -8158,23 +8418,23 @@
         <v/>
       </c>
       <c r="Q76" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R76" s="5" t="inlineStr">
         <is>
-          <t>Petits crocs de gobelin enfilés sur une lanière de cuir. — version infusée (améliorée).</t>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>iron_collier</t>
+          <t>titan_gel_core</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Collier en fer</t>
+          <t>Cœur de Gel du Titan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8189,12 +8449,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>boss</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -8209,7 +8469,7 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -8224,30 +8484,30 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P77" s="6">
         <f>ROUND((('⚙️ Calibrage'!$B$2+H77)*(1+(('⚙️ Calibrage'!$B$5+K77)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L77)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N77)/100))*((('⚙️ Calibrage'!$B$4+J77)+('⚙️ Calibrage'!$B$3+I77)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M77)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
       <c r="Q77" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie iron — bonus de set actif dès 2 pièces.</t>
+          <t>Trophée du Titan Visqueux. Régénère le porteur.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>leather_collier</t>
+          <t>gobelin_amulet</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Collier en cuir</t>
+          <t>Amulette gobeline</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -8262,12 +8522,12 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>leather</t>
+          <t>gobelin</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -8276,13 +8536,13 @@
         </is>
       </c>
       <c r="H78" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I78" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K78" s="5" t="n">
         <v>0</v>
@@ -8291,7 +8551,7 @@
         <v>0</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N78" s="5" t="n">
         <v>0</v>
@@ -8304,23 +8564,23 @@
         <v/>
       </c>
       <c r="Q78" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R78" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
+          <t>Petits crocs de gobelin enfilés sur une lanière de cuir.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>linen_collier</t>
+          <t>gobelin_amulet_plus</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Collier en lin</t>
+          <t>Amulette gobeline +</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8335,12 +8595,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>linen</t>
+          <t>gobelin_plus</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -8349,7 +8609,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
@@ -8358,10 +8618,10 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -8377,23 +8637,23 @@
         <v/>
       </c>
       <c r="Q79" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+          <t>Petits crocs de gobelin enfilés sur une lanière de cuir. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>slime_pendant</t>
+          <t>iron_collier</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Pendentif de Slime</t>
+          <t>Collier en fer</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -8408,7 +8668,7 @@
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -8428,7 +8688,7 @@
         <v>0</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="K80" s="5" t="n">
         <v>0</v>
@@ -8443,30 +8703,30 @@
         <v>0</v>
       </c>
       <c r="O80" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P80" s="6">
         <f>ROUND((('⚙️ Calibrage'!$B$2+H80)*(1+(('⚙️ Calibrage'!$B$5+K80)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L80)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N80)/100))*((('⚙️ Calibrage'!$B$4+J80)+('⚙️ Calibrage'!$B$3+I80)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M80)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
       <c r="Q80" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R80" s="5" t="inlineStr">
         <is>
-          <t>Un collier orné d'une perle gélatineuse.</t>
+          <t>Pièce de la panoplie iron — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>slime_pendant_plus</t>
+          <t>leather_collier</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pendentif de Slime +</t>
+          <t>Collier en cuir</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8481,12 +8741,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>slime_plus</t>
+          <t>leather</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -8501,7 +8761,7 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>122</v>
+        <v>30</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -8510,56 +8770,56 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N81" t="n">
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P81" s="6">
         <f>ROUND((('⚙️ Calibrage'!$B$2+H81)*(1+(('⚙️ Calibrage'!$B$5+K81)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L81)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N81)/100))*((('⚙️ Calibrage'!$B$4+J81)+('⚙️ Calibrage'!$B$3+I81)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M81)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Un collier orné d'une perle gélatineuse. — version infusée (améliorée).</t>
+          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>gobelin_bracelet</t>
+          <t>linen_collier</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Bracelet gobelin</t>
+          <t>Collier en lin</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Bracelet</t>
+          <t>Collier</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>bracelet</t>
+          <t>collier</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>gobelin</t>
+          <t>linen</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -8577,10 +8837,10 @@
         <v>0</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M82" s="5" t="n">
         <v>0</v>
@@ -8596,43 +8856,43 @@
         <v/>
       </c>
       <c r="Q82" s="5" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="R82" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>gobelin_bracelet_plus</t>
+          <t>slime_pendant</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bracelet gobelin +</t>
+          <t>Pendentif de Slime</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bracelet</t>
+          <t>Collier</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>bracelet</t>
+          <t>collier</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>gobelin_plus</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -8647,13 +8907,13 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -8662,50 +8922,50 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P83" s="6">
         <f>ROUND((('⚙️ Calibrage'!$B$2+H83)*(1+(('⚙️ Calibrage'!$B$5+K83)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L83)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N83)/100))*((('⚙️ Calibrage'!$B$4+J83)+('⚙️ Calibrage'!$B$3+I83)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M83)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
       <c r="Q83" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
+          <t>Un collier orné d'une perle gélatineuse.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>iron_gauntlets</t>
+          <t>slime_pendant_plus</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Gantelets en fer</t>
+          <t>Pendentif de Slime +</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Bracelet</t>
+          <t>Collier</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>bracelet</t>
+          <t>collier</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>slime_plus</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -8720,7 +8980,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="K84" s="5" t="n">
         <v>0</v>
@@ -8735,7 +8995,7 @@
         <v>0</v>
       </c>
       <c r="O84" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P84" s="6">
         <f>ROUND((('⚙️ Calibrage'!$B$2+H84)*(1+(('⚙️ Calibrage'!$B$5+K84)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L84)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N84)/100))*((('⚙️ Calibrage'!$B$4+J84)+('⚙️ Calibrage'!$B$3+I84)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M84)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
@@ -8746,19 +9006,19 @@
       </c>
       <c r="R84" s="5" t="inlineStr">
         <is>
-          <t>Gantelets articulés, légèrement encombrants mais robustes.</t>
+          <t>Un collier orné d'une perle gélatineuse. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>leather_bracelet</t>
+          <t>gobelin_bracelet</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bracelet en cuir</t>
+          <t>Bracelet gobelin</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -8773,12 +9033,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>leather</t>
+          <t>gobelin</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -8793,13 +9053,13 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -8815,23 +9075,23 @@
         <v/>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Un bracelet simple qui assouplit les mouvements.</t>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>linen_gloves</t>
+          <t>gobelin_bracelet_plus</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Mitaines en lin</t>
+          <t>Bracelet gobelin +</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -8846,12 +9106,12 @@
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>linen</t>
+          <t>gobelin_plus</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -8860,19 +9120,19 @@
         </is>
       </c>
       <c r="H86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="5" t="n">
         <v>11</v>
-      </c>
-      <c r="I86" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="5" t="n">
-        <v>12</v>
       </c>
       <c r="M86" s="5" t="n">
         <v>0</v>
@@ -8888,23 +9148,23 @@
         <v/>
       </c>
       <c r="Q86" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R86" s="5" t="inlineStr">
         <is>
-          <t>Mitaines fines, idéales pour ne pas gêner les manipulations.</t>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>slime_bracelet</t>
+          <t>iron_gauntlets</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bracelet de slime</t>
+          <t>Gantelets en fer</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -8919,7 +9179,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -8939,7 +9199,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -8961,23 +9221,23 @@
         <v/>
       </c>
       <c r="Q87" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
+          <t>Gantelets articulés, légèrement encombrants mais robustes.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>slime_bracelet_plus</t>
+          <t>leather_bracelet</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Bracelet de slime +</t>
+          <t>Bracelet en cuir</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -8992,12 +9252,12 @@
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>slime_plus</t>
+          <t>leather</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -9012,7 +9272,7 @@
         <v>0</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="K88" s="5" t="n">
         <v>0</v>
@@ -9034,43 +9294,43 @@
         <v/>
       </c>
       <c r="Q88" s="5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R88" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
+          <t>Un bracelet simple qui assouplit les mouvements.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>gobelin_ring</t>
+          <t>linen_gloves</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bague gobeline</t>
+          <t>Mitaines en lin</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bague</t>
+          <t>Bracelet</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>bague</t>
+          <t>bracelet</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>gobelin</t>
+          <t>linen</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -9079,7 +9339,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -9088,10 +9348,10 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -9111,39 +9371,39 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Bague de tribu, vibrante d'une étrange énergie.</t>
+          <t>Mitaines fines, idéales pour ne pas gêner les manipulations.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>gobelin_ring_plus</t>
+          <t>slime_bracelet</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Bague gobeline +</t>
+          <t>Bracelet de slime</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Bague</t>
+          <t>Bracelet</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>bague</t>
+          <t>bracelet</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>gobelin_plus</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -9158,10 +9418,10 @@
         <v>0</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L90" s="5" t="n">
         <v>0</v>
@@ -9180,43 +9440,43 @@
         <v/>
       </c>
       <c r="Q90" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R90" s="5" t="inlineStr">
         <is>
-          <t>Bague de tribu, vibrante d'une étrange énergie. — version infusée (améliorée).</t>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>iron_ring</t>
+          <t>slime_bracelet_plus</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Anneau de fer</t>
+          <t>Bracelet de slime +</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bague</t>
+          <t>Bracelet</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>bague</t>
+          <t>bracelet</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>slime_plus</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -9231,7 +9491,7 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -9253,23 +9513,23 @@
         <v/>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Une bague modeste mais bien forgée.</t>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>leather_bague</t>
+          <t>dragon_heart</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Bague en cuir</t>
+          <t>Cœur du Dragon Ancestral</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -9284,12 +9544,12 @@
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>leather</t>
+          <t>boss</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>legendary</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -9298,22 +9558,22 @@
         </is>
       </c>
       <c r="H92" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K92" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N92" s="5" t="n">
         <v>0</v>
@@ -9326,23 +9586,23 @@
         <v/>
       </c>
       <c r="Q92" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R92" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
+          <t>Trophée ultime. La puissance d'un dragon dans une bague.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>linen_bague</t>
+          <t>gobelin_ring</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bague en lin</t>
+          <t>Bague gobeline</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -9357,12 +9617,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>linen</t>
+          <t>gobelin</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -9380,10 +9640,10 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L93" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
@@ -9399,23 +9659,23 @@
         <v/>
       </c>
       <c r="Q93" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+          <t>Bague de tribu, vibrante d'une étrange énergie.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>slime_bague</t>
+          <t>gobelin_ring_plus</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Bague de slime</t>
+          <t>Bague gobeline +</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -9430,12 +9690,12 @@
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>gobelin_plus</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -9450,10 +9710,10 @@
         <v>0</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L94" s="5" t="n">
         <v>0</v>
@@ -9472,23 +9732,23 @@
         <v/>
       </c>
       <c r="Q94" s="5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R94" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
+          <t>Bague de tribu, vibrante d'une étrange énergie. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>slime_bague_plus</t>
+          <t>iron_ring</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bague de slime +</t>
+          <t>Anneau de fer</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -9503,12 +9763,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>slime_plus</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -9523,7 +9783,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -9545,23 +9805,23 @@
         <v/>
       </c>
       <c r="Q95" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
+          <t>Une bague modeste mais bien forgée.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>polished_stone_ring</t>
+          <t>leather_bague</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Anneau de pierre polie</t>
+          <t>Bague en cuir</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
@@ -9574,7 +9834,11 @@
           <t>bague</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr"/>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>leather</t>
+        </is>
+      </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
           <t>common</t>
@@ -9589,10 +9853,10 @@
         <v>0</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="K96" s="5" t="n">
         <v>0</v>
@@ -9601,7 +9865,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N96" s="5" t="n">
         <v>0</v>
@@ -9614,43 +9878,43 @@
         <v/>
       </c>
       <c r="Q96" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R96" s="5" t="inlineStr">
         <is>
-          <t>Un anneau simple, taillé dans de la pierre patinée.</t>
+          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>gobelin_ceinture</t>
+          <t>linen_bague</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ceinture gobelin</t>
+          <t>Bague en lin</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ceinture</t>
+          <t>Bague</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ceinture</t>
+          <t>bague</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>gobelin</t>
+          <t>linen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -9668,10 +9932,10 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L97" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -9687,43 +9951,43 @@
         <v/>
       </c>
       <c r="Q97" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>gobelin_ceinture_plus</t>
+          <t>slime_bague</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Ceinture gobelin +</t>
+          <t>Bague de slime</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Ceinture</t>
+          <t>Bague</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>ceinture</t>
+          <t>bague</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>gobelin_plus</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -9738,13 +10002,13 @@
         <v>0</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K98" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M98" s="5" t="n">
         <v>0</v>
@@ -9760,43 +10024,43 @@
         <v/>
       </c>
       <c r="Q98" s="5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R98" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>iron_ceinture</t>
+          <t>slime_bague_plus</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ceinture en fer</t>
+          <t>Bague de slime +</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ceinture</t>
+          <t>Bague</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ceinture</t>
+          <t>bague</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>slime_plus</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -9811,7 +10075,7 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -9833,40 +10097,36 @@
         <v/>
       </c>
       <c r="Q99" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie iron — bonus de set actif dès 2 pièces.</t>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>leather_belt</t>
+          <t>polished_stone_ring</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Ceinture en cuir</t>
+          <t>Anneau de pierre polie</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Ceinture</t>
+          <t>Bague</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>ceinture</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>leather</t>
-        </is>
-      </c>
+          <t>bague</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="5" t="inlineStr">
         <is>
           <t>common</t>
@@ -9881,10 +10141,10 @@
         <v>0</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="K100" s="5" t="n">
         <v>0</v>
@@ -9910,19 +10170,19 @@
       </c>
       <c r="R100" s="5" t="inlineStr">
         <is>
-          <t>Une ceinture renforcée qui maintient l'équipement.</t>
+          <t>Un anneau simple, taillé dans de la pierre patinée.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>linen_ceinture</t>
+          <t>gobelin_ceinture</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ceinture en lin</t>
+          <t>Ceinture gobelin</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -9937,12 +10197,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>linen</t>
+          <t>gobelin</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -9963,7 +10223,7 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -9979,23 +10239,23 @@
         <v/>
       </c>
       <c r="Q101" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>slime_ceinture</t>
+          <t>gobelin_ceinture_plus</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Ceinture de slime</t>
+          <t>Ceinture gobelin +</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -10010,12 +10270,12 @@
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>gobelin_plus</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -10030,13 +10290,13 @@
         <v>0</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K102" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M102" s="5" t="n">
         <v>0</v>
@@ -10052,23 +10312,23 @@
         <v/>
       </c>
       <c r="Q102" s="5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R102" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>slime_ceinture_plus</t>
+          <t>iron_ceinture</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ceinture de slime +</t>
+          <t>Ceinture en fer</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -10083,12 +10343,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>slime_plus</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -10103,7 +10363,7 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -10125,43 +10385,43 @@
         <v/>
       </c>
       <c r="Q103" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
+          <t>Pièce de la panoplie iron — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>gobelin_cape</t>
+          <t>leather_belt</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Cape gobelin</t>
+          <t>Ceinture en cuir</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Cape</t>
+          <t>Ceinture</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>cape</t>
+          <t>ceinture</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>gobelin</t>
+          <t>leather</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -10176,10 +10436,10 @@
         <v>0</v>
       </c>
       <c r="J104" s="5" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L104" s="5" t="n">
         <v>0</v>
@@ -10198,43 +10458,43 @@
         <v/>
       </c>
       <c r="Q104" s="5" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R104" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
+          <t>Une ceinture renforcée qui maintient l'équipement.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>gobelin_cape_plus</t>
+          <t>linen_ceinture</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Cape gobelin +</t>
+          <t>Ceinture en lin</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cape</t>
+          <t>Ceinture</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>cape</t>
+          <t>ceinture</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>gobelin_plus</t>
+          <t>linen</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -10252,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
@@ -10271,38 +10531,38 @@
         <v/>
       </c>
       <c r="Q105" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>iron_cape</t>
+          <t>slime_ceinture</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Cape en fer</t>
+          <t>Ceinture de slime</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Cape</t>
+          <t>Ceinture</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>cape</t>
+          <t>ceinture</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -10322,7 +10582,7 @@
         <v>0</v>
       </c>
       <c r="J106" s="5" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="K106" s="5" t="n">
         <v>0</v>
@@ -10344,43 +10604,43 @@
         <v/>
       </c>
       <c r="Q106" s="5" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="R106" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie iron — bonus de set actif dès 2 pièces.</t>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>leather_cape</t>
+          <t>slime_ceinture_plus</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cape en cuir</t>
+          <t>Ceinture de slime +</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cape</t>
+          <t>Ceinture</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>cape</t>
+          <t>ceinture</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>leather</t>
+          <t>slime_plus</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -10395,7 +10655,7 @@
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>31</v>
+        <v>120</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -10417,23 +10677,23 @@
         <v/>
       </c>
       <c r="Q107" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>linen_cape</t>
+          <t>wraith_cloak</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Cape en lin</t>
+          <t>Cape du Spectre</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
@@ -10448,12 +10708,12 @@
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>linen</t>
+          <t>boss</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>legendary</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -10471,16 +10731,16 @@
         <v>0</v>
       </c>
       <c r="K108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="M108" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="L108" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="M108" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N108" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O108" s="5" t="n">
         <v>0</v>
@@ -10494,19 +10754,19 @@
       </c>
       <c r="R108" s="5" t="inlineStr">
         <is>
-          <t>Cape légère qui protège du vent et des regards.</t>
+          <t>Trophée du Spectre des Ténèbres. Floue les contours.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>slime_cloak</t>
+          <t>gobelin_cape</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cape gluante</t>
+          <t>Cape gobelin</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -10521,7 +10781,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>gobelin</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -10541,10 +10801,10 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -10563,23 +10823,23 @@
         <v/>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>Cape recouverte d'une pellicule de gel de slime — collante mais étonnamment résistante.</t>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>slime_cloak_plus</t>
+          <t>gobelin_cape_plus</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Cape gluante +</t>
+          <t>Cape gobelin +</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
@@ -10594,7 +10854,7 @@
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>slime_plus</t>
+          <t>gobelin_plus</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -10614,10 +10874,10 @@
         <v>0</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L110" s="5" t="n">
         <v>0</v>
@@ -10636,38 +10896,38 @@
         <v/>
       </c>
       <c r="Q110" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R110" s="5" t="inlineStr">
         <is>
-          <t>Cape recouverte d'une pellicule de gel de slime — collante mais étonnamment résistante. — version infusée (améliorée).</t>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>gobelin_boucle_oreille</t>
+          <t>iron_cape</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Boucle gobelin</t>
+          <t>Cape en fer</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Boucle d'oreille</t>
+          <t>Cape</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>boucle_oreille</t>
+          <t>cape</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>gobelin</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -10687,13 +10947,13 @@
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
         <v>0</v>
@@ -10709,43 +10969,43 @@
         <v/>
       </c>
       <c r="Q111" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
+          <t>Pièce de la panoplie iron — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>gobelin_boucle_oreille_plus</t>
+          <t>leather_cape</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>Boucle gobelin +</t>
+          <t>Cape en cuir</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Boucle d'oreille</t>
+          <t>Cape</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>boucle_oreille</t>
+          <t>cape</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>gobelin_plus</t>
+          <t>leather</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -10760,13 +11020,13 @@
         <v>0</v>
       </c>
       <c r="J112" s="5" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="K112" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M112" s="5" t="n">
         <v>0</v>
@@ -10782,43 +11042,43 @@
         <v/>
       </c>
       <c r="Q112" s="5" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="R112" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
+          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>iron_boucle_oreille</t>
+          <t>linen_cape</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Boucle en fer</t>
+          <t>Cape en lin</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Boucle d'oreille</t>
+          <t>Cape</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>boucle_oreille</t>
+          <t>cape</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>linen</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -10833,13 +11093,13 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
@@ -10855,43 +11115,43 @@
         <v/>
       </c>
       <c r="Q113" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie iron — bonus de set actif dès 2 pièces.</t>
+          <t>Cape légère qui protège du vent et des regards.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>leather_boucle_oreille</t>
+          <t>slime_cloak</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Boucle en cuir</t>
+          <t>Cape gluante</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Boucle d'oreille</t>
+          <t>Cape</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>boucle_oreille</t>
+          <t>cape</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>leather</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -10906,7 +11166,7 @@
         <v>0</v>
       </c>
       <c r="J114" s="5" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="K114" s="5" t="n">
         <v>0</v>
@@ -10928,43 +11188,43 @@
         <v/>
       </c>
       <c r="Q114" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R114" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
+          <t>Cape recouverte d'une pellicule de gel de slime — collante mais étonnamment résistante.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>linen_boucle_oreille</t>
+          <t>slime_cloak_plus</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Boucle en lin</t>
+          <t>Cape gluante +</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Boucle d'oreille</t>
+          <t>Cape</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>boucle_oreille</t>
+          <t>cape</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>linen</t>
+          <t>slime_plus</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -10979,13 +11239,13 @@
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
       </c>
       <c r="L115" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
@@ -11001,23 +11261,23 @@
         <v/>
       </c>
       <c r="Q115" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+          <t>Cape recouverte d'une pellicule de gel de slime — collante mais étonnamment résistante. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>slime_boucle_oreille</t>
+          <t>gobelin_boucle_oreille</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Boucle de slime</t>
+          <t>Boucle gobelin</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
@@ -11032,7 +11292,7 @@
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>gobelin</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
@@ -11052,13 +11312,13 @@
         <v>0</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K116" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M116" s="5" t="n">
         <v>0</v>
@@ -11074,23 +11334,23 @@
         <v/>
       </c>
       <c r="Q116" s="5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R116" s="5" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>slime_boucle_oreille_plus</t>
+          <t>gobelin_boucle_oreille_plus</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Boucle de slime +</t>
+          <t>Boucle gobelin +</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -11105,7 +11365,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>slime_plus</t>
+          <t>gobelin_plus</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -11125,13 +11385,13 @@
         <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
@@ -11147,23 +11407,23 @@
         <v/>
       </c>
       <c r="Q117" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
+          <t>Pièce de la panoplie gobelin — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>stone_earring</t>
+          <t>iron_boucle_oreille</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Boucle de pierre polie</t>
+          <t>Boucle en fer</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -11176,10 +11436,14 @@
           <t>boucle_oreille</t>
         </is>
       </c>
-      <c r="E118" s="5" t="inlineStr"/>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -11194,7 +11458,7 @@
         <v>0</v>
       </c>
       <c r="J118" s="5" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="K118" s="5" t="n">
         <v>0</v>
@@ -11206,7 +11470,7 @@
         <v>0</v>
       </c>
       <c r="N118" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O118" s="5" t="n">
         <v>0</v>
@@ -11216,17 +11480,378 @@
         <v/>
       </c>
       <c r="Q118" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R118" s="5" t="inlineStr">
         <is>
+          <t>Pièce de la panoplie iron — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>leather_boucle_oreille</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Boucle en cuir</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Boucle d'oreille</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>leather</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>31</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H119)*(1+(('⚙️ Calibrage'!$B$5+K119)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L119)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N119)/100))*((('⚙️ Calibrage'!$B$4+J119)+('⚙️ Calibrage'!$B$3+I119)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M119)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q119" t="n">
+        <v>12</v>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie leather — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>linen_boucle_oreille</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Boucle en lin</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Boucle d'oreille</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>linen</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H120)*(1+(('⚙️ Calibrage'!$B$5+K120)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L120)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N120)/100))*((('⚙️ Calibrage'!$B$4+J120)+('⚙️ Calibrage'!$B$3+I120)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M120)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q120" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="R120" s="5" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie linen — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>slime_boucle_oreille</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Boucle de slime</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Boucle d'oreille</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>slime</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>80</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H121)*(1+(('⚙️ Calibrage'!$B$5+K121)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L121)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N121)/100))*((('⚙️ Calibrage'!$B$4+J121)+('⚙️ Calibrage'!$B$3+I121)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M121)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q121" t="n">
+        <v>18</v>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>slime_boucle_oreille_plus</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>Boucle de slime +</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>Boucle d'oreille</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>slime_plus</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H122)*(1+(('⚙️ Calibrage'!$B$5+K122)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L122)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N122)/100))*((('⚙️ Calibrage'!$B$4+J122)+('⚙️ Calibrage'!$B$3+I122)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M122)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q122" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="R122" s="5" t="inlineStr">
+        <is>
+          <t>Pièce de la panoplie slime — bonus de set actif dès 2 pièces. — version infusée (améliorée).</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>stone_earring</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Boucle de pierre polie</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Boucle d'oreille</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>boucle_oreille</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>3</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H123)*(1+(('⚙️ Calibrage'!$B$5+K123)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L123)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N123)/100))*((('⚙️ Calibrage'!$B$4+J123)+('⚙️ Calibrage'!$B$3+I123)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M123)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
           <t>Petit ornement d'oreille modestement enchanté.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R118"/>
-  <conditionalFormatting sqref="P2:P118">
+  <autoFilter ref="A1:R123"/>
+  <conditionalFormatting sqref="P2:P123">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -23,9 +23,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$R$123</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👹 Mobs'!$A$1:$S$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👹 Mobs'!$A$1:$S$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🧪 Consommables'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'📦 Ressources'!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'📦 Ressources'!$A$1:$H$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'🛠️ Recettes'!$A$1:$G$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🏪 Shop'!$A$1:$H$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🧬 Classes'!$A$1:$L$4</definedName>
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-06-22 17:14 UTC</t>
+          <t>Généré le 2026-07-12 15:44 UTC</t>
         </is>
       </c>
     </row>
@@ -11873,12 +11873,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -11894,7 +11894,7 @@
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="28" customWidth="1" min="17" max="17"/>
     <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="36" customWidth="1" min="19" max="19"/>
+    <col width="48" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -12627,9 +12627,492 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>squelette</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Squelette</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mort-vivant</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>714</v>
+      </c>
+      <c r="E11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F11" t="n">
+        <v>29</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>100</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>237</v>
+      </c>
+      <c r="M11" t="n">
+        <v>114</v>
+      </c>
+      <c r="N11" t="n">
+        <v>25</v>
+      </c>
+      <c r="O11" s="7">
+        <f>ROUND((E11*(1+(H11/100)*MAX(0,I11-100)/100)*(1+G11/100))*((D11+F11*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J11/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P11" s="7">
+        <f>IFERROR(VLOOKUP(O11,'⚙️ Calibrage'!$D$2:$E$28,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>squelette.png</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Un pantin d'os réanimé. Le premier pas dans le royaume des morts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>zombie</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Zombie</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>mort-vivant</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1209</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>273</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="O12" s="7">
+        <f>ROUND((E12*(1+(H12/100)*MAX(0,I12-100)/100)*(1+G12/100))*((D12+F12*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J12/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P12" s="7">
+        <f>IFERROR(VLOOKUP(O12,'⚙️ Calibrage'!$D$2:$E$28,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>zombie.png</t>
+        </is>
+      </c>
+      <c r="S12" s="5" t="inlineStr">
+        <is>
+          <t>Une carcasse putride et lente, mais coriace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>fantome</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fantôme</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mort-vivant</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>668</v>
+      </c>
+      <c r="E13" t="n">
+        <v>62</v>
+      </c>
+      <c r="F13" t="n">
+        <v>36</v>
+      </c>
+      <c r="G13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" t="n">
+        <v>150</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>393</v>
+      </c>
+      <c r="M13" t="n">
+        <v>189</v>
+      </c>
+      <c r="N13" t="n">
+        <v>15</v>
+      </c>
+      <c r="O13" s="7">
+        <f>ROUND((E13*(1+(H13/100)*MAX(0,I13-100)/100)*(1+G13/100))*((D13+F13*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J13/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P13" s="7">
+        <f>IFERROR(VLOOKUP(O13,'⚙️ Calibrage'!$D$2:$E$28,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>fantome.png</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Une âme errante insaisissable qui glisse entre les coups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>momie</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Momie</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>mort-vivant</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1691</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>399</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O14" s="7">
+        <f>ROUND((E14*(1+(H14/100)*MAX(0,I14-100)/100)*(1+G14/100))*((D14+F14*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J14/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P14" s="7">
+        <f>IFERROR(VLOOKUP(O14,'⚙️ Calibrage'!$D$2:$E$28,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>momie.png</t>
+        </is>
+      </c>
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>Un corps embaumé aux bandelettes maudites, quasi increvable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>gargouille</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Gargouille</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>mort-vivant</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E15" t="n">
+        <v>116</v>
+      </c>
+      <c r="F15" t="n">
+        <v>26</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>100</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>456</v>
+      </c>
+      <c r="M15" t="n">
+        <v>219</v>
+      </c>
+      <c r="N15" t="n">
+        <v>7</v>
+      </c>
+      <c r="O15" s="7">
+        <f>ROUND((E15*(1+(H15/100)*MAX(0,I15-100)/100)*(1+G15/100))*((D15+F15*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J15/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P15" s="7">
+        <f>IFERROR(VLOOKUP(O15,'⚙️ Calibrage'!$D$2:$E$28,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>gargouille.png</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Une statue de pierre animée qui frappe comme un bélier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>liche_maudite</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Liche maudite</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>mort-vivant</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1193</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>541</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O16" s="7">
+        <f>ROUND((E16*(1+(H16/100)*MAX(0,I16-100)/100)*(1+G16/100))*((D16+F16*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J16/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P16" s="7">
+        <f>IFERROR(VLOOKUP(O16,'⚙️ Calibrage'!$D$2:$E$28,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>liche_maudite.png</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>Un sorcier mort-vivant dont la magie noire dévaste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>banshee</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Banshee</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>mort-vivant</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1188</v>
+      </c>
+      <c r="E17" t="n">
+        <v>107</v>
+      </c>
+      <c r="F17" t="n">
+        <v>65</v>
+      </c>
+      <c r="G17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" t="n">
+        <v>150</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>733</v>
+      </c>
+      <c r="M17" t="n">
+        <v>352</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" s="7">
+        <f>ROUND((E17*(1+(H17/100)*MAX(0,I17-100)/100)*(1+G17/100))*((D17+F17*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J17/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P17" s="7">
+        <f>IFERROR(VLOOKUP(O17,'⚙️ Calibrage'!$D$2:$E$28,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>banshee.png</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Un spectre hurlant dont le cri glaçant transperce l'âme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S10"/>
-  <conditionalFormatting sqref="O2:O10">
+  <autoFilter ref="A1:S17"/>
+  <conditionalFormatting sqref="O2:O17">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -12826,7 +13309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -13261,8 +13744,44 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>os_ancien</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Os ancien</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>999</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Ossement imprégné d'énergie nécrotique, laissé par les morts-vivants. Matériau de craft.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:H12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18102,7 +18621,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>métier mining niv. 2</t>
+          <t>{"type": "has_item", "item_code": "gobelin_tooth", "quantity": 5}</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
@@ -18148,7 +18667,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>métier woodcutting niv. 2</t>
+          <t>{"type": "has_item", "item_code": "slime_gel", "quantity": 5}</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -18194,8 +18713,8 @@
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>métier mining niv. 3
-{"type": "has_item", "item_code": "slime_gel", "quantity": 5}</t>
+          <t>{"type": "has_item", "item_code": "gobelin_tooth", "quantity": 10}
+{"type": "has_item", "item_code": "slime_gel", "quantity": 3}</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
@@ -18220,7 +18739,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
@@ -22785,7 +23304,7 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Chance 1</t>
+          <t>Sagesse 1</t>
         </is>
       </c>
       <c r="C102" s="5" t="n">
@@ -22798,7 +23317,7 @@
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
+          <t>xp_drop_percent → [1,2,3]</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -22813,12 +23332,12 @@
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>🎁</t>
+          <t>✨</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -22830,7 +23349,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bourse 1</t>
+          <t>Chance 1</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -22843,7 +23362,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>gold_drop_percent → [1,2,3]</t>
+          <t>drop_rate_multiplier → [1,2,3]</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -22858,12 +23377,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>💰</t>
+          <t>🎁</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -22875,7 +23394,7 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Sagesse 1</t>
+          <t>Réserve d'énergie 1</t>
         </is>
       </c>
       <c r="C104" s="5" t="n">
@@ -22888,7 +23407,7 @@
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>xp_drop_percent → [1,2,3]</t>
+          <t>mana_max_flat → [20,40,60]</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -22903,12 +23422,12 @@
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>🔷</t>
         </is>
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
+          <t>+20 Mana max par niveau · max +60 Mana max (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -22920,7 +23439,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Chance 1</t>
+          <t>Bourse 1</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -22933,7 +23452,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
+          <t>gold_drop_percent → [1,2,3]</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -22948,12 +23467,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>🎁</t>
+          <t>💰</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -22965,7 +23484,7 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Bourse 1</t>
+          <t>Sagesse 1</t>
         </is>
       </c>
       <c r="C106" s="5" t="n">
@@ -22978,7 +23497,7 @@
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>gold_drop_percent → [1,2,3]</t>
+          <t>xp_drop_percent → [1,2,3]</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -22993,12 +23512,12 @@
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>💰</t>
+          <t>✨</t>
         </is>
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -23055,7 +23574,7 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Sagesse 2</t>
+          <t>Chance 2</t>
         </is>
       </c>
       <c r="C108" s="5" t="n">
@@ -23068,7 +23587,7 @@
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>xp_drop_percent → [1,2,3]</t>
+          <t>drop_rate_multiplier → [1,2,3]</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
@@ -23083,12 +23602,12 @@
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>🎁</t>
         </is>
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -23100,7 +23619,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Chance 2</t>
+          <t>Réserve d'énergie 2</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -23113,7 +23632,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
+          <t>mana_max_flat → [25,50,75]</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -23128,12 +23647,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>🎁</t>
+          <t>🔷</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
+          <t>+25 Mana max par niveau · max +75 Mana max (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -23325,7 +23844,7 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Bourse 3</t>
+          <t>Réserve d'énergie 3</t>
         </is>
       </c>
       <c r="C114" s="5" t="n">
@@ -23338,7 +23857,7 @@
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>gold_drop_percent → [1,2,3]</t>
+          <t>mana_max_flat → [30,60,90]</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
@@ -23353,12 +23872,12 @@
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
-          <t>💰</t>
+          <t>🔷</t>
         </is>
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
+          <t>+30 Mana max par niveau · max +90 Mana max (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -23370,7 +23889,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Sagesse 3</t>
+          <t>Bourse 3</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -23383,7 +23902,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>xp_drop_percent → [1,2,3]</t>
+          <t>gold_drop_percent → [1,2,3]</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -23398,12 +23917,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>💰</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -23415,7 +23934,7 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Chance 3</t>
+          <t>Sagesse 3</t>
         </is>
       </c>
       <c r="C116" s="5" t="n">
@@ -23428,7 +23947,7 @@
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
+          <t>xp_drop_percent → [1,2,3]</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
@@ -23443,12 +23962,12 @@
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
-          <t>🎁</t>
+          <t>✨</t>
         </is>
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -23460,7 +23979,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Bourse 3</t>
+          <t>Chance 3</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -23473,7 +23992,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>gold_drop_percent → [1,2,3]</t>
+          <t>drop_rate_multiplier → [1,2,3]</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -23488,12 +24007,12 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>💰</t>
+          <t>🎁</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -23505,7 +24024,7 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Sagesse 3</t>
+          <t>Réserve d'énergie 3</t>
         </is>
       </c>
       <c r="C118" s="5" t="n">
@@ -23518,7 +24037,7 @@
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>xp_drop_percent → [1,2,3]</t>
+          <t>mana_max_flat → [30,60,90]</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
@@ -23533,12 +24052,12 @@
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>🔷</t>
         </is>
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
+          <t>+30 Mana max par niveau · max +90 Mana max (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -23595,7 +24114,7 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Chance 4</t>
+          <t>Bourse 4</t>
         </is>
       </c>
       <c r="C120" s="5" t="n">
@@ -23608,7 +24127,7 @@
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
+          <t>gold_drop_percent → [1,2,3]</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
@@ -23623,12 +24142,12 @@
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>🎁</t>
+          <t>💰</t>
         </is>
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -23640,7 +24159,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Bourse 4</t>
+          <t>Sagesse 4</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -23653,7 +24172,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>gold_drop_percent → [1,2,3]</t>
+          <t>xp_drop_percent → [1,2,3]</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -23668,12 +24187,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>💰</t>
+          <t>✨</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -23685,7 +24204,7 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Sagesse 4</t>
+          <t>Chance 4</t>
         </is>
       </c>
       <c r="C122" s="5" t="n">
@@ -23698,7 +24217,7 @@
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>xp_drop_percent → [1,2,3]</t>
+          <t>drop_rate_multiplier → [1,2,3]</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
@@ -23713,12 +24232,12 @@
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>🎁</t>
         </is>
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -23730,7 +24249,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Chance 4</t>
+          <t>Réserve d'énergie 4</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -23743,7 +24262,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
+          <t>mana_max_flat → [35,70,105]</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -23758,12 +24277,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>🎁</t>
+          <t>🔷</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
+          <t>+35 Mana max par niveau · max +105 Mana max (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -23820,7 +24339,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Fortune</t>
+          <t>Flux de mana</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -23833,7 +24352,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>gold_drop_percent → [2]</t>
+          <t>mana_regeneration_flat → [1]</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -23848,12 +24367,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>💰</t>
+          <t>🌊</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Nœud spécial : +2% d'or gagné (1 amélioration, 3 pts).</t>
+          <t>Nœud spécial : +1 Régénération de mana (1 amélioration, 3 pts).</t>
         </is>
       </c>
     </row>
@@ -23955,7 +24474,7 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>Bourse 5</t>
+          <t>Réserve d'énergie 5</t>
         </is>
       </c>
       <c r="C128" s="5" t="n">
@@ -23968,7 +24487,7 @@
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>gold_drop_percent → [1,2,3]</t>
+          <t>mana_max_flat → [40,80,120]</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
@@ -23983,12 +24502,12 @@
       </c>
       <c r="H128" s="5" t="inlineStr">
         <is>
-          <t>💰</t>
+          <t>🔷</t>
         </is>
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
+          <t>+40 Mana max par niveau · max +120 Mana max (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -24000,7 +24519,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Sagesse 5</t>
+          <t>Bourse 5</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -24013,7 +24532,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>xp_drop_percent → [1,2,3]</t>
+          <t>gold_drop_percent → [1,2,3]</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -24028,12 +24547,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>💰</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -24045,7 +24564,7 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Chance 5</t>
+          <t>Sagesse 5</t>
         </is>
       </c>
       <c r="C130" s="5" t="n">
@@ -24058,7 +24577,7 @@
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
+          <t>xp_drop_percent → [1,2,3]</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
@@ -24073,12 +24592,12 @@
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>🎁</t>
+          <t>✨</t>
         </is>
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -24090,7 +24609,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Érudition</t>
+          <t>Fortune</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -24103,7 +24622,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>xp_drop_percent → [2]</t>
+          <t>gold_drop_percent → [2]</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -24118,12 +24637,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>💰</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Nœud spécial : +2% d'XP gagnée (1 amélioration, 3 pts).</t>
+          <t>Nœud spécial : +2% d'or gagné (1 amélioration, 3 pts).</t>
         </is>
       </c>
     </row>
@@ -24135,7 +24654,7 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Bourse 6</t>
+          <t>Chance 6</t>
         </is>
       </c>
       <c r="C132" s="5" t="n">
@@ -24148,7 +24667,7 @@
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>gold_drop_percent → [1,2,3]</t>
+          <t>drop_rate_multiplier → [1,2,3]</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
@@ -24163,12 +24682,12 @@
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>💰</t>
+          <t>🎁</t>
         </is>
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -24180,7 +24699,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Sagesse 6</t>
+          <t>Réserve d'énergie 6</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -24193,7 +24712,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>xp_drop_percent → [1,2,3]</t>
+          <t>mana_max_flat → [45,90,135]</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -24208,12 +24727,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>🔷</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
+          <t>+45 Mana max par niveau · max +135 Mana max (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -24225,7 +24744,7 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Chance 6</t>
+          <t>Bourse 6</t>
         </is>
       </c>
       <c r="C134" s="5" t="n">
@@ -24238,7 +24757,7 @@
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
+          <t>gold_drop_percent → [1,2,3]</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
@@ -24253,12 +24772,12 @@
       </c>
       <c r="H134" s="5" t="inlineStr">
         <is>
-          <t>🎁</t>
+          <t>💰</t>
         </is>
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -24270,7 +24789,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Bourse 6</t>
+          <t>Sagesse 6</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -24283,7 +24802,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>gold_drop_percent → [1,2,3]</t>
+          <t>xp_drop_percent → [1,2,3]</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -24298,12 +24817,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>💰</t>
+          <t>✨</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -24315,7 +24834,7 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Sagesse 6</t>
+          <t>Chance 6</t>
         </is>
       </c>
       <c r="C136" s="5" t="n">
@@ -24328,7 +24847,7 @@
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>xp_drop_percent → [1,2,3]</t>
+          <t>drop_rate_multiplier → [1,2,3]</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
@@ -24343,12 +24862,12 @@
       </c>
       <c r="H136" s="5" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>🎁</t>
         </is>
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -24360,7 +24879,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Pillage</t>
+          <t>Érudition</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -24373,7 +24892,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>drop_rate_multiplier → [2]</t>
+          <t>xp_drop_percent → [2]</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -24388,12 +24907,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>🎁</t>
+          <t>✨</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Nœud spécial : +2% de chance de butin (1 amélioration, 3 pts).</t>
+          <t>Nœud spécial : +2% d'XP gagnée (1 amélioration, 3 pts).</t>
         </is>
       </c>
     </row>
@@ -24405,7 +24924,7 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Chance 7</t>
+          <t>Réserve d'énergie 7</t>
         </is>
       </c>
       <c r="C138" s="5" t="n">
@@ -24418,7 +24937,7 @@
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
+          <t>mana_max_flat → [50,100,150]</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
@@ -24433,12 +24952,12 @@
       </c>
       <c r="H138" s="5" t="inlineStr">
         <is>
-          <t>🎁</t>
+          <t>🔷</t>
         </is>
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
+          <t>+50 Mana max par niveau · max +150 Mana max (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -24585,7 +25104,7 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Bourse 7</t>
+          <t>Réserve d'énergie 7</t>
         </is>
       </c>
       <c r="C142" s="5" t="n">
@@ -24598,7 +25117,7 @@
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>gold_drop_percent → [1,2,3]</t>
+          <t>mana_max_flat → [50,100,150]</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
@@ -24613,12 +25132,12 @@
       </c>
       <c r="H142" s="5" t="inlineStr">
         <is>
-          <t>💰</t>
+          <t>🔷</t>
         </is>
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
+          <t>+50 Mana max par niveau · max +150 Mana max (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -24630,7 +25149,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Fortune</t>
+          <t>Pillage</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -24643,7 +25162,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>gold_drop_percent → [2]</t>
+          <t>drop_rate_multiplier → [2]</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -24658,12 +25177,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>💰</t>
+          <t>🎁</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Nœud spécial : +2% d'or gagné (1 amélioration, 3 pts).</t>
+          <t>Nœud spécial : +2% de chance de butin (1 amélioration, 3 pts).</t>
         </is>
       </c>
     </row>
@@ -24675,7 +25194,7 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>Sagesse 8</t>
+          <t>Bourse 8</t>
         </is>
       </c>
       <c r="C144" s="5" t="n">
@@ -24688,7 +25207,7 @@
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>xp_drop_percent → [1,2,3]</t>
+          <t>gold_drop_percent → [1,2,3]</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
@@ -24703,12 +25222,12 @@
       </c>
       <c r="H144" s="5" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>💰</t>
         </is>
       </c>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -24720,7 +25239,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Chance 8</t>
+          <t>Sagesse 8</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -24733,7 +25252,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
+          <t>xp_drop_percent → [1,2,3]</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -24748,12 +25267,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>🎁</t>
+          <t>✨</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -24765,7 +25284,7 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Bourse 8</t>
+          <t>Chance 8</t>
         </is>
       </c>
       <c r="C146" s="5" t="n">
@@ -24778,7 +25297,7 @@
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>gold_drop_percent → [1,2,3]</t>
+          <t>drop_rate_multiplier → [1,2,3]</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
@@ -24793,12 +25312,12 @@
       </c>
       <c r="H146" s="5" t="inlineStr">
         <is>
-          <t>💰</t>
+          <t>🎁</t>
         </is>
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -24810,7 +25329,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Sagesse 8</t>
+          <t>Réserve d'énergie 8</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -24823,7 +25342,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>xp_drop_percent → [1,2,3]</t>
+          <t>mana_max_flat → [55,110,165]</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -24838,12 +25357,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>🔷</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
+          <t>+55 Mana max par niveau · max +165 Mana max (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -24855,7 +25374,7 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>Chance 8</t>
+          <t>Bourse 8</t>
         </is>
       </c>
       <c r="C148" s="5" t="n">
@@ -24868,7 +25387,7 @@
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
+          <t>gold_drop_percent → [1,2,3]</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
@@ -24883,12 +25402,12 @@
       </c>
       <c r="H148" s="5" t="inlineStr">
         <is>
-          <t>🎁</t>
+          <t>💰</t>
         </is>
       </c>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
+          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
         </is>
       </c>
     </row>
@@ -24900,7 +25419,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Érudition</t>
+          <t>Flux de mana</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -24913,7 +25432,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>xp_drop_percent → [2]</t>
+          <t>mana_regeneration_flat → [1]</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -24928,12 +25447,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>🌊</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Nœud spécial : +2% d'XP gagnée (1 amélioration, 3 pts).</t>
+          <t>Nœud spécial : +1 Régénération de mana (1 amélioration, 3 pts).</t>
         </is>
       </c>
     </row>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-07-12 15:44 UTC</t>
+          <t>Généré le 2026-07-13 00:23 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👹 Mobs'!$A$1:$S$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🧪 Consommables'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'📦 Ressources'!$A$1:$H$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'🛠️ Recettes'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'🛠️ Recettes'!$A$1:$G$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🏪 Shop'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🧬 Classes'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🌳 Skill Tree'!$A$1:$I$149</definedName>
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-08-29 20:50 UTC</t>
+          <t>Généré le 2026-08-30 20:11 UTC</t>
         </is>
       </c>
     </row>
@@ -10820,16 +10820,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -10869,8 +10869,1140 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>baton_simple_recipe</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Baton simple</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>baton_simple</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>bois ×3
+silex ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>p_simple_recipe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>épé simple</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>p_simple</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>silex ×2
+bois ×2
+cuir_brut ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>dague_rouillee_recipe</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Dague rouillée</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>dague_rouillee</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>silex ×3
+os_poli ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bandana_recipe</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>bandana</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bandana</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>morceau_de_tissu ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>capuche_recipe</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>capuche</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>capuche</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>morceau_de_tissu ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>casque_recipe</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Casque</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>casque</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>eclat_de_pierre ×3
+cuir_brut ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>armure_de_garde_recipe</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>armure de garde</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>armure_de_garde</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>cuir_brut ×4
+morceau_de_tissu ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tenu_d_aventurier_recipe</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>tenu d'aventurier</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>tenu_d_aventurier</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>cuir_brut ×5
+morceau_de_tissu ×3
+os_poli ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>arc_recipe</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>bois ×4
+corne_naissante ×2
+morceau_de_tissu ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>hache_recipe</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>hache</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>hache</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>eclat_de_pierre ×4
+bois ×3
+dent_de_gobelin ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>baton_a_crane_recipe</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Bâton à crâne</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>baton_a_crane</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>os_massif ×2
+poussiere_d_ossements ×3
+bois ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sabre_recipe</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sabre</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>sabre</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>coeur_de_granit ×2
+silex ×4
+cuir_brut ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>casque_a_cornes_recipe</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Casque à cornes</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>casque_a_cornes</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>corne_naissante ×3
+eclat_de_pierre ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>faux_recipe</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Faux</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>faux</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>os_massif ×3
+larme_spectrale ×2
+coeur_de_granit ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>plaque_rouillee_recipe</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Plaque rouillée</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>plaque_rouillee</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>coeur_de_granit ×3
+eclat_de_pierre ×5
+resine_d_embaumement ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>lame_infernale_recipe</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lame infernale</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>lame_infernale</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>braise_infernale ×3
+corne_de_demon ×2
+coeur_de_granit ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>masse_cloutee_recipe</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Masse cloutée</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>masse_cloutee</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>coeur_de_granit ×4
+croc_d_ogre ×3
+os_massif ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>lame_des_enfers_recipe</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lame des enfers</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>lame_des_enfers</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>braise_infernale ×5
+corne_de_demon ×3
+c_ur_corrompu ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>couronne_dechue_recipe</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Couronne déchue</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>couronne_dechue</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>diamant ×1
+pierre_runique ×3
+larme_spectrale ×4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>katana_recipe</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>katana (D7)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>katana</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>diamant ×2
+coeur_de_granit ×5
+flamme_sacree ×1
+croc_triple ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>collier_de_perles_recipe</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Collier de perles</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>collier_de_perles</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>gel_e ×3
+morceau_de_tissu ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>fetiche_d_os_recipe</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fétiche d'os</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>fetiche_d_os</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>os_poli ×3
+lambeau_de_vetement ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>cape_silencieuse_recipe</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Cape silencieuse</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>cape_silencieuse</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>morceau_de_tissu ×4
+plume_noircie ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>aile_de_cuir_recipe</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Aile de cuir</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>aile_de_cuir</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>cuir_brut ×3
+dent_de_gobelin ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>ceinturon_epais_recipe</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Ceinturon épais</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>ceinturon_epais</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>cuir_brut ×4
+os_poli ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>brassard_de_cuir_recipe</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Brassard de cuir</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>brassard_de_cuir</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>cuir_brut ×3
+morceau_de_tissu ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>chaine_spectrale_recipe</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Chaîne spectrale</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>chaine_spectrale</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>larme_spectrale ×3
+echo_de_cri ×2
+os_poli ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ceinturon_cloute_recipe</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ceinturon clouté</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ceinturon_cloute</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>cuir_brut ×5
+eclat_de_pierre ×3
+dent_gatee ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>aile_de_pierre_recipe</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Aile de pierre</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>aile_de_pierre</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>eclat_de_pierre ×5
+coeur_de_granit ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>collier_a_pointes_recipe</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Collier à pointes</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>collier_a_pointes</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>croc_d_ogre ×3
+corne_naissante ×2
+cuir_brut ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>sceau_de_corruption_recipe</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Sceau de corruption</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>sceau_de_corruption</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>c_ur_corrompu ×2
+encre_rituelle ×2
+pierre_runique ×2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:G32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -22,7 +22,7 @@
     <sheet name="⚙️ Calibrage" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$T$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$T$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👹 Mobs'!$A$1:$S$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🧪 Consommables'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'📦 Ressources'!$A$1:$H$39</definedName>
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-08-30 20:11 UTC</t>
+          <t>Généré le 2026-08-31 10:21 UTC</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T68"/>
+  <dimension ref="A1:T73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3076,12 +3076,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dague_rouillee</t>
+          <t>dragon_heart</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dague rouillée</t>
+          <t>Cœur du Dragon Ancestral</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3097,7 +3097,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>legendary</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3106,19 +3106,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -3139,17 +3139,21 @@
       <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Il bat encore. On l'entend quand le combat se tait.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>dague_simple</t>
+          <t>dague_rouillee</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Dague simple</t>
+          <t>Dague rouillée</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3165,7 +3169,7 @@
       <c r="E8" s="5" t="inlineStr"/>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -3174,19 +3178,19 @@
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M8" s="5" t="n">
         <v>0</v>
@@ -3206,23 +3210,19 @@
       </c>
       <c r="R8" s="5" t="n"/>
       <c r="S8" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="T8" s="5" t="inlineStr">
-        <is>
-          <t>(D3)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dagues_jumelles</t>
+          <t>dague_simple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dagues jumelles</t>
+          <t>Dague simple</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3238,28 +3238,28 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L9" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -3278,23 +3278,23 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Une paire de dagues gobelines bien affutées.</t>
+          <t>(D3)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>espadon_dentele</t>
+          <t>dagues_jumelles</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Espadon denté</t>
+          <t>Dagues jumelles</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3310,19 +3310,19 @@
       <c r="E10" s="5" t="inlineStr"/>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>0</v>
@@ -3353,17 +3353,21 @@
       <c r="S10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>Une paire de dagues gobelines bien affutées.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>faux</t>
+          <t>espadon_dentele</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Faux</t>
+          <t>Espadon denté</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3379,7 +3383,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3388,25 +3392,25 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -3421,7 +3425,76 @@
       <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="T11" s="8" t="inlineStr">
+      <c r="T11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>faux</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Faux</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Arme</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H12)*(1+(('⚙️ Calibrage'!$B$5+K12)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L12)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N12)/100))*((('⚙️ Calibrage'!$B$4+J12)+('⚙️ Calibrage'!$B$3+I12)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M12)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="5" t="n"/>
+      <c r="S12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
         <is>
           <t>(D3)
 craft :fer ,boi ,griffe de goblin 
@@ -3429,84 +3502,15 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>gourdin_de_tronc</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Gourdin de tronc</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Arme</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H12)*(1+(('⚙️ Calibrage'!$B$5+K12)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L12)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N12)/100))*((('⚙️ Calibrage'!$B$4+J12)+('⚙️ Calibrage'!$B$3+I12)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M12)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="5" t="n"/>
-      <c r="S12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="5" t="inlineStr"/>
-    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>griffe_noircie</t>
+          <t>gourdin_de_tronc</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Griffe noircie</t>
+          <t>Gourdin de tronc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3522,7 +3526,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3531,7 +3535,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3540,7 +3544,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3549,7 +3553,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -3569,12 +3573,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>lame_des_enfers</t>
+          <t>griffe_noircie</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Lame des enfers</t>
+          <t>Griffe noircie</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -3590,7 +3594,7 @@
       <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -3599,7 +3603,7 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>0</v>
@@ -3608,10 +3612,10 @@
         <v>0</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>0</v>
@@ -3638,12 +3642,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>lame_infernale</t>
+          <t>lame_des_enfers</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lame infernale</t>
+          <t>Lame des enfers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3659,7 +3663,7 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>legendary</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3668,7 +3672,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3677,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -3706,12 +3710,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>masse_cloutee</t>
+          <t>warlord_blade</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Masse cloutée</t>
+          <t>Lame du Seigneur de Guerre</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -3736,7 +3740,7 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>0</v>
@@ -3745,16 +3749,16 @@
         <v>0</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="O16" s="5" t="n">
         <v>0</v>
@@ -3770,17 +3774,21 @@
       <c r="S16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T16" s="5" t="inlineStr"/>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>L'acier ébréché d'un chef gobelin qui n'a jamais reculé.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>trident_ebreche</t>
+          <t>lame_infernale</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Trident ébréché</t>
+          <t>Lame infernale</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3796,7 +3804,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3805,7 +3813,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3817,13 +3825,13 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -3843,12 +3851,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>arc</t>
+          <t>masse_cloutee</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>arc</t>
+          <t>Masse cloutée</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3864,7 +3872,7 @@
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -3873,25 +3881,25 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="O18" s="5" t="n">
         <v>0</v>
@@ -3907,7 +3915,144 @@
       <c r="S18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T18" s="7" t="inlineStr">
+      <c r="T18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>trident_ebreche</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Trident ébréché</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Arme</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H19)*(1+(('⚙️ Calibrage'!$B$5+K19)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L19)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N19)/100))*((('⚙️ Calibrage'!$B$4+J19)+('⚙️ Calibrage'!$B$3+I19)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M19)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Arme</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>arme</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H20)*(1+(('⚙️ Calibrage'!$B$5+K20)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L20)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N20)/100))*((('⚙️ Calibrage'!$B$4+J20)+('⚙️ Calibrage'!$B$3+I20)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M20)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="7" t="inlineStr">
         <is>
           <t>(D8)
 (snipeur) ta première ataque inflige +5dégat
@@ -3916,73 +4061,73 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>boucli_piquant</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>bouclié piquant</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Arme</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>arme</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="H21" t="n">
         <v>5</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I21" t="n">
         <v>2</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J21" t="n">
         <v>5</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>5</v>
       </c>
-      <c r="P19" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H19)*(1+(('⚙️ Calibrage'!$B$5+K19)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L19)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N19)/100))*((('⚙️ Calibrage'!$B$4+J19)+('⚙️ Calibrage'!$B$3+I19)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M19)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+      <c r="P21" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H21)*(1+(('⚙️ Calibrage'!$B$5+K21)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L21)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N21)/100))*((('⚙️ Calibrage'!$B$4+J21)+('⚙️ Calibrage'!$B$3+I21)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M21)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>(D2),(D4)
 quand un énémie l'ataque il perd 2pv
@@ -3991,142 +4136,142 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>grife_nergis_e_d6_energis_e_10_du_mana_en_attaque</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>grife énergisée (D6) energisée (+10% du mana en attaque)</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Arme</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>arme</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="H22" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="I20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H20)*(1+(('⚙️ Calibrage'!$B$5+K20)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L20)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N20)/100))*((('⚙️ Calibrage'!$B$4+J20)+('⚙️ Calibrage'!$B$3+I20)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M20)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+      <c r="I22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H22)*(1+(('⚙️ Calibrage'!$B$5+K22)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L22)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N22)/100))*((('⚙️ Calibrage'!$B$4+J22)+('⚙️ Calibrage'!$B$3+I22)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M22)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
-      <c r="Q20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="5" t="n">
+      <c r="Q22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="5" t="n"/>
+      <c r="S22" s="5" t="n">
         <v>1200</v>
       </c>
-      <c r="T20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="T22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>hache</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>hache</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Arme</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>arme</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="H23" t="n">
         <v>7</v>
       </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
         <v>7</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
         <v>15</v>
       </c>
-      <c r="P21" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H21)*(1+(('⚙️ Calibrage'!$B$5+K21)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L21)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N21)/100))*((('⚙️ Calibrage'!$B$4+J21)+('⚙️ Calibrage'!$B$3+I21)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M21)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+      <c r="P23" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H23)*(1+(('⚙️ Calibrage'!$B$5+K23)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L23)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N23)/100))*((('⚙️ Calibrage'!$B$4+J23)+('⚙️ Calibrage'!$B$3+I23)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M23)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>(D4)
 craft: fer ,bois ,gelé de slime ,griff de goblin
@@ -4134,142 +4279,142 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>katana</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>katana (D7)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Arme</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>arme</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="H24" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="I22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="5" t="n">
+      <c r="I24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="L22" s="5" t="n">
+      <c r="L24" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="M22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H22)*(1+(('⚙️ Calibrage'!$B$5+K22)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L22)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N22)/100))*((('⚙️ Calibrage'!$B$4+J22)+('⚙️ Calibrage'!$B$3+I22)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M22)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+      <c r="M24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H24)*(1+(('⚙️ Calibrage'!$B$5+K24)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L24)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N24)/100))*((('⚙️ Calibrage'!$B$4+J24)+('⚙️ Calibrage'!$B$3+I24)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M24)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
-      <c r="Q22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="Q24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="5" t="n"/>
+      <c r="S24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>masse</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>masse</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Arme</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>arme</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="H25" t="n">
         <v>12</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I25" t="n">
         <v>1</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>-2</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H23)*(1+(('⚙️ Calibrage'!$B$5+K23)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L23)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N23)/100))*((('⚙️ Calibrage'!$B$4+J23)+('⚙️ Calibrage'!$B$3+I23)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M23)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H25)*(1+(('⚙️ Calibrage'!$B$5+K25)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L25)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N25)/100))*((('⚙️ Calibrage'!$B$4+J25)+('⚙️ Calibrage'!$B$3+I25)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M25)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>(D5)
 craft :fer, grif de goblin, dent de goblin
@@ -4277,74 +4422,74 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>sabre</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>sabre</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Arme</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>arme</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n">
+      <c r="H26" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="5" t="n">
+      <c r="I26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="K24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="5" t="n">
+      <c r="K26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="5" t="n">
         <v>-1</v>
       </c>
-      <c r="O24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H24)*(1+(('⚙️ Calibrage'!$B$5+K24)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L24)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N24)/100))*((('⚙️ Calibrage'!$B$4+J24)+('⚙️ Calibrage'!$B$3+I24)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M24)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+      <c r="O26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H26)*(1+(('⚙️ Calibrage'!$B$5+K26)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L26)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N26)/100))*((('⚙️ Calibrage'!$B$4+J26)+('⚙️ Calibrage'!$B$3+I26)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M26)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
-      <c r="Q24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="5" t="n"/>
-      <c r="S24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="7" t="inlineStr">
+      <c r="Q26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="5" t="n"/>
+      <c r="S26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="7" t="inlineStr">
         <is>
           <t>(D4)
 craft fer ,gelé de slime ,griffe de goblin
@@ -4352,73 +4497,73 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>p_d_scrime</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>épé d'éscrime</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Arme</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>arme</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="H27" t="n">
         <v>4</v>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>-5</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>10</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N27" t="n">
         <v>3</v>
       </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H25)*(1+(('⚙️ Calibrage'!$B$5+K25)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L25)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N25)/100))*((('⚙️ Calibrage'!$B$4+J25)+('⚙️ Calibrage'!$B$3+I25)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M25)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H27)*(1+(('⚙️ Calibrage'!$B$5+K27)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L27)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N27)/100))*((('⚙️ Calibrage'!$B$4+J27)+('⚙️ Calibrage'!$B$3+I27)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M27)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>(D1)
 craft bois ,fer, gelé de slime
@@ -4426,161 +4571,20 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>p_simple</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>épé simple</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Arme</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H26)*(1+(('⚙️ Calibrage'!$B$5+K26)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L26)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N26)/100))*((('⚙️ Calibrage'!$B$4+J26)+('⚙️ Calibrage'!$B$3+I26)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M26)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
-      <c r="Q26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="5" t="n"/>
-      <c r="S26" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="T26" s="5" t="inlineStr">
-        <is>
-          <t>(D4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>grimoire_en_lambeaux</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Grimoire en lambeaux</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Bouclier</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H27)*(1+(('⚙️ Calibrage'!$B$5+K27)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L27)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N27)/100))*((('⚙️ Calibrage'!$B$4+J27)+('⚙️ Calibrage'!$B$3+I27)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M27)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
-      <c r="Q27" t="n">
-        <v>2</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="inlineStr"/>
-    </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>orbe_maudit</t>
+          <t>p_simple</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Orbe maudit</t>
+          <t>épé simple</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Bouclier</t>
+          <t>Arme</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -4591,7 +4595,7 @@
       <c r="E28" s="5" t="inlineStr"/>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -4600,25 +4604,25 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O28" s="5" t="n">
         <v>0</v>
@@ -4628,39 +4632,43 @@
         <v/>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R28" s="5" t="n"/>
       <c r="S28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="5" t="inlineStr"/>
+        <v>75</v>
+      </c>
+      <c r="T28" s="5" t="inlineStr">
+        <is>
+          <t>(D4)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>casque</t>
+          <t>grimoire_en_lambeaux</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Casque</t>
+          <t>Grimoire en lambeaux</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tête</t>
+          <t>Bouclier</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tete</t>
+          <t>arme</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4672,10 +4680,10 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -4697,42 +4705,38 @@
         <v/>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S29" t="n">
-        <v>80</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>(D2)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>casque_piquant</t>
+          <t>orbe_maudit</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Casque piquant</t>
+          <t>Orbe maudit</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Tête</t>
+          <t>Bouclier</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>tete</t>
+          <t>arme</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -4741,19 +4745,19 @@
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M30" s="5" t="n">
         <v>0</v>
@@ -4769,13 +4773,154 @@
         <v/>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R30" s="5" t="n"/>
       <c r="S30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T30" s="7" t="inlineStr">
+      <c r="T30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>casque</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Casque</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Tête</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H31)*(1+(('⚙️ Calibrage'!$B$5+K31)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L31)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N31)/100))*((('⚙️ Calibrage'!$B$4+J31)+('⚙️ Calibrage'!$B$3+I31)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M31)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>80</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>(D2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>casque_piquant</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Casque piquant</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Tête</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H32)*(1+(('⚙️ Calibrage'!$B$5+K32)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L32)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N32)/100))*((('⚙️ Calibrage'!$B$4+J32)+('⚙️ Calibrage'!$B$3+I32)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M32)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="5" t="n"/>
+      <c r="S32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="7" t="inlineStr">
         <is>
           <t>(D4)(D5)
 craft: grife de goblin ,fer
@@ -4783,152 +4928,15 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>casque_a_cornes</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Casque à cornes</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Tête</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>8</v>
-      </c>
-      <c r="J31" t="n">
-        <v>25</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H31)*(1+(('⚙️ Calibrage'!$B$5+K31)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L31)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N31)/100))*((('⚙️ Calibrage'!$B$4+J31)+('⚙️ Calibrage'!$B$3+I31)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M31)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>couronne_d_epines</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Couronne d'épines</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Tête</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr"/>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>-10</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H32)*(1+(('⚙️ Calibrage'!$B$5+K32)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L32)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N32)/100))*((('⚙️ Calibrage'!$B$4+J32)+('⚙️ Calibrage'!$B$3+I32)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M32)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
-      <c r="Q32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="5" t="n"/>
-      <c r="S32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="5" t="inlineStr"/>
-    </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>couronne_dechue</t>
+          <t>casque_a_cornes</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Couronne déchue</t>
+          <t>Casque à cornes</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4944,7 +4952,7 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4953,19 +4961,19 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4991,12 +4999,12 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>couronne_ternie</t>
+          <t>couronne_d_epines</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Couronne ternie</t>
+          <t>Couronne d'épines</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -5024,16 +5032,16 @@
         <v>0</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M34" s="5" t="n">
         <v>0</v>
@@ -5060,12 +5068,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>home_blind</t>
+          <t>couronne_dechue</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Home blindé</t>
+          <t>Couronne déchue</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5081,7 +5089,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>legendary</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5090,19 +5098,19 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J35" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -5111,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P35" s="6">
         <f>ROUND((('⚙️ Calibrage'!$B$2+H35)*(1+(('⚙️ Calibrage'!$B$5+K35)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L35)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N35)/100))*((('⚙️ Calibrage'!$B$4+J35)+('⚙️ Calibrage'!$B$3+I35)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M35)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
@@ -5123,7 +5131,144 @@
       <c r="S35" t="n">
         <v>0</v>
       </c>
-      <c r="T35" s="8" t="inlineStr">
+      <c r="T35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>couronne_ternie</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Couronne ternie</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Tête</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H36)*(1+(('⚙️ Calibrage'!$B$5+K36)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L36)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N36)/100))*((('⚙️ Calibrage'!$B$4+J36)+('⚙️ Calibrage'!$B$3+I36)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M36)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="5" t="n"/>
+      <c r="S36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>home_blind</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Home blindé</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Tête</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>12</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>5</v>
+      </c>
+      <c r="P37" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H37)*(1+(('⚙️ Calibrage'!$B$5+K37)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L37)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N37)/100))*((('⚙️ Calibrage'!$B$4+J37)+('⚙️ Calibrage'!$B$3+I37)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M37)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>(D2)
 craft : fer, fourure ,gelé de slime
@@ -5131,161 +5276,15 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>bandana</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>bandana</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Tête</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H36)*(1+(('⚙️ Calibrage'!$B$5+K36)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L36)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N36)/100))*((('⚙️ Calibrage'!$B$4+J36)+('⚙️ Calibrage'!$B$3+I36)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M36)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="5" t="n"/>
-      <c r="S36" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="T36" s="5" t="inlineStr">
-        <is>
-          <t>(D1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>capuche</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>capuche</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Tête</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>5</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H37)*(1+(('⚙️ Calibrage'!$B$5+K37)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L37)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N37)/100))*((('⚙️ Calibrage'!$B$4+J37)+('⚙️ Calibrage'!$B$3+I37)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M37)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>80</v>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>(D4) (D6)
-+20 de mana aussi</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>casque_infligeur</t>
+          <t>bandana</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>casque infligeur</t>
+          <t>bandana</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -5301,7 +5300,7 @@
       <c r="E38" s="5" t="inlineStr"/>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -5310,16 +5309,16 @@
         </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L38" s="5" t="n">
         <v>0</v>
@@ -5328,7 +5327,7 @@
         <v>0</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" s="5" t="n">
         <v>0</v>
@@ -5342,19 +5341,23 @@
       </c>
       <c r="R38" s="5" t="n"/>
       <c r="S38" s="5" t="n">
-        <v>1200</v>
-      </c>
-      <c r="T38" s="5" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="T38" s="5" t="inlineStr">
+        <is>
+          <t>(D1)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>chapeau</t>
+          <t>capuche</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>chapeau</t>
+          <t>capuche</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5379,25 +5382,25 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>5</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
       <c r="L39" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5412,21 +5415,22 @@
       <c r="S39" t="n">
         <v>80</v>
       </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>(D4</t>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>(D4) (D6)
++20 de mana aussi</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>chapeau_de_sorcier</t>
+          <t>casque_infligeur</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>chapeau de sorcier</t>
+          <t>casque infligeur</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -5442,7 +5446,7 @@
       <c r="E40" s="5" t="inlineStr"/>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -5451,19 +5455,19 @@
         </is>
       </c>
       <c r="H40" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M40" s="5" t="n">
         <v>0</v>
@@ -5483,9 +5487,150 @@
       </c>
       <c r="R40" s="5" t="n"/>
       <c r="S40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="7" t="inlineStr">
+        <v>1200</v>
+      </c>
+      <c r="T40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>chapeau</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>chapeau</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Tête</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-20</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H41)*(1+(('⚙️ Calibrage'!$B$5+K41)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L41)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N41)/100))*((('⚙️ Calibrage'!$B$4+J41)+('⚙️ Calibrage'!$B$3+I41)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M41)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>80</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>(D4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>chapeau_de_sorcier</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>chapeau de sorcier</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Tête</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H42)*(1+(('⚙️ Calibrage'!$B$5+K42)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L42)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N42)/100))*((('⚙️ Calibrage'!$B$4+J42)+('⚙️ Calibrage'!$B$3+I42)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M42)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="5" t="n"/>
+      <c r="S42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="7" t="inlineStr">
         <is>
           <t>(D6)
 craft :tissu + drop du chaman goblin
@@ -5494,142 +5639,142 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>lunette_de_pr_cision_d8_snipeur_20_de_degat_a_la_premi_re_attaque</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>lunette de précision (D8) snipeur+20% de degat a la première attaque</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Tête</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>tete</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="H43" t="n">
         <v>10</v>
       </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>10</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M43" t="n">
         <v>5</v>
       </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H41)*(1+(('⚙️ Calibrage'!$B$5+K41)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L41)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N41)/100))*((('⚙️ Calibrage'!$B$4+J41)+('⚙️ Calibrage'!$B$3+I41)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M41)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H43)*(1+(('⚙️ Calibrage'!$B$5+K43)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L43)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N43)/100))*((('⚙️ Calibrage'!$B$4+J43)+('⚙️ Calibrage'!$B$3+I43)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M43)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
         <v>1200</v>
       </c>
-      <c r="T41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="T43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>masque_de_camouflage</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>masque de camouflage</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>Tête</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>tete</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr"/>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H42" s="5" t="n">
+      <c r="H44" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="5" t="n">
+      <c r="I44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="L42" s="5" t="n">
+      <c r="L44" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="M42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="5" t="n">
+      <c r="M44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="5" t="n">
         <v>-1</v>
       </c>
-      <c r="O42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H42)*(1+(('⚙️ Calibrage'!$B$5+K42)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L42)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N42)/100))*((('⚙️ Calibrage'!$B$4+J42)+('⚙️ Calibrage'!$B$3+I42)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M42)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+      <c r="O44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H44)*(1+(('⚙️ Calibrage'!$B$5+K44)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L44)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N44)/100))*((('⚙️ Calibrage'!$B$4+J44)+('⚙️ Calibrage'!$B$3+I44)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M44)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
-      <c r="Q42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="5" t="n"/>
-      <c r="S42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" s="7" t="inlineStr">
+      <c r="Q44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="5" t="n"/>
+      <c r="S44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="7" t="inlineStr">
         <is>
           <t>(D3)
 craft ,tissu ,gelé de slime ,fourure
@@ -5637,152 +5782,15 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>corset_de_soie_noire</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Corset de soie noire</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>5</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>8</v>
-      </c>
-      <c r="N43" t="n">
-        <v>4</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H43)*(1+(('⚙️ Calibrage'!$B$5+K43)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L43)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N43)/100))*((('⚙️ Calibrage'!$B$4+J43)+('⚙️ Calibrage'!$B$3+I43)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M43)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>plaque_rouillee</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>Plaque rouillée</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr"/>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="J44" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H44)*(1+(('⚙️ Calibrage'!$B$5+K44)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L44)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N44)/100))*((('⚙️ Calibrage'!$B$4+J44)+('⚙️ Calibrage'!$B$3+I44)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M44)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
-      <c r="Q44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="5" t="n"/>
-      <c r="S44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="5" t="inlineStr"/>
-    </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>plaque_a_pointes</t>
+          <t>corset_de_soie_noire</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Plaque à pointes</t>
+          <t>Corset de soie noire</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5798,7 +5806,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5810,22 +5818,22 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5845,12 +5853,12 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>tenu_d_aventurier_niv_goblin</t>
+          <t>plaque_rouillee</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Tenu d'aventurier niv goblin</t>
+          <t>Plaque rouillée</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -5866,7 +5874,7 @@
       <c r="E46" s="5" t="inlineStr"/>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -5875,13 +5883,13 @@
         </is>
       </c>
       <c r="H46" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="K46" s="5" t="n">
         <v>0</v>
@@ -5893,7 +5901,7 @@
         <v>0</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O46" s="5" t="n">
         <v>0</v>
@@ -5909,7 +5917,216 @@
       <c r="S46" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T46" s="7" t="inlineStr">
+      <c r="T46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>plaque_a_pointes</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Plaque à pointes</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>12</v>
+      </c>
+      <c r="J47" t="n">
+        <v>40</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H47)*(1+(('⚙️ Calibrage'!$B$5+K47)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L47)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N47)/100))*((('⚙️ Calibrage'!$B$4+J47)+('⚙️ Calibrage'!$B$3+I47)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M47)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>colossus_plate</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Plastron du Colosse</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H48)*(1+(('⚙️ Calibrage'!$B$5+K48)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L48)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N48)/100))*((('⚙️ Calibrage'!$B$4+J48)+('⚙️ Calibrage'!$B$3+I48)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M48)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="5" t="n"/>
+      <c r="S48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="5" t="inlineStr">
+        <is>
+          <t>Une plaque de granit vivant, taillée dans le Colosse lui-même.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>tenu_d_aventurier_niv_goblin</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Tenu d'aventurier niv goblin</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>5</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2</v>
+      </c>
+      <c r="J49" t="n">
+        <v>15</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H49)*(1+(('⚙️ Calibrage'!$B$5+K49)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L49)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N49)/100))*((('⚙️ Calibrage'!$B$4+J49)+('⚙️ Calibrage'!$B$3+I49)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M49)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>(D4)(D5)  
 craft : tissu ,fourure et dent de goblin
@@ -5917,146 +6134,146 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>v_tement_vagabon</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>Vétement vagabon</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Corps</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>corps</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
+      <c r="H50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K47" t="n">
+      <c r="K50" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
+      <c r="L50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="N47" t="n">
+      <c r="N50" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H47)*(1+(('⚙️ Calibrage'!$B$5+K47)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L47)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N47)/100))*((('⚙️ Calibrage'!$B$4+J47)+('⚙️ Calibrage'!$B$3+I47)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M47)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+      <c r="O50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H50)*(1+(('⚙️ Calibrage'!$B$5+K50)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L50)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N50)/100))*((('⚙️ Calibrage'!$B$4+J50)+('⚙️ Calibrage'!$B$3+I50)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M50)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="inlineStr">
+      <c r="Q50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="5" t="n"/>
+      <c r="S50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="5" t="inlineStr">
         <is>
           <t>(D1) (D3)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>armure_a_suspention_visceuse</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>armure a suspention visceuse</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Corps</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>corps</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="5" t="n">
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
         <v>3</v>
       </c>
-      <c r="J48" s="5" t="n">
+      <c r="J51" t="n">
         <v>25</v>
       </c>
-      <c r="K48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="5" t="n">
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
         <v>5</v>
       </c>
-      <c r="P48" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H48)*(1+(('⚙️ Calibrage'!$B$5+K48)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L48)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N48)/100))*((('⚙️ Calibrage'!$B$4+J48)+('⚙️ Calibrage'!$B$3+I48)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M48)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+      <c r="P51" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H51)*(1+(('⚙️ Calibrage'!$B$5+K51)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L51)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N51)/100))*((('⚙️ Calibrage'!$B$4+J51)+('⚙️ Calibrage'!$B$3+I51)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M51)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
-      <c r="Q48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="5" t="n"/>
-      <c r="S48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" s="7" t="inlineStr">
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>(D2)
 craft: fer beaucoup ,gelé de slime beaucoup
@@ -6064,224 +6281,15 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>armure_de_garde</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>armure de garde</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J49" t="n">
-        <v>20</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>-20</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H49)*(1+(('⚙️ Calibrage'!$B$5+K49)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L49)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N49)/100))*((('⚙️ Calibrage'!$B$4+J49)+('⚙️ Calibrage'!$B$3+I49)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M49)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>120</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>(D2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>armure_de_m_tal_sup_rieur_d4</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>armure de métal supérieur (D2)</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I50" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="J50" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="P50" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H50)*(1+(('⚙️ Calibrage'!$B$5+K50)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L50)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N50)/100))*((('⚙️ Calibrage'!$B$4+J50)+('⚙️ Calibrage'!$B$3+I50)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M50)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
-      <c r="Q50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="5" t="n"/>
-      <c r="S50" s="5" t="n">
-        <v>1600</v>
-      </c>
-      <c r="T50" s="5" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>exo_squelette_exp_rimental_d5_d4</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>exo squelette expérimental (D5)(D4)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>20</v>
-      </c>
-      <c r="I51" t="n">
-        <v>5</v>
-      </c>
-      <c r="J51" t="n">
-        <v>20</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H51)*(1+(('⚙️ Calibrage'!$B$5+K51)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L51)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N51)/100))*((('⚙️ Calibrage'!$B$4+J51)+('⚙️ Calibrage'!$B$3+I51)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M51)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>1600</v>
-      </c>
-      <c r="T51" t="inlineStr"/>
-    </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>robe</t>
+          <t>armure_de_garde</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>robe</t>
+          <t>armure de garde</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -6309,16 +6317,16 @@
         <v>0</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>10</v>
+        <v>-20</v>
       </c>
       <c r="M52" s="5" t="n">
         <v>0</v>
@@ -6340,22 +6348,21 @@
       <c r="S52" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="T52" s="7" t="inlineStr">
-        <is>
-          <t>(D3)(D6)
-+30 mana</t>
+      <c r="T52" s="5" t="inlineStr">
+        <is>
+          <t>(D2)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>tenu_d_aprentie</t>
+          <t>armure_de_m_tal_sup_rieur_d4</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>tenu d'aprentie</t>
+          <t>armure de métal supérieur (D2)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6371,7 +6378,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -6380,28 +6387,28 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J53" t="n">
+        <v>70</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
         <v>10</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>5</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
       </c>
       <c r="P53" s="6">
         <f>ROUND((('⚙️ Calibrage'!$B$2+H53)*(1+(('⚙️ Calibrage'!$B$5+K53)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L53)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N53)/100))*((('⚙️ Calibrage'!$B$4+J53)+('⚙️ Calibrage'!$B$3+I53)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M53)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
@@ -6411,9 +6418,220 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
+        <v>1600</v>
+      </c>
+      <c r="T53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>exo_squelette_exp_rimental_d5_d4</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>exo squelette expérimental (D5)(D4)</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr"/>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H54)*(1+(('⚙️ Calibrage'!$B$5+K54)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L54)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N54)/100))*((('⚙️ Calibrage'!$B$4+J54)+('⚙️ Calibrage'!$B$3+I54)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M54)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="5" t="n"/>
+      <c r="S54" s="5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="T54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>robe</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>robe</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>7</v>
+      </c>
+      <c r="K55" t="n">
+        <v>5</v>
+      </c>
+      <c r="L55" t="n">
+        <v>10</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H55)*(1+(('⚙️ Calibrage'!$B$5+K55)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L55)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N55)/100))*((('⚙️ Calibrage'!$B$4+J55)+('⚙️ Calibrage'!$B$3+I55)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M55)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>120</v>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>(D3)(D6)
++30 mana</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>tenu_d_aprentie</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>tenu d'aprentie</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H56)*(1+(('⚙️ Calibrage'!$B$5+K56)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L56)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N56)/100))*((('⚙️ Calibrage'!$B$4+J56)+('⚙️ Calibrage'!$B$3+I56)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M56)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="5" t="n"/>
+      <c r="S56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="7" t="inlineStr">
         <is>
           <t>(D6)(D5)
 craft :fourure ,tissu et (un drop du goblin chaman 
@@ -6422,146 +6640,146 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>tenu_d_aventurier</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>tenu d'aventurier</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Corps</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>corps</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr"/>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H54" s="5" t="n">
+      <c r="H57" t="n">
         <v>3</v>
       </c>
-      <c r="I54" s="5" t="n">
+      <c r="I57" t="n">
         <v>2</v>
       </c>
-      <c r="J54" s="5" t="n">
+      <c r="J57" t="n">
         <v>6</v>
       </c>
-      <c r="K54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="5" t="n">
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
         <v>-1</v>
       </c>
-      <c r="O54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H54)*(1+(('⚙️ Calibrage'!$B$5+K54)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L54)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N54)/100))*((('⚙️ Calibrage'!$B$4+J54)+('⚙️ Calibrage'!$B$3+I54)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M54)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H57)*(1+(('⚙️ Calibrage'!$B$5+K57)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L57)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N57)/100))*((('⚙️ Calibrage'!$B$4+J57)+('⚙️ Calibrage'!$B$3+I57)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M57)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
-      <c r="Q54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="5" t="n"/>
-      <c r="S54" s="5" t="n">
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
         <v>120</v>
       </c>
-      <c r="T54" s="5" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>(D4)</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>tenu_de_mercen_re</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>tenu de mercenère</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>Corps</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>corps</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr"/>
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H55" t="n">
+      <c r="H58" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
+      <c r="I58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K55" t="n">
+      <c r="K58" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="L55" t="n">
+      <c r="L58" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="M55" t="n">
+      <c r="M58" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="N55" t="n">
+      <c r="N58" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H55)*(1+(('⚙️ Calibrage'!$B$5+K55)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L55)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N55)/100))*((('⚙️ Calibrage'!$B$4+J55)+('⚙️ Calibrage'!$B$3+I55)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M55)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+      <c r="O58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H58)*(1+(('⚙️ Calibrage'!$B$5+K58)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L58)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N58)/100))*((('⚙️ Calibrage'!$B$4+J58)+('⚙️ Calibrage'!$B$3+I58)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M58)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
         <v/>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
+      <c r="Q58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="5" t="n"/>
+      <c r="S58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="7" t="inlineStr">
         <is>
           <t>(D3)(D8)
 craft: tissu ,fourures ,griff de goblin
@@ -6569,221 +6787,15 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>aile_de_cuir</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>Aile de cuir</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="N56" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="O56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H56)*(1+(('⚙️ Calibrage'!$B$5+K56)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L56)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N56)/100))*((('⚙️ Calibrage'!$B$4+J56)+('⚙️ Calibrage'!$B$3+I56)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M56)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
-      <c r="Q56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="5" t="n"/>
-      <c r="S56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" s="5" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>aile_de_pierre</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Aile de pierre</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>9</v>
-      </c>
-      <c r="J57" t="n">
-        <v>30</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H57)*(1+(('⚙️ Calibrage'!$B$5+K57)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L57)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N57)/100))*((('⚙️ Calibrage'!$B$4+J57)+('⚙️ Calibrage'!$B$3+I57)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M57)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>brassard_de_cuir</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>Brassard de cuir</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr"/>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H58)*(1+(('⚙️ Calibrage'!$B$5+K58)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L58)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N58)/100))*((('⚙️ Calibrage'!$B$4+J58)+('⚙️ Calibrage'!$B$3+I58)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M58)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
-      <c r="Q58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="5" t="n"/>
-      <c r="S58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" s="5" t="inlineStr"/>
-    </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>cape_silencieuse</t>
+          <t>aile_de_cuir</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cape silencieuse</t>
+          <t>Aile de cuir</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6799,7 +6811,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6817,16 +6829,16 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>4</v>
+      </c>
+      <c r="N59" t="n">
         <v>5</v>
-      </c>
-      <c r="L59" t="n">
-        <v>10</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>4</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -6841,21 +6853,17 @@
       <c r="S59" t="n">
         <v>0</v>
       </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Annule la première attaque subie.</t>
-        </is>
-      </c>
+      <c r="T59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>ceinturon_cloute</t>
+          <t>aile_de_pierre</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Ceinturon clouté</t>
+          <t>Aile de pierre</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -6883,13 +6891,13 @@
         <v>0</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J60" s="5" t="n">
         <v>30</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L60" s="5" t="n">
         <v>0</v>
@@ -6898,7 +6906,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O60" s="5" t="n">
         <v>0</v>
@@ -6919,12 +6927,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ceinturon_epais</t>
+          <t>brassard_de_cuir</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ceinturon épais</t>
+          <t>Brassard de cuir</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6952,10 +6960,10 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -6967,7 +6975,7 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -6987,12 +6995,12 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>chaine_de_l_abime</t>
+          <t>wraith_cloak</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Chaîne de l'abîme</t>
+          <t>Cape du Spectre</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -7008,7 +7016,7 @@
       <c r="E62" s="5" t="inlineStr"/>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>legendary</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -7020,22 +7028,22 @@
         <v>0</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="K62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N62" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O62" s="5" t="n">
         <v>0</v>
@@ -7045,23 +7053,27 @@
         <v/>
       </c>
       <c r="Q62" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R62" s="5" t="n"/>
       <c r="S62" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T62" s="5" t="inlineStr"/>
+      <c r="T62" s="5" t="inlineStr">
+        <is>
+          <t>Elle ne projette aucune ombre. Ceux qui la portent non plus.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>chaine_spectrale</t>
+          <t>cape_silencieuse</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chaîne spectrale</t>
+          <t>Cape silencieuse</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7077,7 +7089,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -7089,22 +7101,22 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7119,17 +7131,21 @@
       <c r="S63" t="n">
         <v>0</v>
       </c>
-      <c r="T63" t="inlineStr"/>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Annule la première attaque subie.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>collier_de_perles</t>
+          <t>ceinturon_cloute</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Collier de perles</t>
+          <t>Ceinturon clouté</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -7145,7 +7161,7 @@
       <c r="E64" s="5" t="inlineStr"/>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -7157,13 +7173,13 @@
         <v>0</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="5" t="n">
         <v>0</v>
@@ -7182,7 +7198,7 @@
         <v/>
       </c>
       <c r="Q64" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R64" s="5" t="n"/>
       <c r="S64" s="5" t="n">
@@ -7193,12 +7209,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>collier_a_pointes</t>
+          <t>ceinturon_epais</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Collier à pointes</t>
+          <t>Ceinturon épais</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7214,7 +7230,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -7223,13 +7239,13 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -7261,12 +7277,12 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>fetiche_d_os</t>
+          <t>chaine_de_l_abime</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Fétiche d'os</t>
+          <t>Chaîne de l'abîme</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -7282,7 +7298,7 @@
       <c r="E66" s="5" t="inlineStr"/>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>uncommon</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -7294,13 +7310,13 @@
         <v>0</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L66" s="5" t="n">
         <v>0</v>
@@ -7330,12 +7346,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>sceau_de_corruption</t>
+          <t>chaine_spectrale</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sceau de corruption</t>
+          <t>Chaîne spectrale</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7351,7 +7367,7 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -7360,22 +7376,22 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J67" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -7398,12 +7414,12 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>voile_ectoplasmique</t>
+          <t>collier_de_perles</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Voile ectoplasmique</t>
+          <t>Collier de perles</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -7419,7 +7435,7 @@
       <c r="E68" s="5" t="inlineStr"/>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -7443,10 +7459,10 @@
         <v>0</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N68" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O68" s="5" t="n">
         <v>0</v>
@@ -7456,7 +7472,7 @@
         <v/>
       </c>
       <c r="Q68" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R68" s="5" t="n"/>
       <c r="S68" s="5" t="n">
@@ -7464,9 +7480,355 @@
       </c>
       <c r="T68" s="5" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>collier_a_pointes</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Collier à pointes</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>6</v>
+      </c>
+      <c r="I69" t="n">
+        <v>5</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H69)*(1+(('⚙️ Calibrage'!$B$5+K69)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L69)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N69)/100))*((('⚙️ Calibrage'!$B$4+J69)+('⚙️ Calibrage'!$B$3+I69)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M69)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>titan_gel_core</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Cœur de Gel du Titan</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr"/>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J70" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="P70" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H70)*(1+(('⚙️ Calibrage'!$B$5+K70)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L70)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N70)/100))*((('⚙️ Calibrage'!$B$4+J70)+('⚙️ Calibrage'!$B$3+I70)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M70)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="5" t="n"/>
+      <c r="S70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="5" t="inlineStr">
+        <is>
+          <t>Un noyau de gelée qui bat encore, arraché au Titan Visqueux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>fetiche_d_os</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Fétiche d'os</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>3</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H71)*(1+(('⚙️ Calibrage'!$B$5+K71)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L71)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N71)/100))*((('⚙️ Calibrage'!$B$4+J71)+('⚙️ Calibrage'!$B$3+I71)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M71)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>sceau_de_corruption</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Sceau de corruption</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr"/>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>legendary</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="M72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H72)*(1+(('⚙️ Calibrage'!$B$5+K72)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L72)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N72)/100))*((('⚙️ Calibrage'!$B$4+J72)+('⚙️ Calibrage'!$B$3+I72)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M72)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="5" t="n"/>
+      <c r="S72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>voile_ectoplasmique</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Voile ectoplasmique</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>6</v>
+      </c>
+      <c r="N73" t="n">
+        <v>3</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="6">
+        <f>ROUND((('⚙️ Calibrage'!$B$2+H73)*(1+(('⚙️ Calibrage'!$B$5+K73)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L73)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N73)/100))*((('⚙️ Calibrage'!$B$4+J73)+('⚙️ Calibrage'!$B$3+I73)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M73)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
+        <v/>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T68"/>
-  <conditionalFormatting sqref="P2:P68">
+  <autoFilter ref="A1:T73"/>
+  <conditionalFormatting sqref="P2:P73">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
